--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -440,7 +440,7 @@
         <v>T260911-00025</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -496,7 +496,7 @@
         <v>T260911-00024</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -552,7 +552,7 @@
         <v>T260911-00023</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -608,7 +608,7 @@
         <v>T260911-00022</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -664,7 +664,7 @@
         <v>T260911-00021</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -720,7 +720,7 @@
         <v>T260911-00020</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -776,7 +776,7 @@
         <v>T260911-00019</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -832,7 +832,7 @@
         <v>T260911-00018</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -888,7 +888,7 @@
         <v>T260911-00017</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -944,7 +944,7 @@
         <v>T260911-00016</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1000,7 +1000,7 @@
         <v>T260911-00015</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1056,7 +1056,7 @@
         <v>T260911-00014</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1112,7 +1112,7 @@
         <v>T260911-00013</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1168,7 +1168,7 @@
         <v>T260911-00012</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1224,7 +1224,7 @@
         <v>T260911-00011</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1280,7 +1280,7 @@
         <v>T260911-00010</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1336,7 +1336,7 @@
         <v>T260911-00009</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>천안FDC</v>
@@ -1392,7 +1392,7 @@
         <v>T260911-00008</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>샤오미 집하장</v>
@@ -1448,7 +1448,7 @@
         <v>T260911-00007</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>아이베</v>
@@ -1504,7 +1504,7 @@
         <v>T260911-00006</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -502,7 +502,7 @@
         <v>T260917-00024</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -561,7 +561,7 @@
         <v>T260917-00023</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -620,7 +620,7 @@
         <v>T260917-00022</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -679,7 +679,7 @@
         <v>T260917-00021</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -738,7 +738,7 @@
         <v>T260917-00019</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -797,7 +797,7 @@
         <v>T260917-00018</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -856,7 +856,7 @@
         <v>T260917-00016</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -915,7 +915,7 @@
         <v>T260917-00015</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -974,7 +974,7 @@
         <v>T260917-00014</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1033,7 +1033,7 @@
         <v>T260917-00013</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1092,7 +1092,7 @@
         <v>T260917-00012</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1151,7 +1151,7 @@
         <v>T260917-00011</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>남양주FDC</v>
@@ -1210,7 +1210,7 @@
         <v>T260917-00010</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>아이베</v>
@@ -1269,7 +1269,7 @@
         <v>T260917-00009</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -443,7 +443,7 @@
         <v>T260918-00019</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -502,7 +502,7 @@
         <v>T260918-00018</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -561,7 +561,7 @@
         <v>T260918-00017</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -620,7 +620,7 @@
         <v>T260918-00016</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -679,7 +679,7 @@
         <v>T260918-00015</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -738,7 +738,7 @@
         <v>T260918-00013</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -797,7 +797,7 @@
         <v>T260918-00012</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -856,7 +856,7 @@
         <v>T260918-00011</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -915,7 +915,7 @@
         <v>T260918-00010</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -974,7 +974,7 @@
         <v>T260918-00009</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1033,7 +1033,7 @@
         <v>T260918-00008</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1092,7 +1092,7 @@
         <v>T260918-00007</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1151,7 +1151,7 @@
         <v>T260918-00006</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1210,7 +1210,7 @@
         <v>T260918-00005</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1269,7 +1269,7 @@
         <v>T260918-00004</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>샤오미 집하장</v>
@@ -1328,7 +1328,7 @@
         <v>T260918-00003</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>아이베</v>
@@ -1387,7 +1387,7 @@
         <v>T260918-00002</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -1033,7 +1033,7 @@
         <v>T260921-00013</v>
       </c>
       <c r="B12" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1072,7 +1072,7 @@
         <v>2026-09-21 19:50:11</v>
       </c>
       <c r="O12" s="1">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="P12" s="1">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v/>
       </c>
       <c r="R12" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S12" t="str">
         <v>(주)위니온로지스</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -502,7 +502,7 @@
         <v>T260922-00026</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -561,7 +561,7 @@
         <v>T260922-00025</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -620,7 +620,7 @@
         <v>T260922-00024</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -679,7 +679,7 @@
         <v>T260922-00023</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -738,7 +738,7 @@
         <v>T260922-00022</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -797,7 +797,7 @@
         <v>T260922-00021</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -856,7 +856,7 @@
         <v>T260922-00020</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -915,7 +915,7 @@
         <v>T260922-00019</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -974,7 +974,7 @@
         <v>T260922-00018</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1033,7 +1033,7 @@
         <v>T260922-00017</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1092,7 +1092,7 @@
         <v>T260922-00016</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1151,7 +1151,7 @@
         <v>T260922-00015</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1210,7 +1210,7 @@
         <v>T260922-00014</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1269,7 +1269,7 @@
         <v>T260922-00013</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1328,7 +1328,7 @@
         <v>T260922-00012</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>샤오미 집하장</v>
@@ -1387,7 +1387,7 @@
         <v>T260922-00011</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>샤오미 집하장</v>
@@ -1446,7 +1446,7 @@
         <v>T260922-00010</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>아이베</v>
@@ -1505,7 +1505,7 @@
         <v>T260922-00009</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -443,7 +443,7 @@
         <v>T260923-00009</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -502,7 +502,7 @@
         <v>T260923-00008</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -561,7 +561,7 @@
         <v>T260923-00007</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -620,7 +620,7 @@
         <v>T260923-00006</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -679,7 +679,7 @@
         <v>T260923-00005</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -738,7 +738,7 @@
         <v>T260923-00004</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -797,7 +797,7 @@
         <v>T260923-00003</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>샤오미 집하장</v>
@@ -856,7 +856,7 @@
         <v>T260923-00002</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S509"/>
+  <dimension ref="A1:S460"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -27519,2900 +27519,9 @@
         <v>마이디어</v>
       </c>
     </row>
-    <row r="461">
-      <c r="A461" t="str">
-        <v>T260902-00030</v>
-      </c>
-      <c r="B461" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C461" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D461" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E461" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F461" t="str">
-        <v>대전중구ACP</v>
-      </c>
-      <c r="G461">
-        <v>1</v>
-      </c>
-      <c r="H461" t="str">
-        <v>대전대덕ACP</v>
-      </c>
-      <c r="I461" t="str">
-        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
-      </c>
-      <c r="J461" t="str">
-        <v>2026-09-03 06:00</v>
-      </c>
-      <c r="K461" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L461">
-        <v>1</v>
-      </c>
-      <c r="M461" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N461" t="str">
-        <v>2026-09-02 19:24:10</v>
-      </c>
-      <c r="O461" s="1">
-        <v>170000</v>
-      </c>
-      <c r="P461" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q461" t="str">
-        <v/>
-      </c>
-      <c r="R461" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S461" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="str">
-        <v>T260902-00029</v>
-      </c>
-      <c r="B462" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C462" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D462" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E462" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F462" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="G462">
-        <v>1</v>
-      </c>
-      <c r="H462" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="I462" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="J462" t="str">
-        <v>2026-09-03 07:00</v>
-      </c>
-      <c r="K462" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L462">
-        <v>1</v>
-      </c>
-      <c r="M462" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N462" t="str">
-        <v>2026-09-02 19:23:42</v>
-      </c>
-      <c r="O462" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P462" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q462" t="str">
-        <v/>
-      </c>
-      <c r="R462" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S462" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="str">
-        <v>T260902-00028</v>
-      </c>
-      <c r="B463" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C463" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D463" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E463" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F463" t="str">
-        <v>이천ACP,원주ACP</v>
-      </c>
-      <c r="G463">
-        <v>2</v>
-      </c>
-      <c r="H463" t="str">
-        <v>춘천ACP</v>
-      </c>
-      <c r="I463" t="str">
-        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
-      </c>
-      <c r="J463" t="str">
-        <v>2026-09-03 06:00</v>
-      </c>
-      <c r="K463" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L463">
-        <v>1</v>
-      </c>
-      <c r="M463" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N463" t="str">
-        <v>2026-09-02 19:23:13</v>
-      </c>
-      <c r="O463" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P463" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q463" t="str">
-        <v/>
-      </c>
-      <c r="R463" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S463" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="str">
-        <v>T260902-00027</v>
-      </c>
-      <c r="B464" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C464" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D464" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E464" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F464" t="str">
-        <v>군산ACP</v>
-      </c>
-      <c r="G464">
-        <v>1</v>
-      </c>
-      <c r="H464" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="I464" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="J464" t="str">
-        <v>2026-09-03 08:00</v>
-      </c>
-      <c r="K464" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L464">
-        <v>1</v>
-      </c>
-      <c r="M464" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N464" t="str">
-        <v>2026-09-02 19:22:37</v>
-      </c>
-      <c r="O464" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P464" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q464" t="str">
-        <v/>
-      </c>
-      <c r="R464" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S464" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="str">
-        <v>T260902-00026</v>
-      </c>
-      <c r="B465" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C465" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D465" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E465" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F465" t="str">
-        <v>용인ACP,화성ACP</v>
-      </c>
-      <c r="G465">
-        <v>2</v>
-      </c>
-      <c r="H465" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="I465" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="J465" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K465" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L465">
-        <v>1</v>
-      </c>
-      <c r="M465" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N465" t="str">
-        <v>2026-09-02 19:22:09</v>
-      </c>
-      <c r="O465" s="1">
-        <v>220000</v>
-      </c>
-      <c r="P465" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q465" t="str">
-        <v/>
-      </c>
-      <c r="R465" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S465" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="str">
-        <v>T260902-00025</v>
-      </c>
-      <c r="B466" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C466" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D466" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E466" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F466" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="G466">
-        <v>1</v>
-      </c>
-      <c r="H466" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="I466" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="J466" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K466" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L466">
-        <v>1</v>
-      </c>
-      <c r="M466" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N466" t="str">
-        <v>2026-09-02 19:21:37</v>
-      </c>
-      <c r="O466" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P466" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q466" t="str">
-        <v/>
-      </c>
-      <c r="R466" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S466" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="str">
-        <v>T260902-00024</v>
-      </c>
-      <c r="B467" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C467" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D467" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E467" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F467" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="G467">
-        <v>1</v>
-      </c>
-      <c r="H467" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="I467" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="J467" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K467" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L467">
-        <v>1</v>
-      </c>
-      <c r="M467" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N467" t="str">
-        <v>2026-09-02 19:21:17</v>
-      </c>
-      <c r="O467" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P467" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q467" t="str">
-        <v/>
-      </c>
-      <c r="R467" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S467" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="str">
-        <v>T260902-00023</v>
-      </c>
-      <c r="B468" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C468" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D468" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E468" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F468" t="str">
-        <v>원주FDC(신규)</v>
-      </c>
-      <c r="G468">
-        <v>1</v>
-      </c>
-      <c r="H468" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="I468" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="J468" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K468" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L468">
-        <v>1</v>
-      </c>
-      <c r="M468" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N468" t="str">
-        <v>2026-09-02 19:20:40</v>
-      </c>
-      <c r="O468" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P468" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q468" t="str">
-        <v/>
-      </c>
-      <c r="R468" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S468" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="str">
-        <v>T260902-00022</v>
-      </c>
-      <c r="B469" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C469" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D469" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E469" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F469" t="str">
-        <v>진주FDC,창원FDC</v>
-      </c>
-      <c r="G469">
-        <v>2</v>
-      </c>
-      <c r="H469" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="I469" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="J469" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K469" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L469">
-        <v>1</v>
-      </c>
-      <c r="M469" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N469" t="str">
-        <v>2026-09-02 19:20:16</v>
-      </c>
-      <c r="O469" s="1">
-        <v>730000</v>
-      </c>
-      <c r="P469" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q469" t="str">
-        <v/>
-      </c>
-      <c r="R469" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S469" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="str">
-        <v>T260902-00021</v>
-      </c>
-      <c r="B470" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C470" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D470" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E470" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F470" t="str">
-        <v/>
-      </c>
-      <c r="G470">
-        <v>0</v>
-      </c>
-      <c r="H470" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="I470" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="J470" t="str">
-        <v>2026-09-02 21:00</v>
-      </c>
-      <c r="K470" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L470">
-        <v>1</v>
-      </c>
-      <c r="M470" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N470" t="str">
-        <v>2026-09-02 19:19:46</v>
-      </c>
-      <c r="O470" s="1">
-        <v>250000</v>
-      </c>
-      <c r="P470" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q470" t="str">
-        <v/>
-      </c>
-      <c r="R470" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S470" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="str">
-        <v>T260902-00020</v>
-      </c>
-      <c r="B471" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C471" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D471" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E471" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F471" t="str">
-        <v/>
-      </c>
-      <c r="G471">
-        <v>0</v>
-      </c>
-      <c r="H471" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="I471" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="J471" t="str">
-        <v>2026-09-02 21:00</v>
-      </c>
-      <c r="K471" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L471">
-        <v>1</v>
-      </c>
-      <c r="M471" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N471" t="str">
-        <v>2026-09-02 19:19:30</v>
-      </c>
-      <c r="O471" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P471" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q471" t="str">
-        <v/>
-      </c>
-      <c r="R471" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S471" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="str">
-        <v>T260902-00019</v>
-      </c>
-      <c r="B472" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C472" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D472" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E472" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F472" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="G472">
-        <v>1</v>
-      </c>
-      <c r="H472" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="I472" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="J472" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K472" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L472">
-        <v>1</v>
-      </c>
-      <c r="M472" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N472" t="str">
-        <v>2026-09-02 19:19:13</v>
-      </c>
-      <c r="O472" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P472" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q472" t="str">
-        <v/>
-      </c>
-      <c r="R472" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S472" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="str">
-        <v>T260902-00018</v>
-      </c>
-      <c r="B473" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C473" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D473" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E473" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F473" t="str">
-        <v/>
-      </c>
-      <c r="G473">
-        <v>0</v>
-      </c>
-      <c r="H473" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="I473" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="J473" t="str">
-        <v>2026-09-02 21:00</v>
-      </c>
-      <c r="K473" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L473">
-        <v>1</v>
-      </c>
-      <c r="M473" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N473" t="str">
-        <v>2026-09-02 19:18:47</v>
-      </c>
-      <c r="O473" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P473" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q473" t="str">
-        <v/>
-      </c>
-      <c r="R473" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S473" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="str">
-        <v>T260902-00017</v>
-      </c>
-      <c r="B474" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C474" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D474" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E474" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F474" t="str">
-        <v>구미FDC(신규)</v>
-      </c>
-      <c r="G474">
-        <v>1</v>
-      </c>
-      <c r="H474" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="I474" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="J474" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K474" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L474">
-        <v>1</v>
-      </c>
-      <c r="M474" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N474" t="str">
-        <v>2026-09-02 19:17:37</v>
-      </c>
-      <c r="O474" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P474" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q474" t="str">
-        <v/>
-      </c>
-      <c r="R474" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S474" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="str">
-        <v>T260902-00016</v>
-      </c>
-      <c r="B475" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C475" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D475" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E475" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F475" t="str">
-        <v>강릉ACP</v>
-      </c>
-      <c r="G475">
-        <v>1</v>
-      </c>
-      <c r="H475" t="str">
-        <v>강릉FDC</v>
-      </c>
-      <c r="I475" t="str">
-        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
-      </c>
-      <c r="J475" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K475" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L475">
-        <v>1</v>
-      </c>
-      <c r="M475" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N475" t="str">
-        <v>2026-09-02 19:16:53</v>
-      </c>
-      <c r="O475" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P475" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q475" t="str">
-        <v/>
-      </c>
-      <c r="R475" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S475" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="str">
-        <v>T260902-00015</v>
-      </c>
-      <c r="B476" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C476" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D476" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E476" t="str">
-        <v>2026-09-02 18:10</v>
-      </c>
-      <c r="F476" t="str">
-        <v/>
-      </c>
-      <c r="G476">
-        <v>0</v>
-      </c>
-      <c r="H476" t="str">
-        <v>양산 하이마트 하이얼</v>
-      </c>
-      <c r="I476" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 하이얼</v>
-      </c>
-      <c r="J476" t="str">
-        <v>2026-09-03 21:30</v>
-      </c>
-      <c r="K476" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L476">
-        <v>1</v>
-      </c>
-      <c r="M476" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N476" t="str">
-        <v>2026-09-02 17:49:53</v>
-      </c>
-      <c r="O476" s="1">
-        <v>340000</v>
-      </c>
-      <c r="P476" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q476" t="str">
-        <v>하이얼 양산 하이마트 물류</v>
-      </c>
-      <c r="R476" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S476" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="str">
-        <v>T260902-00014</v>
-      </c>
-      <c r="B477" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C477" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D477" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E477" t="str">
-        <v>2026-09-02 17:30</v>
-      </c>
-      <c r="F477" t="str">
-        <v/>
-      </c>
-      <c r="G477">
-        <v>0</v>
-      </c>
-      <c r="H477" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="I477" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="J477" t="str">
-        <v>2026-09-02 18:30</v>
-      </c>
-      <c r="K477" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L477">
-        <v>1</v>
-      </c>
-      <c r="M477" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N477" t="str">
-        <v>2026-09-02 17:27:54</v>
-      </c>
-      <c r="O477" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P477" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q477" t="str">
-        <v/>
-      </c>
-      <c r="R477" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S477" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="str">
-        <v>T260902-00013</v>
-      </c>
-      <c r="B478" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C478" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="D478" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="E478" t="str">
-        <v>2026-09-02 11:00</v>
-      </c>
-      <c r="F478" t="str">
-        <v/>
-      </c>
-      <c r="G478">
-        <v>0</v>
-      </c>
-      <c r="H478" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I478" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J478" t="str">
-        <v>2026-09-02 13:30</v>
-      </c>
-      <c r="K478" t="str">
-        <v>1톤 기타차량</v>
-      </c>
-      <c r="L478">
-        <v>1</v>
-      </c>
-      <c r="M478" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N478" t="str">
-        <v>2026-09-02 17:27:24</v>
-      </c>
-      <c r="O478" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P478" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q478" t="str">
-        <v>거래처비용청구(1대)</v>
-      </c>
-      <c r="R478" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S478" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="str">
-        <v>T260902-00012</v>
-      </c>
-      <c r="B479" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C479" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D479" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E479" t="str">
-        <v>2026-09-02 14:30</v>
-      </c>
-      <c r="F479" t="str">
-        <v/>
-      </c>
-      <c r="G479">
-        <v>0</v>
-      </c>
-      <c r="H479" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I479" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J479" t="str">
-        <v>2026-09-02 15:30</v>
-      </c>
-      <c r="K479" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L479">
-        <v>1</v>
-      </c>
-      <c r="M479" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N479" t="str">
-        <v>2026-09-02 17:26:30</v>
-      </c>
-      <c r="O479" s="1">
-        <v>70000</v>
-      </c>
-      <c r="P479" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q479" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="R479" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S479" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="str">
-        <v>T260902-00011</v>
-      </c>
-      <c r="B480" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C480" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D480" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E480" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="F480" t="str">
-        <v/>
-      </c>
-      <c r="G480">
-        <v>0</v>
-      </c>
-      <c r="H480" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I480" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J480" t="str">
-        <v>2026-09-02 13:30</v>
-      </c>
-      <c r="K480" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L480">
-        <v>1</v>
-      </c>
-      <c r="M480" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N480" t="str">
-        <v>2026-09-02 17:25:43</v>
-      </c>
-      <c r="O480" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P480" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q480" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="R480" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S480" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="str">
-        <v>T260902-00010</v>
-      </c>
-      <c r="B481" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C481" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D481" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E481" t="str">
-        <v>2026-09-02 17:10</v>
-      </c>
-      <c r="F481" t="str">
-        <v/>
-      </c>
-      <c r="G481">
-        <v>0</v>
-      </c>
-      <c r="H481" t="str">
-        <v>마산 하이마트 하이얼</v>
-      </c>
-      <c r="I481" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 하이얼</v>
-      </c>
-      <c r="J481" t="str">
-        <v>2026-09-03 09:30</v>
-      </c>
-      <c r="K481" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L481">
-        <v>1</v>
-      </c>
-      <c r="M481" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N481" t="str">
-        <v>2026-09-02 16:04:12</v>
-      </c>
-      <c r="O481" s="1">
-        <v>340000</v>
-      </c>
-      <c r="P481" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q481" t="str">
-        <v>하이얼  마산 하이마트 물류</v>
-      </c>
-      <c r="R481" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S481" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="str">
-        <v>T260902-00009</v>
-      </c>
-      <c r="B482" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C482" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D482" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E482" t="str">
-        <v>2026-09-02 16:30</v>
-      </c>
-      <c r="F482" t="str">
-        <v/>
-      </c>
-      <c r="G482">
-        <v>0</v>
-      </c>
-      <c r="H482" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I482" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="J482" t="str">
-        <v>2026-09-02 17:30</v>
-      </c>
-      <c r="K482" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L482">
-        <v>1</v>
-      </c>
-      <c r="M482" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N482" t="str">
-        <v>2026-09-02 16:01:28</v>
-      </c>
-      <c r="O482" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P482" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q482" t="str">
-        <v/>
-      </c>
-      <c r="R482" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S482" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="str">
-        <v>T260902-00008</v>
-      </c>
-      <c r="B483" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C483" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D483" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E483" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="F483" t="str">
-        <v/>
-      </c>
-      <c r="G483">
-        <v>0</v>
-      </c>
-      <c r="H483" t="str">
-        <v>이천 하이마트 하이얼</v>
-      </c>
-      <c r="I483" t="str">
-        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 하이얼</v>
-      </c>
-      <c r="J483" t="str">
-        <v>2026-09-02 15:00</v>
-      </c>
-      <c r="K483" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L483">
-        <v>1</v>
-      </c>
-      <c r="M483" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N483" t="str">
-        <v>2026-09-02 10:54:59</v>
-      </c>
-      <c r="O483" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P483" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q483" t="str">
-        <v>하이얼 이천 하이마트 물류</v>
-      </c>
-      <c r="R483" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S483" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="str">
-        <v>T260902-00007</v>
-      </c>
-      <c r="B484" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C484" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D484" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E484" t="str">
-        <v>2026-09-02 09:40</v>
-      </c>
-      <c r="F484" t="str">
-        <v/>
-      </c>
-      <c r="G484">
-        <v>0</v>
-      </c>
-      <c r="H484" t="str">
-        <v>화성 하이마트 하이얼</v>
-      </c>
-      <c r="I484" t="str">
-        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 하이얼</v>
-      </c>
-      <c r="J484" t="str">
-        <v>2026-09-02 03:00</v>
-      </c>
-      <c r="K484" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L484">
-        <v>1</v>
-      </c>
-      <c r="M484" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N484" t="str">
-        <v>2026-09-02 10:50:30</v>
-      </c>
-      <c r="O484" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P484" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q484" t="str">
-        <v>히이얼 화성 하이마트 물류</v>
-      </c>
-      <c r="R484" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S484" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="str">
-        <v>T260902-00006</v>
-      </c>
-      <c r="B485" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C485" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D485" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E485" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F485" t="str">
-        <v/>
-      </c>
-      <c r="G485">
-        <v>0</v>
-      </c>
-      <c r="H485" t="str">
-        <v>인천 하이마트 하이얼</v>
-      </c>
-      <c r="I485" t="str">
-        <v>인천 중구 서해대로94번길 132 인천 하이마트 하이얼</v>
-      </c>
-      <c r="J485" t="str">
-        <v>2026-09-02 03:00</v>
-      </c>
-      <c r="K485" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L485">
-        <v>1</v>
-      </c>
-      <c r="M485" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N485" t="str">
-        <v>2026-09-02 10:36:26</v>
-      </c>
-      <c r="O485" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P485" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q485" t="str">
-        <v>하이얼 인천 하이마트 물류</v>
-      </c>
-      <c r="R485" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S485" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="str">
-        <v>T260902-00005</v>
-      </c>
-      <c r="B486" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C486" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D486" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E486" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F486" t="str">
-        <v/>
-      </c>
-      <c r="G486">
-        <v>0</v>
-      </c>
-      <c r="H486" t="str">
-        <v>아임테크날러지 창고</v>
-      </c>
-      <c r="I486" t="str">
-        <v>경기 김포시 통진읍 월하로479번길 32-42 가동, 나동</v>
-      </c>
-      <c r="J486" t="str">
-        <v>2026-09-02 11:00</v>
-      </c>
-      <c r="K486" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L486">
-        <v>1</v>
-      </c>
-      <c r="M486" t="str">
-        <v>차순권</v>
-      </c>
-      <c r="N486" t="str">
-        <v>2026-09-02 09:52:58</v>
-      </c>
-      <c r="O486" s="1">
-        <v>230000</v>
-      </c>
-      <c r="P486" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q486" t="str">
-        <v>아임테크 날러지 회수2, 가용 1파렛트 출하</v>
-      </c>
-      <c r="R486" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S486" t="str">
-        <v>아임테크날러지</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="str">
-        <v>T260902-00004</v>
-      </c>
-      <c r="B487" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C487" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D487" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E487" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F487" t="str">
-        <v/>
-      </c>
-      <c r="G487">
-        <v>0</v>
-      </c>
-      <c r="H487" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I487" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J487" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="K487" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L487">
-        <v>1</v>
-      </c>
-      <c r="M487" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N487" t="str">
-        <v>2026-09-02 09:49:55</v>
-      </c>
-      <c r="O487" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P487" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q487" t="str">
-        <v>중산물산 회수품</v>
-      </c>
-      <c r="R487" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S487" t="str">
-        <v>중산물산</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="str">
-        <v>T260902-00003</v>
-      </c>
-      <c r="B488" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C488" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D488" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E488" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F488" t="str">
-        <v/>
-      </c>
-      <c r="G488">
-        <v>0</v>
-      </c>
-      <c r="H488" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I488" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J488" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="K488" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L488">
-        <v>1</v>
-      </c>
-      <c r="M488" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N488" t="str">
-        <v>2026-09-02 09:37:44</v>
-      </c>
-      <c r="O488" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P488" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q488" t="str">
-        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
-      </c>
-      <c r="R488" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S488" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="str">
-        <v>T260902-00002</v>
-      </c>
-      <c r="B489" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C489" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D489" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E489" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F489" t="str">
-        <v/>
-      </c>
-      <c r="G489">
-        <v>0</v>
-      </c>
-      <c r="H489" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I489" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J489" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="K489" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L489">
-        <v>1</v>
-      </c>
-      <c r="M489" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N489" t="str">
-        <v>2026-09-02 09:37:02</v>
-      </c>
-      <c r="O489" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P489" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q489" t="str">
-        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
-      </c>
-      <c r="R489" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S489" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="str">
-        <v>T260902-00001</v>
-      </c>
-      <c r="B490" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C490" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D490" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E490" t="str">
-        <v>2026-09-02 09:50</v>
-      </c>
-      <c r="F490" t="str">
-        <v/>
-      </c>
-      <c r="G490">
-        <v>0</v>
-      </c>
-      <c r="H490" t="str">
-        <v>아임테크</v>
-      </c>
-      <c r="I490" t="str">
-        <v>경기 김포시 통진읍 귀전리 537-4 아임테크</v>
-      </c>
-      <c r="J490" t="str">
-        <v>2026-09-02 11:00</v>
-      </c>
-      <c r="K490" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L490">
-        <v>1</v>
-      </c>
-      <c r="M490" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N490" t="str">
-        <v>2026-09-02 09:33:24</v>
-      </c>
-      <c r="O490" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P490" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q490" t="str">
-        <v>아임테크날러지 전량 출하</v>
-      </c>
-      <c r="R490" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S490" t="str">
-        <v>아임테크날러지</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="str">
-        <v>T260901-00019</v>
-      </c>
-      <c r="B491" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C491" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D491" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E491" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F491" t="str">
-        <v>시흥ACP,인천ACP</v>
-      </c>
-      <c r="G491">
-        <v>2</v>
-      </c>
-      <c r="H491" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="I491" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="J491" t="str">
-        <v>2026-09-02 07:00</v>
-      </c>
-      <c r="K491" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L491">
-        <v>1</v>
-      </c>
-      <c r="M491" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N491" t="str">
-        <v>2026-09-01 19:27:06</v>
-      </c>
-      <c r="O491" s="1">
-        <v>230000</v>
-      </c>
-      <c r="P491" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q491" t="str">
-        <v/>
-      </c>
-      <c r="R491" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S491" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="str">
-        <v>T260901-00018</v>
-      </c>
-      <c r="B492" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C492" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D492" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E492" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F492" t="str">
-        <v>대전중구ACP,대전대덕ACP</v>
-      </c>
-      <c r="G492">
-        <v>2</v>
-      </c>
-      <c r="H492" t="str">
-        <v>군산ACP</v>
-      </c>
-      <c r="I492" t="str">
-        <v>전북특별자치도 군산시 구암3.1로 60 군산ACP</v>
-      </c>
-      <c r="J492" t="str">
-        <v>2026-09-02 07:00</v>
-      </c>
-      <c r="K492" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L492">
-        <v>1</v>
-      </c>
-      <c r="M492" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N492" t="str">
-        <v>2026-09-01 19:26:35</v>
-      </c>
-      <c r="O492" s="1">
-        <v>300000</v>
-      </c>
-      <c r="P492" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q492" t="str">
-        <v/>
-      </c>
-      <c r="R492" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S492" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="str">
-        <v>T260901-00017</v>
-      </c>
-      <c r="B493" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C493" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D493" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E493" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F493" t="str">
-        <v>안성ACP,화성ACP,용인ACP</v>
-      </c>
-      <c r="G493">
-        <v>3</v>
-      </c>
-      <c r="H493" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="I493" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="J493" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K493" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L493">
-        <v>1</v>
-      </c>
-      <c r="M493" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N493" t="str">
-        <v>2026-09-01 19:25:58</v>
-      </c>
-      <c r="O493" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P493" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q493" t="str">
-        <v/>
-      </c>
-      <c r="R493" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S493" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="str">
-        <v>T260901-00016</v>
-      </c>
-      <c r="B494" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C494" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D494" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E494" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F494" t="str">
-        <v/>
-      </c>
-      <c r="G494">
-        <v>0</v>
-      </c>
-      <c r="H494" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="I494" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="J494" t="str">
-        <v>2026-09-01 21:00</v>
-      </c>
-      <c r="K494" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L494">
-        <v>1</v>
-      </c>
-      <c r="M494" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N494" t="str">
-        <v>2026-09-01 19:25:13</v>
-      </c>
-      <c r="O494" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P494" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q494" t="str">
-        <v/>
-      </c>
-      <c r="R494" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S494" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="str">
-        <v>T260901-00015</v>
-      </c>
-      <c r="B495" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C495" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D495" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E495" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F495" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="G495">
-        <v>1</v>
-      </c>
-      <c r="H495" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="I495" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="J495" t="str">
-        <v>2026-09-01 22:00</v>
-      </c>
-      <c r="K495" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L495">
-        <v>1</v>
-      </c>
-      <c r="M495" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N495" t="str">
-        <v>2026-09-01 19:24:58</v>
-      </c>
-      <c r="O495" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P495" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q495" t="str">
-        <v/>
-      </c>
-      <c r="R495" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S495" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="str">
-        <v>T260901-00014</v>
-      </c>
-      <c r="B496" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C496" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D496" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E496" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F496" t="str">
-        <v/>
-      </c>
-      <c r="G496">
-        <v>0</v>
-      </c>
-      <c r="H496" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="I496" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="J496" t="str">
-        <v>2026-09-01 21:00</v>
-      </c>
-      <c r="K496" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L496">
-        <v>1</v>
-      </c>
-      <c r="M496" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N496" t="str">
-        <v>2026-09-01 19:24:38</v>
-      </c>
-      <c r="O496" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P496" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q496" t="str">
-        <v/>
-      </c>
-      <c r="R496" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S496" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="str">
-        <v>T260901-00013</v>
-      </c>
-      <c r="B497" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C497" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D497" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E497" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F497" t="str">
-        <v>원주FDC(신규)</v>
-      </c>
-      <c r="G497">
-        <v>1</v>
-      </c>
-      <c r="H497" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="I497" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="J497" t="str">
-        <v>2026-09-01 22:00</v>
-      </c>
-      <c r="K497" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L497">
-        <v>1</v>
-      </c>
-      <c r="M497" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N497" t="str">
-        <v>2026-09-01 19:24:22</v>
-      </c>
-      <c r="O497" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P497" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q497" t="str">
-        <v/>
-      </c>
-      <c r="R497" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S497" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="str">
-        <v>T260901-00012</v>
-      </c>
-      <c r="B498" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C498" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D498" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E498" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F498" t="str">
-        <v>진주FDC,창원FDC</v>
-      </c>
-      <c r="G498">
-        <v>2</v>
-      </c>
-      <c r="H498" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="I498" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="J498" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K498" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L498">
-        <v>1</v>
-      </c>
-      <c r="M498" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N498" t="str">
-        <v>2026-09-01 19:23:57</v>
-      </c>
-      <c r="O498" s="1">
-        <v>730000</v>
-      </c>
-      <c r="P498" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q498" t="str">
-        <v/>
-      </c>
-      <c r="R498" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S498" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="str">
-        <v>T260901-00011</v>
-      </c>
-      <c r="B499" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C499" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D499" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E499" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F499" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="G499">
-        <v>1</v>
-      </c>
-      <c r="H499" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="I499" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="J499" t="str">
-        <v>2026-09-01 22:00</v>
-      </c>
-      <c r="K499" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L499">
-        <v>1</v>
-      </c>
-      <c r="M499" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N499" t="str">
-        <v>2026-09-01 19:23:32</v>
-      </c>
-      <c r="O499" s="1">
-        <v>370000</v>
-      </c>
-      <c r="P499" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q499" t="str">
-        <v/>
-      </c>
-      <c r="R499" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S499" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="str">
-        <v>T260901-00010</v>
-      </c>
-      <c r="B500" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C500" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D500" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E500" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F500" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="G500">
-        <v>1</v>
-      </c>
-      <c r="H500" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="I500" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="J500" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K500" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L500">
-        <v>1</v>
-      </c>
-      <c r="M500" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N500" t="str">
-        <v>2026-09-01 19:23:13</v>
-      </c>
-      <c r="O500" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P500" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q500" t="str">
-        <v/>
-      </c>
-      <c r="R500" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S500" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="str">
-        <v>T260901-00009</v>
-      </c>
-      <c r="B501" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C501" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D501" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E501" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F501" t="str">
-        <v/>
-      </c>
-      <c r="G501">
-        <v>0</v>
-      </c>
-      <c r="H501" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="I501" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="J501" t="str">
-        <v>2026-09-01 21:00</v>
-      </c>
-      <c r="K501" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L501">
-        <v>1</v>
-      </c>
-      <c r="M501" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N501" t="str">
-        <v>2026-09-01 19:22:26</v>
-      </c>
-      <c r="O501" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P501" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q501" t="str">
-        <v/>
-      </c>
-      <c r="R501" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S501" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="str">
-        <v>T260901-00008</v>
-      </c>
-      <c r="B502" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C502" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D502" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E502" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F502" t="str">
-        <v>구미FDC(신규)</v>
-      </c>
-      <c r="G502">
-        <v>1</v>
-      </c>
-      <c r="H502" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="I502" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="J502" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K502" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L502">
-        <v>1</v>
-      </c>
-      <c r="M502" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N502" t="str">
-        <v>2026-09-01 19:22:10</v>
-      </c>
-      <c r="O502" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P502" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q502" t="str">
-        <v/>
-      </c>
-      <c r="R502" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S502" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="str">
-        <v>T260901-00007</v>
-      </c>
-      <c r="B503" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C503" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D503" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E503" t="str">
-        <v>2026-09-01 17:20</v>
-      </c>
-      <c r="F503" t="str">
-        <v/>
-      </c>
-      <c r="G503">
-        <v>0</v>
-      </c>
-      <c r="H503" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="I503" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="J503" t="str">
-        <v>2026-09-01 18:20</v>
-      </c>
-      <c r="K503" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L503">
-        <v>1</v>
-      </c>
-      <c r="M503" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N503" t="str">
-        <v>2026-09-01 19:20:06</v>
-      </c>
-      <c r="O503" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P503" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q503" t="str">
-        <v/>
-      </c>
-      <c r="R503" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S503" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="str">
-        <v>T260901-00006</v>
-      </c>
-      <c r="B504" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C504" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="D504" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="E504" t="str">
-        <v>2026-09-01 11:20</v>
-      </c>
-      <c r="F504" t="str">
-        <v/>
-      </c>
-      <c r="G504">
-        <v>0</v>
-      </c>
-      <c r="H504" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I504" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J504" t="str">
-        <v>2026-09-01 13:20</v>
-      </c>
-      <c r="K504" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L504">
-        <v>1</v>
-      </c>
-      <c r="M504" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N504" t="str">
-        <v>2026-09-01 19:19:31</v>
-      </c>
-      <c r="O504" s="1">
-        <v>120000</v>
-      </c>
-      <c r="P504" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q504" t="str">
-        <v>거래처비용청구(2대)</v>
-      </c>
-      <c r="R504" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S504" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="str">
-        <v>T260901-00005</v>
-      </c>
-      <c r="B505" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C505" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D505" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E505" t="str">
-        <v>2026-09-01 14:20</v>
-      </c>
-      <c r="F505" t="str">
-        <v/>
-      </c>
-      <c r="G505">
-        <v>0</v>
-      </c>
-      <c r="H505" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I505" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J505" t="str">
-        <v>2026-09-01 15:20</v>
-      </c>
-      <c r="K505" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L505">
-        <v>1</v>
-      </c>
-      <c r="M505" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N505" t="str">
-        <v>2026-09-01 19:18:39</v>
-      </c>
-      <c r="O505" s="1">
-        <v>70000</v>
-      </c>
-      <c r="P505" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q505" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="R505" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S505" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="str">
-        <v>T260901-00004</v>
-      </c>
-      <c r="B506" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C506" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D506" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E506" t="str">
-        <v>2026-09-01 15:50</v>
-      </c>
-      <c r="F506" t="str">
-        <v/>
-      </c>
-      <c r="G506">
-        <v>0</v>
-      </c>
-      <c r="H506" t="str">
-        <v>공주 하이마트 하이얼</v>
-      </c>
-      <c r="I506" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="J506" t="str">
-        <v>2026-09-02 15:00</v>
-      </c>
-      <c r="K506" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L506">
-        <v>1</v>
-      </c>
-      <c r="M506" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N506" t="str">
-        <v>2026-09-01 15:50:14</v>
-      </c>
-      <c r="O506" s="1">
-        <v>220000</v>
-      </c>
-      <c r="P506" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q506" t="str">
-        <v>하이얼 공주 하이마트 물류</v>
-      </c>
-      <c r="R506" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S506" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="str">
-        <v>T260901-00003</v>
-      </c>
-      <c r="B507" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C507" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D507" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E507" t="str">
-        <v>2026-09-01 15:35</v>
-      </c>
-      <c r="F507" t="str">
-        <v/>
-      </c>
-      <c r="G507">
-        <v>0</v>
-      </c>
-      <c r="H507" t="str">
-        <v>대구 하이마트 하이얼</v>
-      </c>
-      <c r="I507" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="J507" t="str">
-        <v>2026-09-02 15:00</v>
-      </c>
-      <c r="K507" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L507">
-        <v>1</v>
-      </c>
-      <c r="M507" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N507" t="str">
-        <v>2026-09-01 13:37:23</v>
-      </c>
-      <c r="O507" s="1">
-        <v>300000</v>
-      </c>
-      <c r="P507" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q507" t="str">
-        <v>하이얼 대구 하이마트 물류</v>
-      </c>
-      <c r="R507" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S507" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="str">
-        <v>T260901-00002</v>
-      </c>
-      <c r="B508" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C508" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="D508" t="str">
-        <v>인천 서구 오류동 1653-2 인천FDC</v>
-      </c>
-      <c r="E508" t="str">
-        <v>2026-09-02 08:00</v>
-      </c>
-      <c r="F508" t="str">
-        <v/>
-      </c>
-      <c r="G508">
-        <v>0</v>
-      </c>
-      <c r="H508" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="I508" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="J508" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="K508" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L508">
-        <v>1</v>
-      </c>
-      <c r="M508" t="str">
-        <v>차순권</v>
-      </c>
-      <c r="N508" t="str">
-        <v>2026-09-01 13:22:36</v>
-      </c>
-      <c r="O508" s="1">
-        <v>50000</v>
-      </c>
-      <c r="P508" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q508" t="str">
-        <v>접수번호 : 1565331 / 취소 건 샤오미 창고로 출하 / 인천FDC에서 직접 배송함</v>
-      </c>
-      <c r="R508" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S508" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="str">
-        <v>T260901-00001</v>
-      </c>
-      <c r="B509" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C509" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="D509" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 821 곤지암FDC</v>
-      </c>
-      <c r="E509" t="str">
-        <v>2026-09-01 08:00</v>
-      </c>
-      <c r="F509" t="str">
-        <v/>
-      </c>
-      <c r="G509">
-        <v>0</v>
-      </c>
-      <c r="H509" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I509" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J509" t="str">
-        <v>2026-09-01 10:00</v>
-      </c>
-      <c r="K509" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L509">
-        <v>1</v>
-      </c>
-      <c r="M509" t="str">
-        <v>차순권</v>
-      </c>
-      <c r="N509" t="str">
-        <v>2026-09-01 09:03:56</v>
-      </c>
-      <c r="O509" s="1">
-        <v>80000</v>
-      </c>
-      <c r="P509" s="1">
-        <v>5000</v>
-      </c>
-      <c r="Q509" t="str">
-        <v>하이얼 가용재고 10개 이동</v>
-      </c>
-      <c r="R509" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S509" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S509"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S460"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S460"/>
+  <dimension ref="A1:S509"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -27519,9 +27519,2900 @@
         <v>마이디어</v>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>T260902-00030</v>
+      </c>
+      <c r="B461" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C461" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D461" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E461" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F461" t="str">
+        <v>대전중구ACP</v>
+      </c>
+      <c r="G461">
+        <v>1</v>
+      </c>
+      <c r="H461" t="str">
+        <v>대전대덕ACP</v>
+      </c>
+      <c r="I461" t="str">
+        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
+      </c>
+      <c r="J461" t="str">
+        <v>2026-09-03 06:00</v>
+      </c>
+      <c r="K461" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L461">
+        <v>1</v>
+      </c>
+      <c r="M461" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N461" t="str">
+        <v>2026-09-02 19:24:10</v>
+      </c>
+      <c r="O461" s="1">
+        <v>170000</v>
+      </c>
+      <c r="P461" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q461" t="str">
+        <v/>
+      </c>
+      <c r="R461" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S461" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>T260902-00029</v>
+      </c>
+      <c r="B462" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C462" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D462" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E462" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F462" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="G462">
+        <v>1</v>
+      </c>
+      <c r="H462" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="I462" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="J462" t="str">
+        <v>2026-09-03 07:00</v>
+      </c>
+      <c r="K462" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L462">
+        <v>1</v>
+      </c>
+      <c r="M462" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N462" t="str">
+        <v>2026-09-02 19:23:42</v>
+      </c>
+      <c r="O462" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P462" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q462" t="str">
+        <v/>
+      </c>
+      <c r="R462" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S462" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>T260902-00028</v>
+      </c>
+      <c r="B463" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C463" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D463" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E463" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F463" t="str">
+        <v>이천ACP,원주ACP</v>
+      </c>
+      <c r="G463">
+        <v>2</v>
+      </c>
+      <c r="H463" t="str">
+        <v>춘천ACP</v>
+      </c>
+      <c r="I463" t="str">
+        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
+      </c>
+      <c r="J463" t="str">
+        <v>2026-09-03 06:00</v>
+      </c>
+      <c r="K463" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L463">
+        <v>1</v>
+      </c>
+      <c r="M463" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N463" t="str">
+        <v>2026-09-02 19:23:13</v>
+      </c>
+      <c r="O463" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P463" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q463" t="str">
+        <v/>
+      </c>
+      <c r="R463" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S463" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>T260902-00027</v>
+      </c>
+      <c r="B464" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C464" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D464" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E464" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F464" t="str">
+        <v>군산ACP</v>
+      </c>
+      <c r="G464">
+        <v>1</v>
+      </c>
+      <c r="H464" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="I464" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="J464" t="str">
+        <v>2026-09-03 08:00</v>
+      </c>
+      <c r="K464" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L464">
+        <v>1</v>
+      </c>
+      <c r="M464" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N464" t="str">
+        <v>2026-09-02 19:22:37</v>
+      </c>
+      <c r="O464" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P464" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q464" t="str">
+        <v/>
+      </c>
+      <c r="R464" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S464" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>T260902-00026</v>
+      </c>
+      <c r="B465" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C465" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D465" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E465" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F465" t="str">
+        <v>용인ACP,화성ACP</v>
+      </c>
+      <c r="G465">
+        <v>2</v>
+      </c>
+      <c r="H465" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="I465" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="J465" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K465" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L465">
+        <v>1</v>
+      </c>
+      <c r="M465" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N465" t="str">
+        <v>2026-09-02 19:22:09</v>
+      </c>
+      <c r="O465" s="1">
+        <v>220000</v>
+      </c>
+      <c r="P465" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q465" t="str">
+        <v/>
+      </c>
+      <c r="R465" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S465" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>T260902-00025</v>
+      </c>
+      <c r="B466" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C466" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D466" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E466" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F466" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="G466">
+        <v>1</v>
+      </c>
+      <c r="H466" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="I466" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="J466" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K466" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L466">
+        <v>1</v>
+      </c>
+      <c r="M466" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N466" t="str">
+        <v>2026-09-02 19:21:37</v>
+      </c>
+      <c r="O466" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P466" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q466" t="str">
+        <v/>
+      </c>
+      <c r="R466" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S466" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>T260902-00024</v>
+      </c>
+      <c r="B467" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C467" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D467" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E467" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F467" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="G467">
+        <v>1</v>
+      </c>
+      <c r="H467" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="I467" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="J467" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K467" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L467">
+        <v>1</v>
+      </c>
+      <c r="M467" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N467" t="str">
+        <v>2026-09-02 19:21:17</v>
+      </c>
+      <c r="O467" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P467" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q467" t="str">
+        <v/>
+      </c>
+      <c r="R467" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S467" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>T260902-00023</v>
+      </c>
+      <c r="B468" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C468" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D468" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E468" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F468" t="str">
+        <v>원주FDC(신규)</v>
+      </c>
+      <c r="G468">
+        <v>1</v>
+      </c>
+      <c r="H468" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="I468" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="J468" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K468" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L468">
+        <v>1</v>
+      </c>
+      <c r="M468" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N468" t="str">
+        <v>2026-09-02 19:20:40</v>
+      </c>
+      <c r="O468" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P468" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q468" t="str">
+        <v/>
+      </c>
+      <c r="R468" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S468" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>T260902-00022</v>
+      </c>
+      <c r="B469" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C469" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D469" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E469" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F469" t="str">
+        <v>진주FDC,창원FDC</v>
+      </c>
+      <c r="G469">
+        <v>2</v>
+      </c>
+      <c r="H469" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="I469" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="J469" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K469" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L469">
+        <v>1</v>
+      </c>
+      <c r="M469" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N469" t="str">
+        <v>2026-09-02 19:20:16</v>
+      </c>
+      <c r="O469" s="1">
+        <v>730000</v>
+      </c>
+      <c r="P469" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q469" t="str">
+        <v/>
+      </c>
+      <c r="R469" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S469" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>T260902-00021</v>
+      </c>
+      <c r="B470" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C470" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D470" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E470" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F470" t="str">
+        <v/>
+      </c>
+      <c r="G470">
+        <v>0</v>
+      </c>
+      <c r="H470" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="I470" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="J470" t="str">
+        <v>2026-09-02 21:00</v>
+      </c>
+      <c r="K470" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L470">
+        <v>1</v>
+      </c>
+      <c r="M470" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N470" t="str">
+        <v>2026-09-02 19:19:46</v>
+      </c>
+      <c r="O470" s="1">
+        <v>250000</v>
+      </c>
+      <c r="P470" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q470" t="str">
+        <v/>
+      </c>
+      <c r="R470" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S470" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>T260902-00020</v>
+      </c>
+      <c r="B471" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C471" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D471" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E471" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F471" t="str">
+        <v/>
+      </c>
+      <c r="G471">
+        <v>0</v>
+      </c>
+      <c r="H471" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="I471" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="J471" t="str">
+        <v>2026-09-02 21:00</v>
+      </c>
+      <c r="K471" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L471">
+        <v>1</v>
+      </c>
+      <c r="M471" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N471" t="str">
+        <v>2026-09-02 19:19:30</v>
+      </c>
+      <c r="O471" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P471" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q471" t="str">
+        <v/>
+      </c>
+      <c r="R471" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S471" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>T260902-00019</v>
+      </c>
+      <c r="B472" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C472" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D472" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E472" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F472" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="G472">
+        <v>1</v>
+      </c>
+      <c r="H472" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="I472" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="J472" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K472" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L472">
+        <v>1</v>
+      </c>
+      <c r="M472" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N472" t="str">
+        <v>2026-09-02 19:19:13</v>
+      </c>
+      <c r="O472" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P472" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q472" t="str">
+        <v/>
+      </c>
+      <c r="R472" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S472" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>T260902-00018</v>
+      </c>
+      <c r="B473" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C473" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D473" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E473" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F473" t="str">
+        <v/>
+      </c>
+      <c r="G473">
+        <v>0</v>
+      </c>
+      <c r="H473" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="I473" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="J473" t="str">
+        <v>2026-09-02 21:00</v>
+      </c>
+      <c r="K473" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L473">
+        <v>1</v>
+      </c>
+      <c r="M473" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N473" t="str">
+        <v>2026-09-02 19:18:47</v>
+      </c>
+      <c r="O473" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P473" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q473" t="str">
+        <v/>
+      </c>
+      <c r="R473" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S473" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>T260902-00017</v>
+      </c>
+      <c r="B474" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C474" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D474" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E474" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F474" t="str">
+        <v>구미FDC(신규)</v>
+      </c>
+      <c r="G474">
+        <v>1</v>
+      </c>
+      <c r="H474" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="I474" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="J474" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K474" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L474">
+        <v>1</v>
+      </c>
+      <c r="M474" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N474" t="str">
+        <v>2026-09-02 19:17:37</v>
+      </c>
+      <c r="O474" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P474" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q474" t="str">
+        <v/>
+      </c>
+      <c r="R474" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S474" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>T260902-00016</v>
+      </c>
+      <c r="B475" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C475" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D475" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E475" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F475" t="str">
+        <v>강릉ACP</v>
+      </c>
+      <c r="G475">
+        <v>1</v>
+      </c>
+      <c r="H475" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="I475" t="str">
+        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="J475" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K475" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L475">
+        <v>1</v>
+      </c>
+      <c r="M475" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N475" t="str">
+        <v>2026-09-02 19:16:53</v>
+      </c>
+      <c r="O475" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P475" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q475" t="str">
+        <v/>
+      </c>
+      <c r="R475" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S475" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>T260902-00015</v>
+      </c>
+      <c r="B476" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C476" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D476" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E476" t="str">
+        <v>2026-09-02 18:10</v>
+      </c>
+      <c r="F476" t="str">
+        <v/>
+      </c>
+      <c r="G476">
+        <v>0</v>
+      </c>
+      <c r="H476" t="str">
+        <v>양산 하이마트 하이얼</v>
+      </c>
+      <c r="I476" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 하이얼</v>
+      </c>
+      <c r="J476" t="str">
+        <v>2026-09-03 21:30</v>
+      </c>
+      <c r="K476" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L476">
+        <v>1</v>
+      </c>
+      <c r="M476" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N476" t="str">
+        <v>2026-09-02 17:49:53</v>
+      </c>
+      <c r="O476" s="1">
+        <v>340000</v>
+      </c>
+      <c r="P476" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q476" t="str">
+        <v>하이얼 양산 하이마트 물류</v>
+      </c>
+      <c r="R476" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S476" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>T260902-00014</v>
+      </c>
+      <c r="B477" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C477" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D477" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E477" t="str">
+        <v>2026-09-02 17:30</v>
+      </c>
+      <c r="F477" t="str">
+        <v/>
+      </c>
+      <c r="G477">
+        <v>0</v>
+      </c>
+      <c r="H477" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="I477" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="J477" t="str">
+        <v>2026-09-02 18:30</v>
+      </c>
+      <c r="K477" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L477">
+        <v>1</v>
+      </c>
+      <c r="M477" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N477" t="str">
+        <v>2026-09-02 17:27:54</v>
+      </c>
+      <c r="O477" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P477" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q477" t="str">
+        <v/>
+      </c>
+      <c r="R477" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S477" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>T260902-00013</v>
+      </c>
+      <c r="B478" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C478" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="D478" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="E478" t="str">
+        <v>2026-09-02 11:00</v>
+      </c>
+      <c r="F478" t="str">
+        <v/>
+      </c>
+      <c r="G478">
+        <v>0</v>
+      </c>
+      <c r="H478" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I478" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J478" t="str">
+        <v>2026-09-02 13:30</v>
+      </c>
+      <c r="K478" t="str">
+        <v>1톤 기타차량</v>
+      </c>
+      <c r="L478">
+        <v>1</v>
+      </c>
+      <c r="M478" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N478" t="str">
+        <v>2026-09-02 17:27:24</v>
+      </c>
+      <c r="O478" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P478" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q478" t="str">
+        <v>거래처비용청구(1대)</v>
+      </c>
+      <c r="R478" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S478" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>T260902-00012</v>
+      </c>
+      <c r="B479" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C479" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D479" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E479" t="str">
+        <v>2026-09-02 14:30</v>
+      </c>
+      <c r="F479" t="str">
+        <v/>
+      </c>
+      <c r="G479">
+        <v>0</v>
+      </c>
+      <c r="H479" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I479" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J479" t="str">
+        <v>2026-09-02 15:30</v>
+      </c>
+      <c r="K479" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L479">
+        <v>1</v>
+      </c>
+      <c r="M479" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N479" t="str">
+        <v>2026-09-02 17:26:30</v>
+      </c>
+      <c r="O479" s="1">
+        <v>70000</v>
+      </c>
+      <c r="P479" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q479" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="R479" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S479" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>T260902-00011</v>
+      </c>
+      <c r="B480" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C480" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D480" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E480" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="F480" t="str">
+        <v/>
+      </c>
+      <c r="G480">
+        <v>0</v>
+      </c>
+      <c r="H480" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I480" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J480" t="str">
+        <v>2026-09-02 13:30</v>
+      </c>
+      <c r="K480" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L480">
+        <v>1</v>
+      </c>
+      <c r="M480" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N480" t="str">
+        <v>2026-09-02 17:25:43</v>
+      </c>
+      <c r="O480" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P480" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q480" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="R480" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S480" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>T260902-00010</v>
+      </c>
+      <c r="B481" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C481" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D481" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E481" t="str">
+        <v>2026-09-02 17:10</v>
+      </c>
+      <c r="F481" t="str">
+        <v/>
+      </c>
+      <c r="G481">
+        <v>0</v>
+      </c>
+      <c r="H481" t="str">
+        <v>마산 하이마트 하이얼</v>
+      </c>
+      <c r="I481" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 하이얼</v>
+      </c>
+      <c r="J481" t="str">
+        <v>2026-09-03 09:30</v>
+      </c>
+      <c r="K481" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L481">
+        <v>1</v>
+      </c>
+      <c r="M481" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N481" t="str">
+        <v>2026-09-02 16:04:12</v>
+      </c>
+      <c r="O481" s="1">
+        <v>340000</v>
+      </c>
+      <c r="P481" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q481" t="str">
+        <v>하이얼  마산 하이마트 물류</v>
+      </c>
+      <c r="R481" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S481" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>T260902-00009</v>
+      </c>
+      <c r="B482" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C482" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D482" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E482" t="str">
+        <v>2026-09-02 16:30</v>
+      </c>
+      <c r="F482" t="str">
+        <v/>
+      </c>
+      <c r="G482">
+        <v>0</v>
+      </c>
+      <c r="H482" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I482" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="J482" t="str">
+        <v>2026-09-02 17:30</v>
+      </c>
+      <c r="K482" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L482">
+        <v>1</v>
+      </c>
+      <c r="M482" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N482" t="str">
+        <v>2026-09-02 16:01:28</v>
+      </c>
+      <c r="O482" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P482" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q482" t="str">
+        <v/>
+      </c>
+      <c r="R482" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S482" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>T260902-00008</v>
+      </c>
+      <c r="B483" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C483" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D483" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E483" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="F483" t="str">
+        <v/>
+      </c>
+      <c r="G483">
+        <v>0</v>
+      </c>
+      <c r="H483" t="str">
+        <v>이천 하이마트 하이얼</v>
+      </c>
+      <c r="I483" t="str">
+        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 하이얼</v>
+      </c>
+      <c r="J483" t="str">
+        <v>2026-09-02 15:00</v>
+      </c>
+      <c r="K483" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L483">
+        <v>1</v>
+      </c>
+      <c r="M483" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N483" t="str">
+        <v>2026-09-02 10:54:59</v>
+      </c>
+      <c r="O483" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P483" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q483" t="str">
+        <v>하이얼 이천 하이마트 물류</v>
+      </c>
+      <c r="R483" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S483" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>T260902-00007</v>
+      </c>
+      <c r="B484" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C484" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D484" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E484" t="str">
+        <v>2026-09-02 09:40</v>
+      </c>
+      <c r="F484" t="str">
+        <v/>
+      </c>
+      <c r="G484">
+        <v>0</v>
+      </c>
+      <c r="H484" t="str">
+        <v>화성 하이마트 하이얼</v>
+      </c>
+      <c r="I484" t="str">
+        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 하이얼</v>
+      </c>
+      <c r="J484" t="str">
+        <v>2026-09-02 03:00</v>
+      </c>
+      <c r="K484" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L484">
+        <v>1</v>
+      </c>
+      <c r="M484" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N484" t="str">
+        <v>2026-09-02 10:50:30</v>
+      </c>
+      <c r="O484" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P484" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q484" t="str">
+        <v>히이얼 화성 하이마트 물류</v>
+      </c>
+      <c r="R484" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S484" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>T260902-00006</v>
+      </c>
+      <c r="B485" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C485" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D485" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E485" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F485" t="str">
+        <v/>
+      </c>
+      <c r="G485">
+        <v>0</v>
+      </c>
+      <c r="H485" t="str">
+        <v>인천 하이마트 하이얼</v>
+      </c>
+      <c r="I485" t="str">
+        <v>인천 중구 서해대로94번길 132 인천 하이마트 하이얼</v>
+      </c>
+      <c r="J485" t="str">
+        <v>2026-09-02 03:00</v>
+      </c>
+      <c r="K485" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L485">
+        <v>1</v>
+      </c>
+      <c r="M485" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N485" t="str">
+        <v>2026-09-02 10:36:26</v>
+      </c>
+      <c r="O485" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P485" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q485" t="str">
+        <v>하이얼 인천 하이마트 물류</v>
+      </c>
+      <c r="R485" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S485" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>T260902-00005</v>
+      </c>
+      <c r="B486" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C486" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D486" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E486" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F486" t="str">
+        <v/>
+      </c>
+      <c r="G486">
+        <v>0</v>
+      </c>
+      <c r="H486" t="str">
+        <v>아임테크날러지 창고</v>
+      </c>
+      <c r="I486" t="str">
+        <v>경기 김포시 통진읍 월하로479번길 32-42 가동, 나동</v>
+      </c>
+      <c r="J486" t="str">
+        <v>2026-09-02 11:00</v>
+      </c>
+      <c r="K486" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L486">
+        <v>1</v>
+      </c>
+      <c r="M486" t="str">
+        <v>차순권</v>
+      </c>
+      <c r="N486" t="str">
+        <v>2026-09-02 09:52:58</v>
+      </c>
+      <c r="O486" s="1">
+        <v>230000</v>
+      </c>
+      <c r="P486" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q486" t="str">
+        <v>아임테크 날러지 회수2, 가용 1파렛트 출하</v>
+      </c>
+      <c r="R486" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S486" t="str">
+        <v>아임테크날러지</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>T260902-00004</v>
+      </c>
+      <c r="B487" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C487" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D487" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E487" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F487" t="str">
+        <v/>
+      </c>
+      <c r="G487">
+        <v>0</v>
+      </c>
+      <c r="H487" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I487" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J487" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="K487" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L487">
+        <v>1</v>
+      </c>
+      <c r="M487" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N487" t="str">
+        <v>2026-09-02 09:49:55</v>
+      </c>
+      <c r="O487" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P487" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q487" t="str">
+        <v>중산물산 회수품</v>
+      </c>
+      <c r="R487" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S487" t="str">
+        <v>중산물산</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>T260902-00003</v>
+      </c>
+      <c r="B488" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C488" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D488" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E488" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F488" t="str">
+        <v/>
+      </c>
+      <c r="G488">
+        <v>0</v>
+      </c>
+      <c r="H488" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I488" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J488" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="K488" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L488">
+        <v>1</v>
+      </c>
+      <c r="M488" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N488" t="str">
+        <v>2026-09-02 09:37:44</v>
+      </c>
+      <c r="O488" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P488" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q488" t="str">
+        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
+      </c>
+      <c r="R488" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S488" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>T260902-00002</v>
+      </c>
+      <c r="B489" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C489" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D489" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E489" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F489" t="str">
+        <v/>
+      </c>
+      <c r="G489">
+        <v>0</v>
+      </c>
+      <c r="H489" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I489" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J489" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="K489" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L489">
+        <v>1</v>
+      </c>
+      <c r="M489" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N489" t="str">
+        <v>2026-09-02 09:37:02</v>
+      </c>
+      <c r="O489" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P489" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q489" t="str">
+        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
+      </c>
+      <c r="R489" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S489" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>T260902-00001</v>
+      </c>
+      <c r="B490" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C490" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D490" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E490" t="str">
+        <v>2026-09-02 09:50</v>
+      </c>
+      <c r="F490" t="str">
+        <v/>
+      </c>
+      <c r="G490">
+        <v>0</v>
+      </c>
+      <c r="H490" t="str">
+        <v>아임테크</v>
+      </c>
+      <c r="I490" t="str">
+        <v>경기 김포시 통진읍 귀전리 537-4 아임테크</v>
+      </c>
+      <c r="J490" t="str">
+        <v>2026-09-02 11:00</v>
+      </c>
+      <c r="K490" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L490">
+        <v>1</v>
+      </c>
+      <c r="M490" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N490" t="str">
+        <v>2026-09-02 09:33:24</v>
+      </c>
+      <c r="O490" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P490" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q490" t="str">
+        <v>아임테크날러지 전량 출하</v>
+      </c>
+      <c r="R490" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S490" t="str">
+        <v>아임테크날러지</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>T260901-00019</v>
+      </c>
+      <c r="B491" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C491" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D491" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E491" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F491" t="str">
+        <v>시흥ACP,인천ACP</v>
+      </c>
+      <c r="G491">
+        <v>2</v>
+      </c>
+      <c r="H491" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="I491" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="J491" t="str">
+        <v>2026-09-02 07:00</v>
+      </c>
+      <c r="K491" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L491">
+        <v>1</v>
+      </c>
+      <c r="M491" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N491" t="str">
+        <v>2026-09-01 19:27:06</v>
+      </c>
+      <c r="O491" s="1">
+        <v>230000</v>
+      </c>
+      <c r="P491" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q491" t="str">
+        <v/>
+      </c>
+      <c r="R491" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S491" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>T260901-00018</v>
+      </c>
+      <c r="B492" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C492" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D492" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E492" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F492" t="str">
+        <v>대전중구ACP,대전대덕ACP</v>
+      </c>
+      <c r="G492">
+        <v>2</v>
+      </c>
+      <c r="H492" t="str">
+        <v>군산ACP</v>
+      </c>
+      <c r="I492" t="str">
+        <v>전북특별자치도 군산시 구암3.1로 60 군산ACP</v>
+      </c>
+      <c r="J492" t="str">
+        <v>2026-09-02 07:00</v>
+      </c>
+      <c r="K492" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L492">
+        <v>1</v>
+      </c>
+      <c r="M492" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N492" t="str">
+        <v>2026-09-01 19:26:35</v>
+      </c>
+      <c r="O492" s="1">
+        <v>300000</v>
+      </c>
+      <c r="P492" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q492" t="str">
+        <v/>
+      </c>
+      <c r="R492" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S492" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>T260901-00017</v>
+      </c>
+      <c r="B493" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C493" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D493" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E493" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F493" t="str">
+        <v>안성ACP,화성ACP,용인ACP</v>
+      </c>
+      <c r="G493">
+        <v>3</v>
+      </c>
+      <c r="H493" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="I493" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="J493" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K493" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L493">
+        <v>1</v>
+      </c>
+      <c r="M493" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N493" t="str">
+        <v>2026-09-01 19:25:58</v>
+      </c>
+      <c r="O493" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P493" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q493" t="str">
+        <v/>
+      </c>
+      <c r="R493" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S493" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>T260901-00016</v>
+      </c>
+      <c r="B494" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C494" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D494" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E494" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F494" t="str">
+        <v/>
+      </c>
+      <c r="G494">
+        <v>0</v>
+      </c>
+      <c r="H494" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="I494" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="J494" t="str">
+        <v>2026-09-01 21:00</v>
+      </c>
+      <c r="K494" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L494">
+        <v>1</v>
+      </c>
+      <c r="M494" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N494" t="str">
+        <v>2026-09-01 19:25:13</v>
+      </c>
+      <c r="O494" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P494" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q494" t="str">
+        <v/>
+      </c>
+      <c r="R494" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S494" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>T260901-00015</v>
+      </c>
+      <c r="B495" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C495" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D495" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E495" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F495" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="G495">
+        <v>1</v>
+      </c>
+      <c r="H495" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="I495" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="J495" t="str">
+        <v>2026-09-01 22:00</v>
+      </c>
+      <c r="K495" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L495">
+        <v>1</v>
+      </c>
+      <c r="M495" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N495" t="str">
+        <v>2026-09-01 19:24:58</v>
+      </c>
+      <c r="O495" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P495" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q495" t="str">
+        <v/>
+      </c>
+      <c r="R495" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S495" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>T260901-00014</v>
+      </c>
+      <c r="B496" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C496" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D496" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E496" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F496" t="str">
+        <v/>
+      </c>
+      <c r="G496">
+        <v>0</v>
+      </c>
+      <c r="H496" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="I496" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="J496" t="str">
+        <v>2026-09-01 21:00</v>
+      </c>
+      <c r="K496" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L496">
+        <v>1</v>
+      </c>
+      <c r="M496" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N496" t="str">
+        <v>2026-09-01 19:24:38</v>
+      </c>
+      <c r="O496" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P496" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q496" t="str">
+        <v/>
+      </c>
+      <c r="R496" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S496" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>T260901-00013</v>
+      </c>
+      <c r="B497" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C497" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D497" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E497" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F497" t="str">
+        <v>원주FDC(신규)</v>
+      </c>
+      <c r="G497">
+        <v>1</v>
+      </c>
+      <c r="H497" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="I497" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="J497" t="str">
+        <v>2026-09-01 22:00</v>
+      </c>
+      <c r="K497" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L497">
+        <v>1</v>
+      </c>
+      <c r="M497" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N497" t="str">
+        <v>2026-09-01 19:24:22</v>
+      </c>
+      <c r="O497" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P497" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q497" t="str">
+        <v/>
+      </c>
+      <c r="R497" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S497" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
+        <v>T260901-00012</v>
+      </c>
+      <c r="B498" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C498" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D498" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E498" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F498" t="str">
+        <v>진주FDC,창원FDC</v>
+      </c>
+      <c r="G498">
+        <v>2</v>
+      </c>
+      <c r="H498" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="I498" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="J498" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K498" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L498">
+        <v>1</v>
+      </c>
+      <c r="M498" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N498" t="str">
+        <v>2026-09-01 19:23:57</v>
+      </c>
+      <c r="O498" s="1">
+        <v>730000</v>
+      </c>
+      <c r="P498" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q498" t="str">
+        <v/>
+      </c>
+      <c r="R498" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S498" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>T260901-00011</v>
+      </c>
+      <c r="B499" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C499" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D499" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E499" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F499" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="G499">
+        <v>1</v>
+      </c>
+      <c r="H499" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="I499" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="J499" t="str">
+        <v>2026-09-01 22:00</v>
+      </c>
+      <c r="K499" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L499">
+        <v>1</v>
+      </c>
+      <c r="M499" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N499" t="str">
+        <v>2026-09-01 19:23:32</v>
+      </c>
+      <c r="O499" s="1">
+        <v>370000</v>
+      </c>
+      <c r="P499" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q499" t="str">
+        <v/>
+      </c>
+      <c r="R499" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S499" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>T260901-00010</v>
+      </c>
+      <c r="B500" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C500" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D500" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E500" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F500" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="G500">
+        <v>1</v>
+      </c>
+      <c r="H500" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="I500" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="J500" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K500" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L500">
+        <v>1</v>
+      </c>
+      <c r="M500" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N500" t="str">
+        <v>2026-09-01 19:23:13</v>
+      </c>
+      <c r="O500" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P500" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q500" t="str">
+        <v/>
+      </c>
+      <c r="R500" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S500" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>T260901-00009</v>
+      </c>
+      <c r="B501" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C501" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D501" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E501" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F501" t="str">
+        <v/>
+      </c>
+      <c r="G501">
+        <v>0</v>
+      </c>
+      <c r="H501" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="I501" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="J501" t="str">
+        <v>2026-09-01 21:00</v>
+      </c>
+      <c r="K501" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L501">
+        <v>1</v>
+      </c>
+      <c r="M501" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N501" t="str">
+        <v>2026-09-01 19:22:26</v>
+      </c>
+      <c r="O501" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P501" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q501" t="str">
+        <v/>
+      </c>
+      <c r="R501" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S501" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
+        <v>T260901-00008</v>
+      </c>
+      <c r="B502" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C502" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D502" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E502" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F502" t="str">
+        <v>구미FDC(신규)</v>
+      </c>
+      <c r="G502">
+        <v>1</v>
+      </c>
+      <c r="H502" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="I502" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="J502" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K502" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L502">
+        <v>1</v>
+      </c>
+      <c r="M502" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N502" t="str">
+        <v>2026-09-01 19:22:10</v>
+      </c>
+      <c r="O502" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P502" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q502" t="str">
+        <v/>
+      </c>
+      <c r="R502" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S502" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>T260901-00007</v>
+      </c>
+      <c r="B503" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C503" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D503" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E503" t="str">
+        <v>2026-09-01 17:20</v>
+      </c>
+      <c r="F503" t="str">
+        <v/>
+      </c>
+      <c r="G503">
+        <v>0</v>
+      </c>
+      <c r="H503" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="I503" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="J503" t="str">
+        <v>2026-09-01 18:20</v>
+      </c>
+      <c r="K503" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L503">
+        <v>1</v>
+      </c>
+      <c r="M503" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N503" t="str">
+        <v>2026-09-01 19:20:06</v>
+      </c>
+      <c r="O503" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P503" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q503" t="str">
+        <v/>
+      </c>
+      <c r="R503" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S503" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>T260901-00006</v>
+      </c>
+      <c r="B504" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C504" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="D504" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="E504" t="str">
+        <v>2026-09-01 11:20</v>
+      </c>
+      <c r="F504" t="str">
+        <v/>
+      </c>
+      <c r="G504">
+        <v>0</v>
+      </c>
+      <c r="H504" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I504" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J504" t="str">
+        <v>2026-09-01 13:20</v>
+      </c>
+      <c r="K504" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L504">
+        <v>1</v>
+      </c>
+      <c r="M504" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N504" t="str">
+        <v>2026-09-01 19:19:31</v>
+      </c>
+      <c r="O504" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P504" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q504" t="str">
+        <v>거래처비용청구(2대)</v>
+      </c>
+      <c r="R504" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S504" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>T260901-00005</v>
+      </c>
+      <c r="B505" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C505" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D505" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E505" t="str">
+        <v>2026-09-01 14:20</v>
+      </c>
+      <c r="F505" t="str">
+        <v/>
+      </c>
+      <c r="G505">
+        <v>0</v>
+      </c>
+      <c r="H505" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I505" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J505" t="str">
+        <v>2026-09-01 15:20</v>
+      </c>
+      <c r="K505" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L505">
+        <v>1</v>
+      </c>
+      <c r="M505" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N505" t="str">
+        <v>2026-09-01 19:18:39</v>
+      </c>
+      <c r="O505" s="1">
+        <v>70000</v>
+      </c>
+      <c r="P505" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q505" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="R505" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S505" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>T260901-00004</v>
+      </c>
+      <c r="B506" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C506" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D506" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E506" t="str">
+        <v>2026-09-01 15:50</v>
+      </c>
+      <c r="F506" t="str">
+        <v/>
+      </c>
+      <c r="G506">
+        <v>0</v>
+      </c>
+      <c r="H506" t="str">
+        <v>공주 하이마트 하이얼</v>
+      </c>
+      <c r="I506" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="J506" t="str">
+        <v>2026-09-02 15:00</v>
+      </c>
+      <c r="K506" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L506">
+        <v>1</v>
+      </c>
+      <c r="M506" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N506" t="str">
+        <v>2026-09-01 15:50:14</v>
+      </c>
+      <c r="O506" s="1">
+        <v>220000</v>
+      </c>
+      <c r="P506" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q506" t="str">
+        <v>하이얼 공주 하이마트 물류</v>
+      </c>
+      <c r="R506" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S506" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>T260901-00003</v>
+      </c>
+      <c r="B507" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C507" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D507" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E507" t="str">
+        <v>2026-09-01 15:35</v>
+      </c>
+      <c r="F507" t="str">
+        <v/>
+      </c>
+      <c r="G507">
+        <v>0</v>
+      </c>
+      <c r="H507" t="str">
+        <v>대구 하이마트 하이얼</v>
+      </c>
+      <c r="I507" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="J507" t="str">
+        <v>2026-09-02 15:00</v>
+      </c>
+      <c r="K507" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L507">
+        <v>1</v>
+      </c>
+      <c r="M507" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N507" t="str">
+        <v>2026-09-01 13:37:23</v>
+      </c>
+      <c r="O507" s="1">
+        <v>300000</v>
+      </c>
+      <c r="P507" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q507" t="str">
+        <v>하이얼 대구 하이마트 물류</v>
+      </c>
+      <c r="R507" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S507" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>T260901-00002</v>
+      </c>
+      <c r="B508" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C508" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="D508" t="str">
+        <v>인천 서구 오류동 1653-2 인천FDC</v>
+      </c>
+      <c r="E508" t="str">
+        <v>2026-09-02 08:00</v>
+      </c>
+      <c r="F508" t="str">
+        <v/>
+      </c>
+      <c r="G508">
+        <v>0</v>
+      </c>
+      <c r="H508" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="I508" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="J508" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="K508" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L508">
+        <v>1</v>
+      </c>
+      <c r="M508" t="str">
+        <v>차순권</v>
+      </c>
+      <c r="N508" t="str">
+        <v>2026-09-01 13:22:36</v>
+      </c>
+      <c r="O508" s="1">
+        <v>50000</v>
+      </c>
+      <c r="P508" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q508" t="str">
+        <v>접수번호 : 1565331 / 취소 건 샤오미 창고로 출하 / 인천FDC에서 직접 배송함</v>
+      </c>
+      <c r="R508" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S508" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>T260901-00001</v>
+      </c>
+      <c r="B509" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C509" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="D509" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 821 곤지암FDC</v>
+      </c>
+      <c r="E509" t="str">
+        <v>2026-09-01 08:00</v>
+      </c>
+      <c r="F509" t="str">
+        <v/>
+      </c>
+      <c r="G509">
+        <v>0</v>
+      </c>
+      <c r="H509" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I509" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J509" t="str">
+        <v>2026-09-01 10:00</v>
+      </c>
+      <c r="K509" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L509">
+        <v>1</v>
+      </c>
+      <c r="M509" t="str">
+        <v>차순권</v>
+      </c>
+      <c r="N509" t="str">
+        <v>2026-09-01 09:03:56</v>
+      </c>
+      <c r="O509" s="1">
+        <v>80000</v>
+      </c>
+      <c r="P509" s="1">
+        <v>5000</v>
+      </c>
+      <c r="Q509" t="str">
+        <v>하이얼 가용재고 10개 이동</v>
+      </c>
+      <c r="R509" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S509" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S460"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S509"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -443,7 +443,7 @@
         <v>T261002-00019</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -502,7 +502,7 @@
         <v>T261002-00018</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -561,7 +561,7 @@
         <v>T261002-00017</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -620,7 +620,7 @@
         <v>T261002-00016</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -679,7 +679,7 @@
         <v>T261002-00015</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -738,7 +738,7 @@
         <v>T261002-00014</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -797,7 +797,7 @@
         <v>T261002-00013</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -856,7 +856,7 @@
         <v>T261002-00012</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -915,7 +915,7 @@
         <v>T261002-00011</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -974,7 +974,7 @@
         <v>T261002-00010</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1033,7 +1033,7 @@
         <v>T261002-00009</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1092,7 +1092,7 @@
         <v>T261002-00008</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1151,7 +1151,7 @@
         <v>T261002-00007</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>인천FDC</v>
@@ -1210,7 +1210,7 @@
         <v>T261002-00006</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>샤오미 집하장</v>
@@ -1269,7 +1269,7 @@
         <v>T261002-00005</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>아이베</v>
@@ -1328,7 +1328,7 @@
         <v>T261002-00004</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S509"/>
+  <dimension ref="A1:S431"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -25808,4611 +25808,9 @@
         <v>일코전자</v>
       </c>
     </row>
-    <row r="432">
-      <c r="A432" t="str">
-        <v>T260903-00029</v>
-      </c>
-      <c r="B432" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C432" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D432" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E432" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F432" t="str">
-        <v>시흥ACP,인천ACP</v>
-      </c>
-      <c r="G432">
-        <v>2</v>
-      </c>
-      <c r="H432" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="I432" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="J432" t="str">
-        <v>2026-09-04 08:00</v>
-      </c>
-      <c r="K432" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L432">
-        <v>1</v>
-      </c>
-      <c r="M432" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N432" t="str">
-        <v>2026-09-03 18:24:00</v>
-      </c>
-      <c r="O432" s="1">
-        <v>230000</v>
-      </c>
-      <c r="P432" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q432" t="str">
-        <v/>
-      </c>
-      <c r="R432" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S432" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="str">
-        <v>T260903-00028</v>
-      </c>
-      <c r="B433" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C433" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D433" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E433" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F433" t="str">
-        <v>대전중구ACP,군산ACP</v>
-      </c>
-      <c r="G433">
-        <v>2</v>
-      </c>
-      <c r="H433" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="I433" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="J433" t="str">
-        <v>2026-09-04 07:00</v>
-      </c>
-      <c r="K433" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L433">
-        <v>1</v>
-      </c>
-      <c r="M433" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N433" t="str">
-        <v>2026-09-03 18:23:24</v>
-      </c>
-      <c r="O433" s="1">
-        <v>300000</v>
-      </c>
-      <c r="P433" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q433" t="str">
-        <v/>
-      </c>
-      <c r="R433" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S433" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="str">
-        <v>T260903-00027</v>
-      </c>
-      <c r="B434" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C434" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D434" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E434" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F434" t="str">
-        <v>안성ACP,용인ACP,화성ACP</v>
-      </c>
-      <c r="G434">
-        <v>3</v>
-      </c>
-      <c r="H434" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="I434" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="J434" t="str">
-        <v>2026-09-03 23:00</v>
-      </c>
-      <c r="K434" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L434">
-        <v>1</v>
-      </c>
-      <c r="M434" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N434" t="str">
-        <v>2026-09-03 18:22:50</v>
-      </c>
-      <c r="O434" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P434" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q434" t="str">
-        <v/>
-      </c>
-      <c r="R434" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S434" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="str">
-        <v>T260903-00026</v>
-      </c>
-      <c r="B435" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C435" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D435" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E435" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F435" t="str">
-        <v/>
-      </c>
-      <c r="G435">
-        <v>0</v>
-      </c>
-      <c r="H435" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="I435" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="J435" t="str">
-        <v>2026-09-03 21:00</v>
-      </c>
-      <c r="K435" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L435">
-        <v>1</v>
-      </c>
-      <c r="M435" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N435" t="str">
-        <v>2026-09-03 18:22:08</v>
-      </c>
-      <c r="O435" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P435" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q435" t="str">
-        <v/>
-      </c>
-      <c r="R435" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S435" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="str">
-        <v>T260903-00025</v>
-      </c>
-      <c r="B436" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C436" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D436" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E436" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F436" t="str">
-        <v/>
-      </c>
-      <c r="G436">
-        <v>0</v>
-      </c>
-      <c r="H436" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="I436" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="J436" t="str">
-        <v>2026-09-03 22:00</v>
-      </c>
-      <c r="K436" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L436">
-        <v>1</v>
-      </c>
-      <c r="M436" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N436" t="str">
-        <v>2026-09-03 18:21:51</v>
-      </c>
-      <c r="O436" s="1">
-        <v>230000</v>
-      </c>
-      <c r="P436" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q436" t="str">
-        <v/>
-      </c>
-      <c r="R436" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S436" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="str">
-        <v>T260903-00024</v>
-      </c>
-      <c r="B437" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C437" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D437" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E437" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F437" t="str">
-        <v/>
-      </c>
-      <c r="G437">
-        <v>0</v>
-      </c>
-      <c r="H437" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="I437" t="str">
-        <v>인천 검단구 오류동 1653-2 인천FDC</v>
-      </c>
-      <c r="J437" t="str">
-        <v>2026-09-03 21:00</v>
-      </c>
-      <c r="K437" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L437">
-        <v>1</v>
-      </c>
-      <c r="M437" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N437" t="str">
-        <v>2026-09-03 18:21:35</v>
-      </c>
-      <c r="O437" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P437" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q437" t="str">
-        <v/>
-      </c>
-      <c r="R437" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S437" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="str">
-        <v>T260903-00023</v>
-      </c>
-      <c r="B438" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C438" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D438" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E438" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F438" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="G438">
-        <v>1</v>
-      </c>
-      <c r="H438" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="I438" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="J438" t="str">
-        <v>2026-09-03 22:00</v>
-      </c>
-      <c r="K438" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L438">
-        <v>1</v>
-      </c>
-      <c r="M438" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N438" t="str">
-        <v>2026-09-03 18:21:18</v>
-      </c>
-      <c r="O438" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P438" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q438" t="str">
-        <v/>
-      </c>
-      <c r="R438" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S438" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="str">
-        <v>T260903-00022</v>
-      </c>
-      <c r="B439" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C439" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D439" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E439" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F439" t="str">
-        <v>원주FDC(신규)</v>
-      </c>
-      <c r="G439">
-        <v>1</v>
-      </c>
-      <c r="H439" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="I439" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="J439" t="str">
-        <v>2026-09-03 22:00</v>
-      </c>
-      <c r="K439" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L439">
-        <v>1</v>
-      </c>
-      <c r="M439" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N439" t="str">
-        <v>2026-09-03 18:20:56</v>
-      </c>
-      <c r="O439" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P439" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q439" t="str">
-        <v/>
-      </c>
-      <c r="R439" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S439" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="str">
-        <v>T260903-00021</v>
-      </c>
-      <c r="B440" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C440" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D440" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E440" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F440" t="str">
-        <v>진주FDC,창원FDC</v>
-      </c>
-      <c r="G440">
-        <v>2</v>
-      </c>
-      <c r="H440" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="I440" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="J440" t="str">
-        <v>2026-09-03 23:00</v>
-      </c>
-      <c r="K440" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L440">
-        <v>1</v>
-      </c>
-      <c r="M440" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N440" t="str">
-        <v>2026-09-03 18:20:35</v>
-      </c>
-      <c r="O440" s="1">
-        <v>730000</v>
-      </c>
-      <c r="P440" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q440" t="str">
-        <v/>
-      </c>
-      <c r="R440" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S440" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="str">
-        <v>T260903-00020</v>
-      </c>
-      <c r="B441" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C441" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D441" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E441" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F441" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="G441">
-        <v>1</v>
-      </c>
-      <c r="H441" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="I441" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="J441" t="str">
-        <v>2026-09-03 22:00</v>
-      </c>
-      <c r="K441" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L441">
-        <v>1</v>
-      </c>
-      <c r="M441" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N441" t="str">
-        <v>2026-09-03 18:20:07</v>
-      </c>
-      <c r="O441" s="1">
-        <v>370000</v>
-      </c>
-      <c r="P441" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q441" t="str">
-        <v/>
-      </c>
-      <c r="R441" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S441" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="str">
-        <v>T260903-00019</v>
-      </c>
-      <c r="B442" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C442" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D442" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E442" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F442" t="str">
-        <v/>
-      </c>
-      <c r="G442">
-        <v>0</v>
-      </c>
-      <c r="H442" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="I442" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="J442" t="str">
-        <v>2026-09-03 23:00</v>
-      </c>
-      <c r="K442" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L442">
-        <v>1</v>
-      </c>
-      <c r="M442" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N442" t="str">
-        <v>2026-09-03 18:19:48</v>
-      </c>
-      <c r="O442" s="1">
-        <v>420000</v>
-      </c>
-      <c r="P442" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q442" t="str">
-        <v/>
-      </c>
-      <c r="R442" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S442" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="str">
-        <v>T260903-00018</v>
-      </c>
-      <c r="B443" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C443" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D443" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E443" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F443" t="str">
-        <v/>
-      </c>
-      <c r="G443">
-        <v>0</v>
-      </c>
-      <c r="H443" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="I443" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="J443" t="str">
-        <v>2026-09-03 21:00</v>
-      </c>
-      <c r="K443" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L443">
-        <v>1</v>
-      </c>
-      <c r="M443" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N443" t="str">
-        <v>2026-09-03 18:19:30</v>
-      </c>
-      <c r="O443" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P443" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q443" t="str">
-        <v/>
-      </c>
-      <c r="R443" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S443" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="str">
-        <v>T260903-00017</v>
-      </c>
-      <c r="B444" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C444" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D444" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E444" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F444" t="str">
-        <v>구미FDC(신규)</v>
-      </c>
-      <c r="G444">
-        <v>1</v>
-      </c>
-      <c r="H444" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="I444" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="J444" t="str">
-        <v>2026-09-03 23:00</v>
-      </c>
-      <c r="K444" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L444">
-        <v>1</v>
-      </c>
-      <c r="M444" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N444" t="str">
-        <v>2026-09-03 18:19:12</v>
-      </c>
-      <c r="O444" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P444" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q444" t="str">
-        <v/>
-      </c>
-      <c r="R444" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S444" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="str">
-        <v>T260903-00016</v>
-      </c>
-      <c r="B445" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C445" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D445" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E445" t="str">
-        <v>2026-09-03 18:00</v>
-      </c>
-      <c r="F445" t="str">
-        <v/>
-      </c>
-      <c r="G445">
-        <v>0</v>
-      </c>
-      <c r="H445" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="I445" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="J445" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="K445" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L445">
-        <v>1</v>
-      </c>
-      <c r="M445" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N445" t="str">
-        <v>2026-09-03 17:43:12</v>
-      </c>
-      <c r="O445" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P445" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q445" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="R445" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S445" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="str">
-        <v>T260903-00015</v>
-      </c>
-      <c r="B446" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C446" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D446" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E446" t="str">
-        <v>2026-09-03 17:30</v>
-      </c>
-      <c r="F446" t="str">
-        <v/>
-      </c>
-      <c r="G446">
-        <v>0</v>
-      </c>
-      <c r="H446" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="I446" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="J446" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="K446" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L446">
-        <v>1</v>
-      </c>
-      <c r="M446" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N446" t="str">
-        <v>2026-09-03 17:10:21</v>
-      </c>
-      <c r="O446" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P446" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q446" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="R446" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S446" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="str">
-        <v>T260903-00014</v>
-      </c>
-      <c r="B447" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C447" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D447" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E447" t="str">
-        <v>2026-09-03 17:30</v>
-      </c>
-      <c r="F447" t="str">
-        <v/>
-      </c>
-      <c r="G447">
-        <v>0</v>
-      </c>
-      <c r="H447" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="I447" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="J447" t="str">
-        <v>2026-09-04 21:00</v>
-      </c>
-      <c r="K447" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L447">
-        <v>1</v>
-      </c>
-      <c r="M447" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N447" t="str">
-        <v>2026-09-03 17:09:57</v>
-      </c>
-      <c r="O447" s="1">
-        <v>220000</v>
-      </c>
-      <c r="P447" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q447" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="R447" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S447" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="str">
-        <v>T260903-00013</v>
-      </c>
-      <c r="B448" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C448" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="D448" t="str">
-        <v>충남 아산시 음봉면 월랑리 440 천안FDC</v>
-      </c>
-      <c r="E448" t="str">
-        <v>2026-09-03 21:30</v>
-      </c>
-      <c r="F448" t="str">
-        <v/>
-      </c>
-      <c r="G448">
-        <v>0</v>
-      </c>
-      <c r="H448" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="I448" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="J448" t="str">
-        <v>2026-09-03 22:30</v>
-      </c>
-      <c r="K448" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L448">
-        <v>1</v>
-      </c>
-      <c r="M448" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N448" t="str">
-        <v>2026-09-03 16:23:31</v>
-      </c>
-      <c r="O448" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P448" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q448" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="R448" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S448" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="str">
-        <v>T260903-00012</v>
-      </c>
-      <c r="B449" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C449" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D449" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E449" t="str">
-        <v>2026-09-03 16:30</v>
-      </c>
-      <c r="F449" t="str">
-        <v/>
-      </c>
-      <c r="G449">
-        <v>0</v>
-      </c>
-      <c r="H449" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I449" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="J449" t="str">
-        <v>2026-09-03 17:30</v>
-      </c>
-      <c r="K449" t="str">
-        <v>1톤 카고/윙</v>
-      </c>
-      <c r="L449">
-        <v>1</v>
-      </c>
-      <c r="M449" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N449" t="str">
-        <v>2026-09-03 15:51:43</v>
-      </c>
-      <c r="O449" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P449" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q449" t="str">
-        <v/>
-      </c>
-      <c r="R449" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S449" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="str">
-        <v>T260903-00011</v>
-      </c>
-      <c r="B450" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C450" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D450" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E450" t="str">
-        <v>2026-09-03 17:30</v>
-      </c>
-      <c r="F450" t="str">
-        <v/>
-      </c>
-      <c r="G450">
-        <v>0</v>
-      </c>
-      <c r="H450" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="I450" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="J450" t="str">
-        <v>2026-09-03 18:30</v>
-      </c>
-      <c r="K450" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L450">
-        <v>1</v>
-      </c>
-      <c r="M450" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N450" t="str">
-        <v>2026-09-03 15:32:57</v>
-      </c>
-      <c r="O450" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P450" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q450" t="str">
-        <v/>
-      </c>
-      <c r="R450" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S450" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="str">
-        <v>T260903-00010</v>
-      </c>
-      <c r="B451" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C451" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="D451" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 821 곤지암FDC</v>
-      </c>
-      <c r="E451" t="str">
-        <v>2026-09-03 21:30</v>
-      </c>
-      <c r="F451" t="str">
-        <v/>
-      </c>
-      <c r="G451">
-        <v>0</v>
-      </c>
-      <c r="H451" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="I451" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="J451" t="str">
-        <v>2026-09-04 08:30</v>
-      </c>
-      <c r="K451" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L451">
-        <v>1</v>
-      </c>
-      <c r="M451" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N451" t="str">
-        <v>2026-09-03 15:32:28</v>
-      </c>
-      <c r="O451" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P451" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q451" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="R451" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S451" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="str">
-        <v>T260903-00009</v>
-      </c>
-      <c r="B452" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C452" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="D452" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5 김포FDC</v>
-      </c>
-      <c r="E452" t="str">
-        <v>2026-09-03 09:00</v>
-      </c>
-      <c r="F452" t="str">
-        <v/>
-      </c>
-      <c r="G452">
-        <v>0</v>
-      </c>
-      <c r="H452" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="I452" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="J452" t="str">
-        <v>2026-09-03 11:30</v>
-      </c>
-      <c r="K452" t="str">
-        <v>5톤 카고</v>
-      </c>
-      <c r="L452">
-        <v>1</v>
-      </c>
-      <c r="M452" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N452" t="str">
-        <v>2026-09-03 15:31:34</v>
-      </c>
-      <c r="O452" s="1">
-        <v>250000</v>
-      </c>
-      <c r="P452" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q452" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="R452" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S452" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="str">
-        <v>T260903-00008</v>
-      </c>
-      <c r="B453" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C453" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="D453" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="E453" t="str">
-        <v>2026-09-03 11:00</v>
-      </c>
-      <c r="F453" t="str">
-        <v/>
-      </c>
-      <c r="G453">
-        <v>0</v>
-      </c>
-      <c r="H453" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I453" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J453" t="str">
-        <v>2026-09-03 13:30</v>
-      </c>
-      <c r="K453" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L453">
-        <v>1</v>
-      </c>
-      <c r="M453" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N453" t="str">
-        <v>2026-09-03 15:30:52</v>
-      </c>
-      <c r="O453" s="1">
-        <v>120000</v>
-      </c>
-      <c r="P453" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q453" t="str">
-        <v>거래처비용청구(3대)</v>
-      </c>
-      <c r="R453" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S453" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="str">
-        <v>T260903-00007</v>
-      </c>
-      <c r="B454" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C454" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D454" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E454" t="str">
-        <v>2026-09-03 14:30</v>
-      </c>
-      <c r="F454" t="str">
-        <v/>
-      </c>
-      <c r="G454">
-        <v>0</v>
-      </c>
-      <c r="H454" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I454" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J454" t="str">
-        <v>2026-09-03 15:30</v>
-      </c>
-      <c r="K454" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L454">
-        <v>1</v>
-      </c>
-      <c r="M454" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N454" t="str">
-        <v>2026-09-03 15:30:00</v>
-      </c>
-      <c r="O454" s="1">
-        <v>70000</v>
-      </c>
-      <c r="P454" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q454" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="R454" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S454" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="str">
-        <v>T260903-00006</v>
-      </c>
-      <c r="B455" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C455" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D455" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E455" t="str">
-        <v>2026-09-03 10:00</v>
-      </c>
-      <c r="F455" t="str">
-        <v/>
-      </c>
-      <c r="G455">
-        <v>0</v>
-      </c>
-      <c r="H455" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I455" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J455" t="str">
-        <v>2026-09-03 13:30</v>
-      </c>
-      <c r="K455" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L455">
-        <v>1</v>
-      </c>
-      <c r="M455" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N455" t="str">
-        <v>2026-09-03 15:29:14</v>
-      </c>
-      <c r="O455" s="1">
-        <v>160000</v>
-      </c>
-      <c r="P455" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q455" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="R455" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S455" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="str">
-        <v>T260903-00005</v>
-      </c>
-      <c r="B456" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C456" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D456" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E456" t="str">
-        <v>2026-09-03 13:50</v>
-      </c>
-      <c r="F456" t="str">
-        <v/>
-      </c>
-      <c r="G456">
-        <v>0</v>
-      </c>
-      <c r="H456" t="str">
-        <v>펠리체산후조리원하이얼</v>
-      </c>
-      <c r="I456" t="str">
-        <v>경기 화성시 만세구 꽃내음1길 19-22 펠리체산후조리원 하이얼</v>
-      </c>
-      <c r="J456" t="str">
-        <v>2026-09-03 16:00</v>
-      </c>
-      <c r="K456" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="L456">
-        <v>1</v>
-      </c>
-      <c r="M456" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N456" t="str">
-        <v>2026-09-03 13:37:58</v>
-      </c>
-      <c r="O456" s="1">
-        <v>110000</v>
-      </c>
-      <c r="P456" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q456" t="str">
-        <v/>
-      </c>
-      <c r="R456" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S456" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="str">
-        <v>T260903-00004</v>
-      </c>
-      <c r="B457" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C457" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D457" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E457" t="str">
-        <v>2026-09-03 16:00</v>
-      </c>
-      <c r="F457" t="str">
-        <v/>
-      </c>
-      <c r="G457">
-        <v>0</v>
-      </c>
-      <c r="H457" t="str">
-        <v>광주 하이마트 물류</v>
-      </c>
-      <c r="I457" t="str">
-        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
-      </c>
-      <c r="J457" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="K457" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L457">
-        <v>1</v>
-      </c>
-      <c r="M457" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N457" t="str">
-        <v>2026-09-03 13:14:56</v>
-      </c>
-      <c r="O457" s="1">
-        <v>400000</v>
-      </c>
-      <c r="P457" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q457" t="str">
-        <v>일코전자 광주 하이마트 물류</v>
-      </c>
-      <c r="R457" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S457" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="str">
-        <v>T260903-00003</v>
-      </c>
-      <c r="B458" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C458" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D458" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E458" t="str">
-        <v>2026-09-03 15:00</v>
-      </c>
-      <c r="F458" t="str">
-        <v/>
-      </c>
-      <c r="G458">
-        <v>0</v>
-      </c>
-      <c r="H458" t="str">
-        <v>대구 하이마트 물류</v>
-      </c>
-      <c r="I458" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="J458" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="K458" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L458">
-        <v>1</v>
-      </c>
-      <c r="M458" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N458" t="str">
-        <v>2026-09-03 10:24:04</v>
-      </c>
-      <c r="O458" s="1">
-        <v>340000</v>
-      </c>
-      <c r="P458" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q458" t="str">
-        <v>일코전자 대구 하이마트 물류</v>
-      </c>
-      <c r="R458" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S458" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="str">
-        <v>T260903-00002</v>
-      </c>
-      <c r="B459" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C459" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D459" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E459" t="str">
-        <v>2026-09-03 10:10</v>
-      </c>
-      <c r="F459" t="str">
-        <v/>
-      </c>
-      <c r="G459">
-        <v>0</v>
-      </c>
-      <c r="H459" t="str">
-        <v>마이디어 늘품마루</v>
-      </c>
-      <c r="I459" t="str">
-        <v>경기 이천시 백사면 지읍로 54 지하 2층 33번 도크</v>
-      </c>
-      <c r="J459" t="str">
-        <v>2026-09-03 11:30</v>
-      </c>
-      <c r="K459" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="L459">
-        <v>1</v>
-      </c>
-      <c r="M459" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N459" t="str">
-        <v>2026-09-03 10:23:19</v>
-      </c>
-      <c r="O459" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P459" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q459" t="str">
-        <v>마이디어 늘품마루</v>
-      </c>
-      <c r="R459" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S459" t="str">
-        <v>마이디어</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="str">
-        <v>T260903-00001</v>
-      </c>
-      <c r="B460" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C460" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D460" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E460" t="str">
-        <v>2026-09-03 09:00</v>
-      </c>
-      <c r="F460" t="str">
-        <v/>
-      </c>
-      <c r="G460">
-        <v>0</v>
-      </c>
-      <c r="H460" t="str">
-        <v>마이디어 늘품마루</v>
-      </c>
-      <c r="I460" t="str">
-        <v>경기 이천시 백사면 지읍로 54 지하 2층 33번 도크</v>
-      </c>
-      <c r="J460" t="str">
-        <v>2026-09-03 11:00</v>
-      </c>
-      <c r="K460" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="L460">
-        <v>1</v>
-      </c>
-      <c r="M460" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N460" t="str">
-        <v>2026-09-03 09:06:29</v>
-      </c>
-      <c r="O460" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P460" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q460" t="str">
-        <v>마이디어 늘품마루</v>
-      </c>
-      <c r="R460" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S460" t="str">
-        <v>마이디어</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="str">
-        <v>T260902-00030</v>
-      </c>
-      <c r="B461" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C461" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D461" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E461" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F461" t="str">
-        <v>대전중구ACP</v>
-      </c>
-      <c r="G461">
-        <v>1</v>
-      </c>
-      <c r="H461" t="str">
-        <v>대전대덕ACP</v>
-      </c>
-      <c r="I461" t="str">
-        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
-      </c>
-      <c r="J461" t="str">
-        <v>2026-09-03 06:00</v>
-      </c>
-      <c r="K461" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L461">
-        <v>1</v>
-      </c>
-      <c r="M461" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N461" t="str">
-        <v>2026-09-02 19:24:10</v>
-      </c>
-      <c r="O461" s="1">
-        <v>170000</v>
-      </c>
-      <c r="P461" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q461" t="str">
-        <v/>
-      </c>
-      <c r="R461" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S461" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="str">
-        <v>T260902-00029</v>
-      </c>
-      <c r="B462" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C462" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D462" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E462" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F462" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="G462">
-        <v>1</v>
-      </c>
-      <c r="H462" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="I462" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="J462" t="str">
-        <v>2026-09-03 07:00</v>
-      </c>
-      <c r="K462" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L462">
-        <v>1</v>
-      </c>
-      <c r="M462" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N462" t="str">
-        <v>2026-09-02 19:23:42</v>
-      </c>
-      <c r="O462" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P462" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q462" t="str">
-        <v/>
-      </c>
-      <c r="R462" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S462" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="str">
-        <v>T260902-00028</v>
-      </c>
-      <c r="B463" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C463" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D463" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E463" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F463" t="str">
-        <v>이천ACP,원주ACP</v>
-      </c>
-      <c r="G463">
-        <v>2</v>
-      </c>
-      <c r="H463" t="str">
-        <v>춘천ACP</v>
-      </c>
-      <c r="I463" t="str">
-        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
-      </c>
-      <c r="J463" t="str">
-        <v>2026-09-03 06:00</v>
-      </c>
-      <c r="K463" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L463">
-        <v>1</v>
-      </c>
-      <c r="M463" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N463" t="str">
-        <v>2026-09-02 19:23:13</v>
-      </c>
-      <c r="O463" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P463" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q463" t="str">
-        <v/>
-      </c>
-      <c r="R463" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S463" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="str">
-        <v>T260902-00027</v>
-      </c>
-      <c r="B464" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C464" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D464" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E464" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F464" t="str">
-        <v>군산ACP</v>
-      </c>
-      <c r="G464">
-        <v>1</v>
-      </c>
-      <c r="H464" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="I464" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="J464" t="str">
-        <v>2026-09-03 08:00</v>
-      </c>
-      <c r="K464" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L464">
-        <v>1</v>
-      </c>
-      <c r="M464" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N464" t="str">
-        <v>2026-09-02 19:22:37</v>
-      </c>
-      <c r="O464" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P464" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q464" t="str">
-        <v/>
-      </c>
-      <c r="R464" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S464" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="str">
-        <v>T260902-00026</v>
-      </c>
-      <c r="B465" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C465" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D465" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E465" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F465" t="str">
-        <v>용인ACP,화성ACP</v>
-      </c>
-      <c r="G465">
-        <v>2</v>
-      </c>
-      <c r="H465" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="I465" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="J465" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K465" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L465">
-        <v>1</v>
-      </c>
-      <c r="M465" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N465" t="str">
-        <v>2026-09-02 19:22:09</v>
-      </c>
-      <c r="O465" s="1">
-        <v>220000</v>
-      </c>
-      <c r="P465" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q465" t="str">
-        <v/>
-      </c>
-      <c r="R465" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S465" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="str">
-        <v>T260902-00025</v>
-      </c>
-      <c r="B466" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C466" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D466" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E466" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F466" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="G466">
-        <v>1</v>
-      </c>
-      <c r="H466" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="I466" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="J466" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K466" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L466">
-        <v>1</v>
-      </c>
-      <c r="M466" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N466" t="str">
-        <v>2026-09-02 19:21:37</v>
-      </c>
-      <c r="O466" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P466" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q466" t="str">
-        <v/>
-      </c>
-      <c r="R466" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S466" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="str">
-        <v>T260902-00024</v>
-      </c>
-      <c r="B467" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C467" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D467" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E467" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F467" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="G467">
-        <v>1</v>
-      </c>
-      <c r="H467" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="I467" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="J467" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K467" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L467">
-        <v>1</v>
-      </c>
-      <c r="M467" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N467" t="str">
-        <v>2026-09-02 19:21:17</v>
-      </c>
-      <c r="O467" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P467" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q467" t="str">
-        <v/>
-      </c>
-      <c r="R467" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S467" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="str">
-        <v>T260902-00023</v>
-      </c>
-      <c r="B468" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C468" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D468" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E468" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F468" t="str">
-        <v>원주FDC(신규)</v>
-      </c>
-      <c r="G468">
-        <v>1</v>
-      </c>
-      <c r="H468" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="I468" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="J468" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K468" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L468">
-        <v>1</v>
-      </c>
-      <c r="M468" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N468" t="str">
-        <v>2026-09-02 19:20:40</v>
-      </c>
-      <c r="O468" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P468" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q468" t="str">
-        <v/>
-      </c>
-      <c r="R468" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S468" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="str">
-        <v>T260902-00022</v>
-      </c>
-      <c r="B469" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C469" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D469" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E469" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F469" t="str">
-        <v>진주FDC,창원FDC</v>
-      </c>
-      <c r="G469">
-        <v>2</v>
-      </c>
-      <c r="H469" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="I469" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="J469" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K469" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L469">
-        <v>1</v>
-      </c>
-      <c r="M469" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N469" t="str">
-        <v>2026-09-02 19:20:16</v>
-      </c>
-      <c r="O469" s="1">
-        <v>730000</v>
-      </c>
-      <c r="P469" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q469" t="str">
-        <v/>
-      </c>
-      <c r="R469" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S469" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="str">
-        <v>T260902-00021</v>
-      </c>
-      <c r="B470" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C470" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D470" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E470" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F470" t="str">
-        <v/>
-      </c>
-      <c r="G470">
-        <v>0</v>
-      </c>
-      <c r="H470" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="I470" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="J470" t="str">
-        <v>2026-09-02 21:00</v>
-      </c>
-      <c r="K470" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L470">
-        <v>1</v>
-      </c>
-      <c r="M470" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N470" t="str">
-        <v>2026-09-02 19:19:46</v>
-      </c>
-      <c r="O470" s="1">
-        <v>250000</v>
-      </c>
-      <c r="P470" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q470" t="str">
-        <v/>
-      </c>
-      <c r="R470" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S470" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="str">
-        <v>T260902-00020</v>
-      </c>
-      <c r="B471" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C471" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D471" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E471" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F471" t="str">
-        <v/>
-      </c>
-      <c r="G471">
-        <v>0</v>
-      </c>
-      <c r="H471" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="I471" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="J471" t="str">
-        <v>2026-09-02 21:00</v>
-      </c>
-      <c r="K471" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L471">
-        <v>1</v>
-      </c>
-      <c r="M471" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N471" t="str">
-        <v>2026-09-02 19:19:30</v>
-      </c>
-      <c r="O471" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P471" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q471" t="str">
-        <v/>
-      </c>
-      <c r="R471" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S471" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="str">
-        <v>T260902-00019</v>
-      </c>
-      <c r="B472" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C472" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D472" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E472" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F472" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="G472">
-        <v>1</v>
-      </c>
-      <c r="H472" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="I472" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="J472" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K472" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L472">
-        <v>1</v>
-      </c>
-      <c r="M472" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N472" t="str">
-        <v>2026-09-02 19:19:13</v>
-      </c>
-      <c r="O472" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P472" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q472" t="str">
-        <v/>
-      </c>
-      <c r="R472" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S472" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="str">
-        <v>T260902-00018</v>
-      </c>
-      <c r="B473" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C473" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D473" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E473" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F473" t="str">
-        <v/>
-      </c>
-      <c r="G473">
-        <v>0</v>
-      </c>
-      <c r="H473" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="I473" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="J473" t="str">
-        <v>2026-09-02 21:00</v>
-      </c>
-      <c r="K473" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L473">
-        <v>1</v>
-      </c>
-      <c r="M473" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N473" t="str">
-        <v>2026-09-02 19:18:47</v>
-      </c>
-      <c r="O473" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P473" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q473" t="str">
-        <v/>
-      </c>
-      <c r="R473" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S473" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="str">
-        <v>T260902-00017</v>
-      </c>
-      <c r="B474" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C474" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D474" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E474" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F474" t="str">
-        <v>구미FDC(신규)</v>
-      </c>
-      <c r="G474">
-        <v>1</v>
-      </c>
-      <c r="H474" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="I474" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="J474" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K474" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L474">
-        <v>1</v>
-      </c>
-      <c r="M474" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N474" t="str">
-        <v>2026-09-02 19:17:37</v>
-      </c>
-      <c r="O474" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P474" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q474" t="str">
-        <v/>
-      </c>
-      <c r="R474" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S474" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="str">
-        <v>T260902-00016</v>
-      </c>
-      <c r="B475" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C475" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D475" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E475" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F475" t="str">
-        <v>강릉ACP</v>
-      </c>
-      <c r="G475">
-        <v>1</v>
-      </c>
-      <c r="H475" t="str">
-        <v>강릉FDC</v>
-      </c>
-      <c r="I475" t="str">
-        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
-      </c>
-      <c r="J475" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K475" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L475">
-        <v>1</v>
-      </c>
-      <c r="M475" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N475" t="str">
-        <v>2026-09-02 19:16:53</v>
-      </c>
-      <c r="O475" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P475" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q475" t="str">
-        <v/>
-      </c>
-      <c r="R475" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S475" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="str">
-        <v>T260902-00015</v>
-      </c>
-      <c r="B476" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C476" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D476" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E476" t="str">
-        <v>2026-09-02 18:10</v>
-      </c>
-      <c r="F476" t="str">
-        <v/>
-      </c>
-      <c r="G476">
-        <v>0</v>
-      </c>
-      <c r="H476" t="str">
-        <v>양산 하이마트 하이얼</v>
-      </c>
-      <c r="I476" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 하이얼</v>
-      </c>
-      <c r="J476" t="str">
-        <v>2026-09-03 21:30</v>
-      </c>
-      <c r="K476" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L476">
-        <v>1</v>
-      </c>
-      <c r="M476" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N476" t="str">
-        <v>2026-09-02 17:49:53</v>
-      </c>
-      <c r="O476" s="1">
-        <v>340000</v>
-      </c>
-      <c r="P476" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q476" t="str">
-        <v>하이얼 양산 하이마트 물류</v>
-      </c>
-      <c r="R476" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S476" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="str">
-        <v>T260902-00014</v>
-      </c>
-      <c r="B477" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C477" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D477" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E477" t="str">
-        <v>2026-09-02 17:30</v>
-      </c>
-      <c r="F477" t="str">
-        <v/>
-      </c>
-      <c r="G477">
-        <v>0</v>
-      </c>
-      <c r="H477" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="I477" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="J477" t="str">
-        <v>2026-09-02 18:30</v>
-      </c>
-      <c r="K477" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L477">
-        <v>1</v>
-      </c>
-      <c r="M477" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N477" t="str">
-        <v>2026-09-02 17:27:54</v>
-      </c>
-      <c r="O477" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P477" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q477" t="str">
-        <v/>
-      </c>
-      <c r="R477" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S477" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="str">
-        <v>T260902-00013</v>
-      </c>
-      <c r="B478" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C478" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="D478" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="E478" t="str">
-        <v>2026-09-02 11:00</v>
-      </c>
-      <c r="F478" t="str">
-        <v/>
-      </c>
-      <c r="G478">
-        <v>0</v>
-      </c>
-      <c r="H478" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I478" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J478" t="str">
-        <v>2026-09-02 13:30</v>
-      </c>
-      <c r="K478" t="str">
-        <v>1톤 기타차량</v>
-      </c>
-      <c r="L478">
-        <v>1</v>
-      </c>
-      <c r="M478" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N478" t="str">
-        <v>2026-09-02 17:27:24</v>
-      </c>
-      <c r="O478" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P478" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q478" t="str">
-        <v>거래처비용청구(1대)</v>
-      </c>
-      <c r="R478" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S478" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="str">
-        <v>T260902-00012</v>
-      </c>
-      <c r="B479" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C479" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D479" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E479" t="str">
-        <v>2026-09-02 14:30</v>
-      </c>
-      <c r="F479" t="str">
-        <v/>
-      </c>
-      <c r="G479">
-        <v>0</v>
-      </c>
-      <c r="H479" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I479" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J479" t="str">
-        <v>2026-09-02 15:30</v>
-      </c>
-      <c r="K479" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L479">
-        <v>1</v>
-      </c>
-      <c r="M479" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N479" t="str">
-        <v>2026-09-02 17:26:30</v>
-      </c>
-      <c r="O479" s="1">
-        <v>70000</v>
-      </c>
-      <c r="P479" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q479" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="R479" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S479" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="str">
-        <v>T260902-00011</v>
-      </c>
-      <c r="B480" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C480" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D480" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E480" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="F480" t="str">
-        <v/>
-      </c>
-      <c r="G480">
-        <v>0</v>
-      </c>
-      <c r="H480" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I480" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J480" t="str">
-        <v>2026-09-02 13:30</v>
-      </c>
-      <c r="K480" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L480">
-        <v>1</v>
-      </c>
-      <c r="M480" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N480" t="str">
-        <v>2026-09-02 17:25:43</v>
-      </c>
-      <c r="O480" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P480" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q480" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="R480" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S480" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="str">
-        <v>T260902-00010</v>
-      </c>
-      <c r="B481" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C481" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D481" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E481" t="str">
-        <v>2026-09-02 17:10</v>
-      </c>
-      <c r="F481" t="str">
-        <v/>
-      </c>
-      <c r="G481">
-        <v>0</v>
-      </c>
-      <c r="H481" t="str">
-        <v>마산 하이마트 하이얼</v>
-      </c>
-      <c r="I481" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 하이얼</v>
-      </c>
-      <c r="J481" t="str">
-        <v>2026-09-03 09:30</v>
-      </c>
-      <c r="K481" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L481">
-        <v>1</v>
-      </c>
-      <c r="M481" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N481" t="str">
-        <v>2026-09-02 16:04:12</v>
-      </c>
-      <c r="O481" s="1">
-        <v>340000</v>
-      </c>
-      <c r="P481" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q481" t="str">
-        <v>하이얼  마산 하이마트 물류</v>
-      </c>
-      <c r="R481" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S481" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="str">
-        <v>T260902-00009</v>
-      </c>
-      <c r="B482" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C482" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D482" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E482" t="str">
-        <v>2026-09-02 16:30</v>
-      </c>
-      <c r="F482" t="str">
-        <v/>
-      </c>
-      <c r="G482">
-        <v>0</v>
-      </c>
-      <c r="H482" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I482" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="J482" t="str">
-        <v>2026-09-02 17:30</v>
-      </c>
-      <c r="K482" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L482">
-        <v>1</v>
-      </c>
-      <c r="M482" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N482" t="str">
-        <v>2026-09-02 16:01:28</v>
-      </c>
-      <c r="O482" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P482" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q482" t="str">
-        <v/>
-      </c>
-      <c r="R482" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S482" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="str">
-        <v>T260902-00008</v>
-      </c>
-      <c r="B483" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C483" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D483" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E483" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="F483" t="str">
-        <v/>
-      </c>
-      <c r="G483">
-        <v>0</v>
-      </c>
-      <c r="H483" t="str">
-        <v>이천 하이마트 하이얼</v>
-      </c>
-      <c r="I483" t="str">
-        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 하이얼</v>
-      </c>
-      <c r="J483" t="str">
-        <v>2026-09-02 15:00</v>
-      </c>
-      <c r="K483" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L483">
-        <v>1</v>
-      </c>
-      <c r="M483" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N483" t="str">
-        <v>2026-09-02 10:54:59</v>
-      </c>
-      <c r="O483" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P483" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q483" t="str">
-        <v>하이얼 이천 하이마트 물류</v>
-      </c>
-      <c r="R483" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S483" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="str">
-        <v>T260902-00007</v>
-      </c>
-      <c r="B484" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C484" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D484" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E484" t="str">
-        <v>2026-09-02 09:40</v>
-      </c>
-      <c r="F484" t="str">
-        <v/>
-      </c>
-      <c r="G484">
-        <v>0</v>
-      </c>
-      <c r="H484" t="str">
-        <v>화성 하이마트 하이얼</v>
-      </c>
-      <c r="I484" t="str">
-        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 하이얼</v>
-      </c>
-      <c r="J484" t="str">
-        <v>2026-09-02 03:00</v>
-      </c>
-      <c r="K484" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L484">
-        <v>1</v>
-      </c>
-      <c r="M484" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N484" t="str">
-        <v>2026-09-02 10:50:30</v>
-      </c>
-      <c r="O484" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P484" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q484" t="str">
-        <v>히이얼 화성 하이마트 물류</v>
-      </c>
-      <c r="R484" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S484" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="str">
-        <v>T260902-00006</v>
-      </c>
-      <c r="B485" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C485" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D485" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E485" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F485" t="str">
-        <v/>
-      </c>
-      <c r="G485">
-        <v>0</v>
-      </c>
-      <c r="H485" t="str">
-        <v>인천 하이마트 하이얼</v>
-      </c>
-      <c r="I485" t="str">
-        <v>인천 중구 서해대로94번길 132 인천 하이마트 하이얼</v>
-      </c>
-      <c r="J485" t="str">
-        <v>2026-09-02 03:00</v>
-      </c>
-      <c r="K485" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L485">
-        <v>1</v>
-      </c>
-      <c r="M485" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N485" t="str">
-        <v>2026-09-02 10:36:26</v>
-      </c>
-      <c r="O485" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P485" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q485" t="str">
-        <v>하이얼 인천 하이마트 물류</v>
-      </c>
-      <c r="R485" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S485" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="str">
-        <v>T260902-00005</v>
-      </c>
-      <c r="B486" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C486" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D486" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E486" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F486" t="str">
-        <v/>
-      </c>
-      <c r="G486">
-        <v>0</v>
-      </c>
-      <c r="H486" t="str">
-        <v>아임테크날러지 창고</v>
-      </c>
-      <c r="I486" t="str">
-        <v>경기 김포시 통진읍 월하로479번길 32-42 가동, 나동</v>
-      </c>
-      <c r="J486" t="str">
-        <v>2026-09-02 11:00</v>
-      </c>
-      <c r="K486" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L486">
-        <v>1</v>
-      </c>
-      <c r="M486" t="str">
-        <v>차순권</v>
-      </c>
-      <c r="N486" t="str">
-        <v>2026-09-02 09:52:58</v>
-      </c>
-      <c r="O486" s="1">
-        <v>230000</v>
-      </c>
-      <c r="P486" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q486" t="str">
-        <v>아임테크 날러지 회수2, 가용 1파렛트 출하</v>
-      </c>
-      <c r="R486" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S486" t="str">
-        <v>아임테크날러지</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="str">
-        <v>T260902-00004</v>
-      </c>
-      <c r="B487" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C487" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D487" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E487" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F487" t="str">
-        <v/>
-      </c>
-      <c r="G487">
-        <v>0</v>
-      </c>
-      <c r="H487" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I487" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J487" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="K487" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L487">
-        <v>1</v>
-      </c>
-      <c r="M487" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N487" t="str">
-        <v>2026-09-02 09:49:55</v>
-      </c>
-      <c r="O487" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P487" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q487" t="str">
-        <v>중산물산 회수품</v>
-      </c>
-      <c r="R487" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S487" t="str">
-        <v>중산물산</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="str">
-        <v>T260902-00003</v>
-      </c>
-      <c r="B488" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C488" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D488" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E488" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F488" t="str">
-        <v/>
-      </c>
-      <c r="G488">
-        <v>0</v>
-      </c>
-      <c r="H488" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I488" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J488" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="K488" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L488">
-        <v>1</v>
-      </c>
-      <c r="M488" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N488" t="str">
-        <v>2026-09-02 09:37:44</v>
-      </c>
-      <c r="O488" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P488" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q488" t="str">
-        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
-      </c>
-      <c r="R488" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S488" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="str">
-        <v>T260902-00002</v>
-      </c>
-      <c r="B489" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C489" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D489" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E489" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F489" t="str">
-        <v/>
-      </c>
-      <c r="G489">
-        <v>0</v>
-      </c>
-      <c r="H489" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I489" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J489" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="K489" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L489">
-        <v>1</v>
-      </c>
-      <c r="M489" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N489" t="str">
-        <v>2026-09-02 09:37:02</v>
-      </c>
-      <c r="O489" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P489" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q489" t="str">
-        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
-      </c>
-      <c r="R489" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S489" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="str">
-        <v>T260902-00001</v>
-      </c>
-      <c r="B490" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C490" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D490" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E490" t="str">
-        <v>2026-09-02 09:50</v>
-      </c>
-      <c r="F490" t="str">
-        <v/>
-      </c>
-      <c r="G490">
-        <v>0</v>
-      </c>
-      <c r="H490" t="str">
-        <v>아임테크</v>
-      </c>
-      <c r="I490" t="str">
-        <v>경기 김포시 통진읍 귀전리 537-4 아임테크</v>
-      </c>
-      <c r="J490" t="str">
-        <v>2026-09-02 11:00</v>
-      </c>
-      <c r="K490" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L490">
-        <v>1</v>
-      </c>
-      <c r="M490" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N490" t="str">
-        <v>2026-09-02 09:33:24</v>
-      </c>
-      <c r="O490" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P490" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q490" t="str">
-        <v>아임테크날러지 전량 출하</v>
-      </c>
-      <c r="R490" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S490" t="str">
-        <v>아임테크날러지</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="str">
-        <v>T260901-00019</v>
-      </c>
-      <c r="B491" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C491" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D491" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E491" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F491" t="str">
-        <v>시흥ACP,인천ACP</v>
-      </c>
-      <c r="G491">
-        <v>2</v>
-      </c>
-      <c r="H491" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="I491" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="J491" t="str">
-        <v>2026-09-02 07:00</v>
-      </c>
-      <c r="K491" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L491">
-        <v>1</v>
-      </c>
-      <c r="M491" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N491" t="str">
-        <v>2026-09-01 19:27:06</v>
-      </c>
-      <c r="O491" s="1">
-        <v>230000</v>
-      </c>
-      <c r="P491" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q491" t="str">
-        <v/>
-      </c>
-      <c r="R491" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S491" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="str">
-        <v>T260901-00018</v>
-      </c>
-      <c r="B492" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C492" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D492" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E492" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F492" t="str">
-        <v>대전중구ACP,대전대덕ACP</v>
-      </c>
-      <c r="G492">
-        <v>2</v>
-      </c>
-      <c r="H492" t="str">
-        <v>군산ACP</v>
-      </c>
-      <c r="I492" t="str">
-        <v>전북특별자치도 군산시 구암3.1로 60 군산ACP</v>
-      </c>
-      <c r="J492" t="str">
-        <v>2026-09-02 07:00</v>
-      </c>
-      <c r="K492" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L492">
-        <v>1</v>
-      </c>
-      <c r="M492" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N492" t="str">
-        <v>2026-09-01 19:26:35</v>
-      </c>
-      <c r="O492" s="1">
-        <v>300000</v>
-      </c>
-      <c r="P492" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q492" t="str">
-        <v/>
-      </c>
-      <c r="R492" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S492" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="str">
-        <v>T260901-00017</v>
-      </c>
-      <c r="B493" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C493" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D493" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E493" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F493" t="str">
-        <v>안성ACP,화성ACP,용인ACP</v>
-      </c>
-      <c r="G493">
-        <v>3</v>
-      </c>
-      <c r="H493" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="I493" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="J493" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K493" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L493">
-        <v>1</v>
-      </c>
-      <c r="M493" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N493" t="str">
-        <v>2026-09-01 19:25:58</v>
-      </c>
-      <c r="O493" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P493" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q493" t="str">
-        <v/>
-      </c>
-      <c r="R493" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S493" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="str">
-        <v>T260901-00016</v>
-      </c>
-      <c r="B494" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C494" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D494" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E494" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F494" t="str">
-        <v/>
-      </c>
-      <c r="G494">
-        <v>0</v>
-      </c>
-      <c r="H494" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="I494" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="J494" t="str">
-        <v>2026-09-01 21:00</v>
-      </c>
-      <c r="K494" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L494">
-        <v>1</v>
-      </c>
-      <c r="M494" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N494" t="str">
-        <v>2026-09-01 19:25:13</v>
-      </c>
-      <c r="O494" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P494" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q494" t="str">
-        <v/>
-      </c>
-      <c r="R494" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S494" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="str">
-        <v>T260901-00015</v>
-      </c>
-      <c r="B495" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C495" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D495" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E495" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F495" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="G495">
-        <v>1</v>
-      </c>
-      <c r="H495" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="I495" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="J495" t="str">
-        <v>2026-09-01 22:00</v>
-      </c>
-      <c r="K495" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L495">
-        <v>1</v>
-      </c>
-      <c r="M495" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N495" t="str">
-        <v>2026-09-01 19:24:58</v>
-      </c>
-      <c r="O495" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P495" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q495" t="str">
-        <v/>
-      </c>
-      <c r="R495" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S495" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="str">
-        <v>T260901-00014</v>
-      </c>
-      <c r="B496" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C496" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D496" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E496" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F496" t="str">
-        <v/>
-      </c>
-      <c r="G496">
-        <v>0</v>
-      </c>
-      <c r="H496" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="I496" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="J496" t="str">
-        <v>2026-09-01 21:00</v>
-      </c>
-      <c r="K496" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L496">
-        <v>1</v>
-      </c>
-      <c r="M496" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N496" t="str">
-        <v>2026-09-01 19:24:38</v>
-      </c>
-      <c r="O496" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P496" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q496" t="str">
-        <v/>
-      </c>
-      <c r="R496" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S496" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="str">
-        <v>T260901-00013</v>
-      </c>
-      <c r="B497" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C497" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D497" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E497" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F497" t="str">
-        <v>원주FDC(신규)</v>
-      </c>
-      <c r="G497">
-        <v>1</v>
-      </c>
-      <c r="H497" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="I497" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="J497" t="str">
-        <v>2026-09-01 22:00</v>
-      </c>
-      <c r="K497" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L497">
-        <v>1</v>
-      </c>
-      <c r="M497" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N497" t="str">
-        <v>2026-09-01 19:24:22</v>
-      </c>
-      <c r="O497" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P497" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q497" t="str">
-        <v/>
-      </c>
-      <c r="R497" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S497" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="str">
-        <v>T260901-00012</v>
-      </c>
-      <c r="B498" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C498" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D498" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E498" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F498" t="str">
-        <v>진주FDC,창원FDC</v>
-      </c>
-      <c r="G498">
-        <v>2</v>
-      </c>
-      <c r="H498" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="I498" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="J498" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K498" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L498">
-        <v>1</v>
-      </c>
-      <c r="M498" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N498" t="str">
-        <v>2026-09-01 19:23:57</v>
-      </c>
-      <c r="O498" s="1">
-        <v>730000</v>
-      </c>
-      <c r="P498" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q498" t="str">
-        <v/>
-      </c>
-      <c r="R498" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S498" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="str">
-        <v>T260901-00011</v>
-      </c>
-      <c r="B499" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C499" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D499" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E499" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F499" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="G499">
-        <v>1</v>
-      </c>
-      <c r="H499" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="I499" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="J499" t="str">
-        <v>2026-09-01 22:00</v>
-      </c>
-      <c r="K499" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L499">
-        <v>1</v>
-      </c>
-      <c r="M499" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N499" t="str">
-        <v>2026-09-01 19:23:32</v>
-      </c>
-      <c r="O499" s="1">
-        <v>370000</v>
-      </c>
-      <c r="P499" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q499" t="str">
-        <v/>
-      </c>
-      <c r="R499" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S499" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="str">
-        <v>T260901-00010</v>
-      </c>
-      <c r="B500" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C500" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D500" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E500" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F500" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="G500">
-        <v>1</v>
-      </c>
-      <c r="H500" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="I500" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="J500" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K500" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L500">
-        <v>1</v>
-      </c>
-      <c r="M500" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N500" t="str">
-        <v>2026-09-01 19:23:13</v>
-      </c>
-      <c r="O500" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P500" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q500" t="str">
-        <v/>
-      </c>
-      <c r="R500" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S500" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="str">
-        <v>T260901-00009</v>
-      </c>
-      <c r="B501" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C501" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D501" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E501" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F501" t="str">
-        <v/>
-      </c>
-      <c r="G501">
-        <v>0</v>
-      </c>
-      <c r="H501" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="I501" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="J501" t="str">
-        <v>2026-09-01 21:00</v>
-      </c>
-      <c r="K501" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L501">
-        <v>1</v>
-      </c>
-      <c r="M501" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N501" t="str">
-        <v>2026-09-01 19:22:26</v>
-      </c>
-      <c r="O501" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P501" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q501" t="str">
-        <v/>
-      </c>
-      <c r="R501" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S501" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="str">
-        <v>T260901-00008</v>
-      </c>
-      <c r="B502" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C502" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D502" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E502" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F502" t="str">
-        <v>구미FDC(신규)</v>
-      </c>
-      <c r="G502">
-        <v>1</v>
-      </c>
-      <c r="H502" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="I502" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="J502" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K502" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L502">
-        <v>1</v>
-      </c>
-      <c r="M502" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N502" t="str">
-        <v>2026-09-01 19:22:10</v>
-      </c>
-      <c r="O502" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P502" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q502" t="str">
-        <v/>
-      </c>
-      <c r="R502" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S502" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="str">
-        <v>T260901-00007</v>
-      </c>
-      <c r="B503" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C503" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D503" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E503" t="str">
-        <v>2026-09-01 17:20</v>
-      </c>
-      <c r="F503" t="str">
-        <v/>
-      </c>
-      <c r="G503">
-        <v>0</v>
-      </c>
-      <c r="H503" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="I503" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="J503" t="str">
-        <v>2026-09-01 18:20</v>
-      </c>
-      <c r="K503" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L503">
-        <v>1</v>
-      </c>
-      <c r="M503" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N503" t="str">
-        <v>2026-09-01 19:20:06</v>
-      </c>
-      <c r="O503" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P503" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q503" t="str">
-        <v/>
-      </c>
-      <c r="R503" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S503" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="str">
-        <v>T260901-00006</v>
-      </c>
-      <c r="B504" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C504" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="D504" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="E504" t="str">
-        <v>2026-09-01 11:20</v>
-      </c>
-      <c r="F504" t="str">
-        <v/>
-      </c>
-      <c r="G504">
-        <v>0</v>
-      </c>
-      <c r="H504" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I504" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J504" t="str">
-        <v>2026-09-01 13:20</v>
-      </c>
-      <c r="K504" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L504">
-        <v>1</v>
-      </c>
-      <c r="M504" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N504" t="str">
-        <v>2026-09-01 19:19:31</v>
-      </c>
-      <c r="O504" s="1">
-        <v>120000</v>
-      </c>
-      <c r="P504" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q504" t="str">
-        <v>거래처비용청구(2대)</v>
-      </c>
-      <c r="R504" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S504" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="str">
-        <v>T260901-00005</v>
-      </c>
-      <c r="B505" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C505" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D505" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E505" t="str">
-        <v>2026-09-01 14:20</v>
-      </c>
-      <c r="F505" t="str">
-        <v/>
-      </c>
-      <c r="G505">
-        <v>0</v>
-      </c>
-      <c r="H505" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I505" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J505" t="str">
-        <v>2026-09-01 15:20</v>
-      </c>
-      <c r="K505" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L505">
-        <v>1</v>
-      </c>
-      <c r="M505" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N505" t="str">
-        <v>2026-09-01 19:18:39</v>
-      </c>
-      <c r="O505" s="1">
-        <v>70000</v>
-      </c>
-      <c r="P505" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q505" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="R505" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S505" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="str">
-        <v>T260901-00004</v>
-      </c>
-      <c r="B506" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C506" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D506" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E506" t="str">
-        <v>2026-09-01 15:50</v>
-      </c>
-      <c r="F506" t="str">
-        <v/>
-      </c>
-      <c r="G506">
-        <v>0</v>
-      </c>
-      <c r="H506" t="str">
-        <v>공주 하이마트 하이얼</v>
-      </c>
-      <c r="I506" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="J506" t="str">
-        <v>2026-09-02 15:00</v>
-      </c>
-      <c r="K506" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L506">
-        <v>1</v>
-      </c>
-      <c r="M506" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N506" t="str">
-        <v>2026-09-01 15:50:14</v>
-      </c>
-      <c r="O506" s="1">
-        <v>220000</v>
-      </c>
-      <c r="P506" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q506" t="str">
-        <v>하이얼 공주 하이마트 물류</v>
-      </c>
-      <c r="R506" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S506" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="str">
-        <v>T260901-00003</v>
-      </c>
-      <c r="B507" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C507" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D507" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E507" t="str">
-        <v>2026-09-01 15:35</v>
-      </c>
-      <c r="F507" t="str">
-        <v/>
-      </c>
-      <c r="G507">
-        <v>0</v>
-      </c>
-      <c r="H507" t="str">
-        <v>대구 하이마트 하이얼</v>
-      </c>
-      <c r="I507" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="J507" t="str">
-        <v>2026-09-02 15:00</v>
-      </c>
-      <c r="K507" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L507">
-        <v>1</v>
-      </c>
-      <c r="M507" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N507" t="str">
-        <v>2026-09-01 13:37:23</v>
-      </c>
-      <c r="O507" s="1">
-        <v>300000</v>
-      </c>
-      <c r="P507" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q507" t="str">
-        <v>하이얼 대구 하이마트 물류</v>
-      </c>
-      <c r="R507" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S507" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="str">
-        <v>T260901-00002</v>
-      </c>
-      <c r="B508" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C508" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="D508" t="str">
-        <v>인천 서구 오류동 1653-2 인천FDC</v>
-      </c>
-      <c r="E508" t="str">
-        <v>2026-09-02 08:00</v>
-      </c>
-      <c r="F508" t="str">
-        <v/>
-      </c>
-      <c r="G508">
-        <v>0</v>
-      </c>
-      <c r="H508" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="I508" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="J508" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="K508" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L508">
-        <v>1</v>
-      </c>
-      <c r="M508" t="str">
-        <v>차순권</v>
-      </c>
-      <c r="N508" t="str">
-        <v>2026-09-01 13:22:36</v>
-      </c>
-      <c r="O508" s="1">
-        <v>50000</v>
-      </c>
-      <c r="P508" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q508" t="str">
-        <v>접수번호 : 1565331 / 취소 건 샤오미 창고로 출하 / 인천FDC에서 직접 배송함</v>
-      </c>
-      <c r="R508" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S508" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="str">
-        <v>T260901-00001</v>
-      </c>
-      <c r="B509" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C509" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="D509" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 821 곤지암FDC</v>
-      </c>
-      <c r="E509" t="str">
-        <v>2026-09-01 08:00</v>
-      </c>
-      <c r="F509" t="str">
-        <v/>
-      </c>
-      <c r="G509">
-        <v>0</v>
-      </c>
-      <c r="H509" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I509" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J509" t="str">
-        <v>2026-09-01 10:00</v>
-      </c>
-      <c r="K509" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L509">
-        <v>1</v>
-      </c>
-      <c r="M509" t="str">
-        <v>차순권</v>
-      </c>
-      <c r="N509" t="str">
-        <v>2026-09-01 09:03:56</v>
-      </c>
-      <c r="O509" s="1">
-        <v>80000</v>
-      </c>
-      <c r="P509" s="1">
-        <v>5000</v>
-      </c>
-      <c r="Q509" t="str">
-        <v>하이얼 가용재고 10개 이동</v>
-      </c>
-      <c r="R509" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S509" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S509"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S431"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S431"/>
+  <dimension ref="A1:S509"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -25808,9 +25808,4611 @@
         <v>일코전자</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>T260903-00029</v>
+      </c>
+      <c r="B432" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C432" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D432" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E432" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F432" t="str">
+        <v>시흥ACP,인천ACP</v>
+      </c>
+      <c r="G432">
+        <v>2</v>
+      </c>
+      <c r="H432" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="I432" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="J432" t="str">
+        <v>2026-09-04 08:00</v>
+      </c>
+      <c r="K432" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L432">
+        <v>1</v>
+      </c>
+      <c r="M432" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N432" t="str">
+        <v>2026-09-03 18:24:00</v>
+      </c>
+      <c r="O432" s="1">
+        <v>230000</v>
+      </c>
+      <c r="P432" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q432" t="str">
+        <v/>
+      </c>
+      <c r="R432" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S432" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>T260903-00028</v>
+      </c>
+      <c r="B433" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C433" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D433" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E433" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F433" t="str">
+        <v>대전중구ACP,군산ACP</v>
+      </c>
+      <c r="G433">
+        <v>2</v>
+      </c>
+      <c r="H433" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="I433" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="J433" t="str">
+        <v>2026-09-04 07:00</v>
+      </c>
+      <c r="K433" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L433">
+        <v>1</v>
+      </c>
+      <c r="M433" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N433" t="str">
+        <v>2026-09-03 18:23:24</v>
+      </c>
+      <c r="O433" s="1">
+        <v>300000</v>
+      </c>
+      <c r="P433" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q433" t="str">
+        <v/>
+      </c>
+      <c r="R433" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S433" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>T260903-00027</v>
+      </c>
+      <c r="B434" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C434" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D434" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E434" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F434" t="str">
+        <v>안성ACP,용인ACP,화성ACP</v>
+      </c>
+      <c r="G434">
+        <v>3</v>
+      </c>
+      <c r="H434" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="I434" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="J434" t="str">
+        <v>2026-09-03 23:00</v>
+      </c>
+      <c r="K434" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L434">
+        <v>1</v>
+      </c>
+      <c r="M434" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N434" t="str">
+        <v>2026-09-03 18:22:50</v>
+      </c>
+      <c r="O434" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P434" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q434" t="str">
+        <v/>
+      </c>
+      <c r="R434" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S434" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>T260903-00026</v>
+      </c>
+      <c r="B435" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C435" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D435" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E435" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F435" t="str">
+        <v/>
+      </c>
+      <c r="G435">
+        <v>0</v>
+      </c>
+      <c r="H435" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="I435" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="J435" t="str">
+        <v>2026-09-03 21:00</v>
+      </c>
+      <c r="K435" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L435">
+        <v>1</v>
+      </c>
+      <c r="M435" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N435" t="str">
+        <v>2026-09-03 18:22:08</v>
+      </c>
+      <c r="O435" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P435" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q435" t="str">
+        <v/>
+      </c>
+      <c r="R435" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S435" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>T260903-00025</v>
+      </c>
+      <c r="B436" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C436" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D436" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E436" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F436" t="str">
+        <v/>
+      </c>
+      <c r="G436">
+        <v>0</v>
+      </c>
+      <c r="H436" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="I436" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="J436" t="str">
+        <v>2026-09-03 22:00</v>
+      </c>
+      <c r="K436" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L436">
+        <v>1</v>
+      </c>
+      <c r="M436" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N436" t="str">
+        <v>2026-09-03 18:21:51</v>
+      </c>
+      <c r="O436" s="1">
+        <v>230000</v>
+      </c>
+      <c r="P436" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q436" t="str">
+        <v/>
+      </c>
+      <c r="R436" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S436" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>T260903-00024</v>
+      </c>
+      <c r="B437" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C437" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D437" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E437" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F437" t="str">
+        <v/>
+      </c>
+      <c r="G437">
+        <v>0</v>
+      </c>
+      <c r="H437" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="I437" t="str">
+        <v>인천 검단구 오류동 1653-2 인천FDC</v>
+      </c>
+      <c r="J437" t="str">
+        <v>2026-09-03 21:00</v>
+      </c>
+      <c r="K437" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L437">
+        <v>1</v>
+      </c>
+      <c r="M437" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N437" t="str">
+        <v>2026-09-03 18:21:35</v>
+      </c>
+      <c r="O437" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P437" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q437" t="str">
+        <v/>
+      </c>
+      <c r="R437" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S437" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>T260903-00023</v>
+      </c>
+      <c r="B438" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C438" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D438" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E438" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F438" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="G438">
+        <v>1</v>
+      </c>
+      <c r="H438" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="I438" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="J438" t="str">
+        <v>2026-09-03 22:00</v>
+      </c>
+      <c r="K438" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L438">
+        <v>1</v>
+      </c>
+      <c r="M438" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N438" t="str">
+        <v>2026-09-03 18:21:18</v>
+      </c>
+      <c r="O438" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P438" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q438" t="str">
+        <v/>
+      </c>
+      <c r="R438" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S438" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>T260903-00022</v>
+      </c>
+      <c r="B439" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C439" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D439" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E439" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F439" t="str">
+        <v>원주FDC(신규)</v>
+      </c>
+      <c r="G439">
+        <v>1</v>
+      </c>
+      <c r="H439" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="I439" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="J439" t="str">
+        <v>2026-09-03 22:00</v>
+      </c>
+      <c r="K439" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L439">
+        <v>1</v>
+      </c>
+      <c r="M439" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N439" t="str">
+        <v>2026-09-03 18:20:56</v>
+      </c>
+      <c r="O439" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P439" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q439" t="str">
+        <v/>
+      </c>
+      <c r="R439" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S439" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>T260903-00021</v>
+      </c>
+      <c r="B440" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C440" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D440" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E440" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F440" t="str">
+        <v>진주FDC,창원FDC</v>
+      </c>
+      <c r="G440">
+        <v>2</v>
+      </c>
+      <c r="H440" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="I440" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="J440" t="str">
+        <v>2026-09-03 23:00</v>
+      </c>
+      <c r="K440" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L440">
+        <v>1</v>
+      </c>
+      <c r="M440" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N440" t="str">
+        <v>2026-09-03 18:20:35</v>
+      </c>
+      <c r="O440" s="1">
+        <v>730000</v>
+      </c>
+      <c r="P440" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q440" t="str">
+        <v/>
+      </c>
+      <c r="R440" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S440" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>T260903-00020</v>
+      </c>
+      <c r="B441" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C441" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D441" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E441" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F441" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="G441">
+        <v>1</v>
+      </c>
+      <c r="H441" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="I441" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="J441" t="str">
+        <v>2026-09-03 22:00</v>
+      </c>
+      <c r="K441" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L441">
+        <v>1</v>
+      </c>
+      <c r="M441" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N441" t="str">
+        <v>2026-09-03 18:20:07</v>
+      </c>
+      <c r="O441" s="1">
+        <v>370000</v>
+      </c>
+      <c r="P441" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q441" t="str">
+        <v/>
+      </c>
+      <c r="R441" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S441" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>T260903-00019</v>
+      </c>
+      <c r="B442" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C442" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D442" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E442" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F442" t="str">
+        <v/>
+      </c>
+      <c r="G442">
+        <v>0</v>
+      </c>
+      <c r="H442" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="I442" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="J442" t="str">
+        <v>2026-09-03 23:00</v>
+      </c>
+      <c r="K442" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L442">
+        <v>1</v>
+      </c>
+      <c r="M442" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N442" t="str">
+        <v>2026-09-03 18:19:48</v>
+      </c>
+      <c r="O442" s="1">
+        <v>420000</v>
+      </c>
+      <c r="P442" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q442" t="str">
+        <v/>
+      </c>
+      <c r="R442" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S442" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>T260903-00018</v>
+      </c>
+      <c r="B443" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C443" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D443" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E443" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F443" t="str">
+        <v/>
+      </c>
+      <c r="G443">
+        <v>0</v>
+      </c>
+      <c r="H443" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="I443" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="J443" t="str">
+        <v>2026-09-03 21:00</v>
+      </c>
+      <c r="K443" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L443">
+        <v>1</v>
+      </c>
+      <c r="M443" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N443" t="str">
+        <v>2026-09-03 18:19:30</v>
+      </c>
+      <c r="O443" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P443" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q443" t="str">
+        <v/>
+      </c>
+      <c r="R443" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S443" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>T260903-00017</v>
+      </c>
+      <c r="B444" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C444" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D444" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E444" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F444" t="str">
+        <v>구미FDC(신규)</v>
+      </c>
+      <c r="G444">
+        <v>1</v>
+      </c>
+      <c r="H444" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="I444" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="J444" t="str">
+        <v>2026-09-03 23:00</v>
+      </c>
+      <c r="K444" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L444">
+        <v>1</v>
+      </c>
+      <c r="M444" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N444" t="str">
+        <v>2026-09-03 18:19:12</v>
+      </c>
+      <c r="O444" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P444" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q444" t="str">
+        <v/>
+      </c>
+      <c r="R444" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S444" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
+        <v>T260903-00016</v>
+      </c>
+      <c r="B445" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C445" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D445" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E445" t="str">
+        <v>2026-09-03 18:00</v>
+      </c>
+      <c r="F445" t="str">
+        <v/>
+      </c>
+      <c r="G445">
+        <v>0</v>
+      </c>
+      <c r="H445" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="I445" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="J445" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="K445" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L445">
+        <v>1</v>
+      </c>
+      <c r="M445" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N445" t="str">
+        <v>2026-09-03 17:43:12</v>
+      </c>
+      <c r="O445" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P445" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q445" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="R445" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S445" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>T260903-00015</v>
+      </c>
+      <c r="B446" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C446" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D446" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E446" t="str">
+        <v>2026-09-03 17:30</v>
+      </c>
+      <c r="F446" t="str">
+        <v/>
+      </c>
+      <c r="G446">
+        <v>0</v>
+      </c>
+      <c r="H446" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="I446" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="J446" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="K446" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L446">
+        <v>1</v>
+      </c>
+      <c r="M446" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N446" t="str">
+        <v>2026-09-03 17:10:21</v>
+      </c>
+      <c r="O446" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P446" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q446" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="R446" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S446" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>T260903-00014</v>
+      </c>
+      <c r="B447" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C447" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D447" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E447" t="str">
+        <v>2026-09-03 17:30</v>
+      </c>
+      <c r="F447" t="str">
+        <v/>
+      </c>
+      <c r="G447">
+        <v>0</v>
+      </c>
+      <c r="H447" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="I447" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="J447" t="str">
+        <v>2026-09-04 21:00</v>
+      </c>
+      <c r="K447" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L447">
+        <v>1</v>
+      </c>
+      <c r="M447" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N447" t="str">
+        <v>2026-09-03 17:09:57</v>
+      </c>
+      <c r="O447" s="1">
+        <v>220000</v>
+      </c>
+      <c r="P447" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q447" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="R447" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S447" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>T260903-00013</v>
+      </c>
+      <c r="B448" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C448" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="D448" t="str">
+        <v>충남 아산시 음봉면 월랑리 440 천안FDC</v>
+      </c>
+      <c r="E448" t="str">
+        <v>2026-09-03 21:30</v>
+      </c>
+      <c r="F448" t="str">
+        <v/>
+      </c>
+      <c r="G448">
+        <v>0</v>
+      </c>
+      <c r="H448" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="I448" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="J448" t="str">
+        <v>2026-09-03 22:30</v>
+      </c>
+      <c r="K448" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L448">
+        <v>1</v>
+      </c>
+      <c r="M448" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N448" t="str">
+        <v>2026-09-03 16:23:31</v>
+      </c>
+      <c r="O448" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P448" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q448" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="R448" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S448" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>T260903-00012</v>
+      </c>
+      <c r="B449" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C449" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D449" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E449" t="str">
+        <v>2026-09-03 16:30</v>
+      </c>
+      <c r="F449" t="str">
+        <v/>
+      </c>
+      <c r="G449">
+        <v>0</v>
+      </c>
+      <c r="H449" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I449" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="J449" t="str">
+        <v>2026-09-03 17:30</v>
+      </c>
+      <c r="K449" t="str">
+        <v>1톤 카고/윙</v>
+      </c>
+      <c r="L449">
+        <v>1</v>
+      </c>
+      <c r="M449" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N449" t="str">
+        <v>2026-09-03 15:51:43</v>
+      </c>
+      <c r="O449" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P449" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q449" t="str">
+        <v/>
+      </c>
+      <c r="R449" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S449" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>T260903-00011</v>
+      </c>
+      <c r="B450" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C450" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D450" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E450" t="str">
+        <v>2026-09-03 17:30</v>
+      </c>
+      <c r="F450" t="str">
+        <v/>
+      </c>
+      <c r="G450">
+        <v>0</v>
+      </c>
+      <c r="H450" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="I450" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="J450" t="str">
+        <v>2026-09-03 18:30</v>
+      </c>
+      <c r="K450" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L450">
+        <v>1</v>
+      </c>
+      <c r="M450" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N450" t="str">
+        <v>2026-09-03 15:32:57</v>
+      </c>
+      <c r="O450" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P450" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q450" t="str">
+        <v/>
+      </c>
+      <c r="R450" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S450" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>T260903-00010</v>
+      </c>
+      <c r="B451" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C451" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="D451" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 821 곤지암FDC</v>
+      </c>
+      <c r="E451" t="str">
+        <v>2026-09-03 21:30</v>
+      </c>
+      <c r="F451" t="str">
+        <v/>
+      </c>
+      <c r="G451">
+        <v>0</v>
+      </c>
+      <c r="H451" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="I451" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="J451" t="str">
+        <v>2026-09-04 08:30</v>
+      </c>
+      <c r="K451" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L451">
+        <v>1</v>
+      </c>
+      <c r="M451" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N451" t="str">
+        <v>2026-09-03 15:32:28</v>
+      </c>
+      <c r="O451" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P451" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q451" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="R451" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S451" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>T260903-00009</v>
+      </c>
+      <c r="B452" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C452" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="D452" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5 김포FDC</v>
+      </c>
+      <c r="E452" t="str">
+        <v>2026-09-03 09:00</v>
+      </c>
+      <c r="F452" t="str">
+        <v/>
+      </c>
+      <c r="G452">
+        <v>0</v>
+      </c>
+      <c r="H452" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="I452" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="J452" t="str">
+        <v>2026-09-03 11:30</v>
+      </c>
+      <c r="K452" t="str">
+        <v>5톤 카고</v>
+      </c>
+      <c r="L452">
+        <v>1</v>
+      </c>
+      <c r="M452" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N452" t="str">
+        <v>2026-09-03 15:31:34</v>
+      </c>
+      <c r="O452" s="1">
+        <v>250000</v>
+      </c>
+      <c r="P452" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q452" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="R452" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S452" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>T260903-00008</v>
+      </c>
+      <c r="B453" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C453" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="D453" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="E453" t="str">
+        <v>2026-09-03 11:00</v>
+      </c>
+      <c r="F453" t="str">
+        <v/>
+      </c>
+      <c r="G453">
+        <v>0</v>
+      </c>
+      <c r="H453" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I453" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J453" t="str">
+        <v>2026-09-03 13:30</v>
+      </c>
+      <c r="K453" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L453">
+        <v>1</v>
+      </c>
+      <c r="M453" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N453" t="str">
+        <v>2026-09-03 15:30:52</v>
+      </c>
+      <c r="O453" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P453" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q453" t="str">
+        <v>거래처비용청구(3대)</v>
+      </c>
+      <c r="R453" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S453" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>T260903-00007</v>
+      </c>
+      <c r="B454" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C454" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D454" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E454" t="str">
+        <v>2026-09-03 14:30</v>
+      </c>
+      <c r="F454" t="str">
+        <v/>
+      </c>
+      <c r="G454">
+        <v>0</v>
+      </c>
+      <c r="H454" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I454" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J454" t="str">
+        <v>2026-09-03 15:30</v>
+      </c>
+      <c r="K454" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L454">
+        <v>1</v>
+      </c>
+      <c r="M454" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N454" t="str">
+        <v>2026-09-03 15:30:00</v>
+      </c>
+      <c r="O454" s="1">
+        <v>70000</v>
+      </c>
+      <c r="P454" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q454" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="R454" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S454" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>T260903-00006</v>
+      </c>
+      <c r="B455" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C455" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D455" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E455" t="str">
+        <v>2026-09-03 10:00</v>
+      </c>
+      <c r="F455" t="str">
+        <v/>
+      </c>
+      <c r="G455">
+        <v>0</v>
+      </c>
+      <c r="H455" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I455" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J455" t="str">
+        <v>2026-09-03 13:30</v>
+      </c>
+      <c r="K455" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L455">
+        <v>1</v>
+      </c>
+      <c r="M455" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N455" t="str">
+        <v>2026-09-03 15:29:14</v>
+      </c>
+      <c r="O455" s="1">
+        <v>160000</v>
+      </c>
+      <c r="P455" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q455" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="R455" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S455" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>T260903-00005</v>
+      </c>
+      <c r="B456" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C456" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D456" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E456" t="str">
+        <v>2026-09-03 13:50</v>
+      </c>
+      <c r="F456" t="str">
+        <v/>
+      </c>
+      <c r="G456">
+        <v>0</v>
+      </c>
+      <c r="H456" t="str">
+        <v>펠리체산후조리원하이얼</v>
+      </c>
+      <c r="I456" t="str">
+        <v>경기 화성시 만세구 꽃내음1길 19-22 펠리체산후조리원 하이얼</v>
+      </c>
+      <c r="J456" t="str">
+        <v>2026-09-03 16:00</v>
+      </c>
+      <c r="K456" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="L456">
+        <v>1</v>
+      </c>
+      <c r="M456" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N456" t="str">
+        <v>2026-09-03 13:37:58</v>
+      </c>
+      <c r="O456" s="1">
+        <v>110000</v>
+      </c>
+      <c r="P456" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q456" t="str">
+        <v/>
+      </c>
+      <c r="R456" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S456" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>T260903-00004</v>
+      </c>
+      <c r="B457" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C457" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D457" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E457" t="str">
+        <v>2026-09-03 16:00</v>
+      </c>
+      <c r="F457" t="str">
+        <v/>
+      </c>
+      <c r="G457">
+        <v>0</v>
+      </c>
+      <c r="H457" t="str">
+        <v>광주 하이마트 물류</v>
+      </c>
+      <c r="I457" t="str">
+        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
+      </c>
+      <c r="J457" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="K457" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L457">
+        <v>1</v>
+      </c>
+      <c r="M457" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N457" t="str">
+        <v>2026-09-03 13:14:56</v>
+      </c>
+      <c r="O457" s="1">
+        <v>400000</v>
+      </c>
+      <c r="P457" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q457" t="str">
+        <v>일코전자 광주 하이마트 물류</v>
+      </c>
+      <c r="R457" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S457" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>T260903-00003</v>
+      </c>
+      <c r="B458" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C458" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D458" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E458" t="str">
+        <v>2026-09-03 15:00</v>
+      </c>
+      <c r="F458" t="str">
+        <v/>
+      </c>
+      <c r="G458">
+        <v>0</v>
+      </c>
+      <c r="H458" t="str">
+        <v>대구 하이마트 물류</v>
+      </c>
+      <c r="I458" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="J458" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="K458" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L458">
+        <v>1</v>
+      </c>
+      <c r="M458" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N458" t="str">
+        <v>2026-09-03 10:24:04</v>
+      </c>
+      <c r="O458" s="1">
+        <v>340000</v>
+      </c>
+      <c r="P458" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q458" t="str">
+        <v>일코전자 대구 하이마트 물류</v>
+      </c>
+      <c r="R458" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S458" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>T260903-00002</v>
+      </c>
+      <c r="B459" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C459" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D459" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E459" t="str">
+        <v>2026-09-03 10:10</v>
+      </c>
+      <c r="F459" t="str">
+        <v/>
+      </c>
+      <c r="G459">
+        <v>0</v>
+      </c>
+      <c r="H459" t="str">
+        <v>마이디어 늘품마루</v>
+      </c>
+      <c r="I459" t="str">
+        <v>경기 이천시 백사면 지읍로 54 지하 2층 33번 도크</v>
+      </c>
+      <c r="J459" t="str">
+        <v>2026-09-03 11:30</v>
+      </c>
+      <c r="K459" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="L459">
+        <v>1</v>
+      </c>
+      <c r="M459" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N459" t="str">
+        <v>2026-09-03 10:23:19</v>
+      </c>
+      <c r="O459" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P459" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q459" t="str">
+        <v>마이디어 늘품마루</v>
+      </c>
+      <c r="R459" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S459" t="str">
+        <v>마이디어</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>T260903-00001</v>
+      </c>
+      <c r="B460" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C460" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D460" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E460" t="str">
+        <v>2026-09-03 09:00</v>
+      </c>
+      <c r="F460" t="str">
+        <v/>
+      </c>
+      <c r="G460">
+        <v>0</v>
+      </c>
+      <c r="H460" t="str">
+        <v>마이디어 늘품마루</v>
+      </c>
+      <c r="I460" t="str">
+        <v>경기 이천시 백사면 지읍로 54 지하 2층 33번 도크</v>
+      </c>
+      <c r="J460" t="str">
+        <v>2026-09-03 11:00</v>
+      </c>
+      <c r="K460" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="L460">
+        <v>1</v>
+      </c>
+      <c r="M460" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N460" t="str">
+        <v>2026-09-03 09:06:29</v>
+      </c>
+      <c r="O460" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P460" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q460" t="str">
+        <v>마이디어 늘품마루</v>
+      </c>
+      <c r="R460" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S460" t="str">
+        <v>마이디어</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>T260902-00030</v>
+      </c>
+      <c r="B461" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C461" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D461" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E461" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F461" t="str">
+        <v>대전중구ACP</v>
+      </c>
+      <c r="G461">
+        <v>1</v>
+      </c>
+      <c r="H461" t="str">
+        <v>대전대덕ACP</v>
+      </c>
+      <c r="I461" t="str">
+        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
+      </c>
+      <c r="J461" t="str">
+        <v>2026-09-03 06:00</v>
+      </c>
+      <c r="K461" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L461">
+        <v>1</v>
+      </c>
+      <c r="M461" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N461" t="str">
+        <v>2026-09-02 19:24:10</v>
+      </c>
+      <c r="O461" s="1">
+        <v>170000</v>
+      </c>
+      <c r="P461" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q461" t="str">
+        <v/>
+      </c>
+      <c r="R461" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S461" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>T260902-00029</v>
+      </c>
+      <c r="B462" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C462" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D462" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E462" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F462" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="G462">
+        <v>1</v>
+      </c>
+      <c r="H462" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="I462" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="J462" t="str">
+        <v>2026-09-03 07:00</v>
+      </c>
+      <c r="K462" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L462">
+        <v>1</v>
+      </c>
+      <c r="M462" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N462" t="str">
+        <v>2026-09-02 19:23:42</v>
+      </c>
+      <c r="O462" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P462" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q462" t="str">
+        <v/>
+      </c>
+      <c r="R462" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S462" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>T260902-00028</v>
+      </c>
+      <c r="B463" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C463" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D463" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E463" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F463" t="str">
+        <v>이천ACP,원주ACP</v>
+      </c>
+      <c r="G463">
+        <v>2</v>
+      </c>
+      <c r="H463" t="str">
+        <v>춘천ACP</v>
+      </c>
+      <c r="I463" t="str">
+        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
+      </c>
+      <c r="J463" t="str">
+        <v>2026-09-03 06:00</v>
+      </c>
+      <c r="K463" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L463">
+        <v>1</v>
+      </c>
+      <c r="M463" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N463" t="str">
+        <v>2026-09-02 19:23:13</v>
+      </c>
+      <c r="O463" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P463" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q463" t="str">
+        <v/>
+      </c>
+      <c r="R463" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S463" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>T260902-00027</v>
+      </c>
+      <c r="B464" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C464" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D464" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E464" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F464" t="str">
+        <v>군산ACP</v>
+      </c>
+      <c r="G464">
+        <v>1</v>
+      </c>
+      <c r="H464" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="I464" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="J464" t="str">
+        <v>2026-09-03 08:00</v>
+      </c>
+      <c r="K464" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L464">
+        <v>1</v>
+      </c>
+      <c r="M464" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N464" t="str">
+        <v>2026-09-02 19:22:37</v>
+      </c>
+      <c r="O464" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P464" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q464" t="str">
+        <v/>
+      </c>
+      <c r="R464" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S464" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>T260902-00026</v>
+      </c>
+      <c r="B465" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C465" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D465" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E465" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F465" t="str">
+        <v>용인ACP,화성ACP</v>
+      </c>
+      <c r="G465">
+        <v>2</v>
+      </c>
+      <c r="H465" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="I465" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="J465" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K465" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L465">
+        <v>1</v>
+      </c>
+      <c r="M465" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N465" t="str">
+        <v>2026-09-02 19:22:09</v>
+      </c>
+      <c r="O465" s="1">
+        <v>220000</v>
+      </c>
+      <c r="P465" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q465" t="str">
+        <v/>
+      </c>
+      <c r="R465" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S465" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>T260902-00025</v>
+      </c>
+      <c r="B466" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C466" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D466" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E466" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F466" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="G466">
+        <v>1</v>
+      </c>
+      <c r="H466" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="I466" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="J466" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K466" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L466">
+        <v>1</v>
+      </c>
+      <c r="M466" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N466" t="str">
+        <v>2026-09-02 19:21:37</v>
+      </c>
+      <c r="O466" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P466" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q466" t="str">
+        <v/>
+      </c>
+      <c r="R466" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S466" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>T260902-00024</v>
+      </c>
+      <c r="B467" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C467" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D467" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E467" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F467" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="G467">
+        <v>1</v>
+      </c>
+      <c r="H467" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="I467" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="J467" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K467" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L467">
+        <v>1</v>
+      </c>
+      <c r="M467" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N467" t="str">
+        <v>2026-09-02 19:21:17</v>
+      </c>
+      <c r="O467" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P467" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q467" t="str">
+        <v/>
+      </c>
+      <c r="R467" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S467" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>T260902-00023</v>
+      </c>
+      <c r="B468" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C468" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D468" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E468" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F468" t="str">
+        <v>원주FDC(신규)</v>
+      </c>
+      <c r="G468">
+        <v>1</v>
+      </c>
+      <c r="H468" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="I468" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="J468" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K468" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L468">
+        <v>1</v>
+      </c>
+      <c r="M468" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N468" t="str">
+        <v>2026-09-02 19:20:40</v>
+      </c>
+      <c r="O468" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P468" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q468" t="str">
+        <v/>
+      </c>
+      <c r="R468" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S468" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>T260902-00022</v>
+      </c>
+      <c r="B469" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C469" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D469" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E469" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F469" t="str">
+        <v>진주FDC,창원FDC</v>
+      </c>
+      <c r="G469">
+        <v>2</v>
+      </c>
+      <c r="H469" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="I469" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="J469" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K469" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L469">
+        <v>1</v>
+      </c>
+      <c r="M469" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N469" t="str">
+        <v>2026-09-02 19:20:16</v>
+      </c>
+      <c r="O469" s="1">
+        <v>730000</v>
+      </c>
+      <c r="P469" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q469" t="str">
+        <v/>
+      </c>
+      <c r="R469" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S469" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>T260902-00021</v>
+      </c>
+      <c r="B470" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C470" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D470" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E470" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F470" t="str">
+        <v/>
+      </c>
+      <c r="G470">
+        <v>0</v>
+      </c>
+      <c r="H470" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="I470" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="J470" t="str">
+        <v>2026-09-02 21:00</v>
+      </c>
+      <c r="K470" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L470">
+        <v>1</v>
+      </c>
+      <c r="M470" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N470" t="str">
+        <v>2026-09-02 19:19:46</v>
+      </c>
+      <c r="O470" s="1">
+        <v>250000</v>
+      </c>
+      <c r="P470" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q470" t="str">
+        <v/>
+      </c>
+      <c r="R470" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S470" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>T260902-00020</v>
+      </c>
+      <c r="B471" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C471" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D471" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E471" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F471" t="str">
+        <v/>
+      </c>
+      <c r="G471">
+        <v>0</v>
+      </c>
+      <c r="H471" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="I471" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="J471" t="str">
+        <v>2026-09-02 21:00</v>
+      </c>
+      <c r="K471" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L471">
+        <v>1</v>
+      </c>
+      <c r="M471" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N471" t="str">
+        <v>2026-09-02 19:19:30</v>
+      </c>
+      <c r="O471" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P471" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q471" t="str">
+        <v/>
+      </c>
+      <c r="R471" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S471" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>T260902-00019</v>
+      </c>
+      <c r="B472" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C472" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D472" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E472" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F472" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="G472">
+        <v>1</v>
+      </c>
+      <c r="H472" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="I472" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="J472" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K472" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L472">
+        <v>1</v>
+      </c>
+      <c r="M472" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N472" t="str">
+        <v>2026-09-02 19:19:13</v>
+      </c>
+      <c r="O472" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P472" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q472" t="str">
+        <v/>
+      </c>
+      <c r="R472" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S472" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>T260902-00018</v>
+      </c>
+      <c r="B473" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C473" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D473" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E473" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F473" t="str">
+        <v/>
+      </c>
+      <c r="G473">
+        <v>0</v>
+      </c>
+      <c r="H473" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="I473" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="J473" t="str">
+        <v>2026-09-02 21:00</v>
+      </c>
+      <c r="K473" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L473">
+        <v>1</v>
+      </c>
+      <c r="M473" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N473" t="str">
+        <v>2026-09-02 19:18:47</v>
+      </c>
+      <c r="O473" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P473" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q473" t="str">
+        <v/>
+      </c>
+      <c r="R473" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S473" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>T260902-00017</v>
+      </c>
+      <c r="B474" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C474" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D474" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E474" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F474" t="str">
+        <v>구미FDC(신규)</v>
+      </c>
+      <c r="G474">
+        <v>1</v>
+      </c>
+      <c r="H474" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="I474" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="J474" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K474" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L474">
+        <v>1</v>
+      </c>
+      <c r="M474" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N474" t="str">
+        <v>2026-09-02 19:17:37</v>
+      </c>
+      <c r="O474" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P474" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q474" t="str">
+        <v/>
+      </c>
+      <c r="R474" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S474" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>T260902-00016</v>
+      </c>
+      <c r="B475" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C475" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D475" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E475" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F475" t="str">
+        <v>강릉ACP</v>
+      </c>
+      <c r="G475">
+        <v>1</v>
+      </c>
+      <c r="H475" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="I475" t="str">
+        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="J475" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K475" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L475">
+        <v>1</v>
+      </c>
+      <c r="M475" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N475" t="str">
+        <v>2026-09-02 19:16:53</v>
+      </c>
+      <c r="O475" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P475" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q475" t="str">
+        <v/>
+      </c>
+      <c r="R475" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S475" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>T260902-00015</v>
+      </c>
+      <c r="B476" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C476" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D476" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E476" t="str">
+        <v>2026-09-02 18:10</v>
+      </c>
+      <c r="F476" t="str">
+        <v/>
+      </c>
+      <c r="G476">
+        <v>0</v>
+      </c>
+      <c r="H476" t="str">
+        <v>양산 하이마트 하이얼</v>
+      </c>
+      <c r="I476" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 하이얼</v>
+      </c>
+      <c r="J476" t="str">
+        <v>2026-09-03 21:30</v>
+      </c>
+      <c r="K476" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L476">
+        <v>1</v>
+      </c>
+      <c r="M476" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N476" t="str">
+        <v>2026-09-02 17:49:53</v>
+      </c>
+      <c r="O476" s="1">
+        <v>340000</v>
+      </c>
+      <c r="P476" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q476" t="str">
+        <v>하이얼 양산 하이마트 물류</v>
+      </c>
+      <c r="R476" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S476" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>T260902-00014</v>
+      </c>
+      <c r="B477" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C477" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D477" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E477" t="str">
+        <v>2026-09-02 17:30</v>
+      </c>
+      <c r="F477" t="str">
+        <v/>
+      </c>
+      <c r="G477">
+        <v>0</v>
+      </c>
+      <c r="H477" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="I477" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="J477" t="str">
+        <v>2026-09-02 18:30</v>
+      </c>
+      <c r="K477" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L477">
+        <v>1</v>
+      </c>
+      <c r="M477" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N477" t="str">
+        <v>2026-09-02 17:27:54</v>
+      </c>
+      <c r="O477" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P477" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q477" t="str">
+        <v/>
+      </c>
+      <c r="R477" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S477" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>T260902-00013</v>
+      </c>
+      <c r="B478" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C478" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="D478" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="E478" t="str">
+        <v>2026-09-02 11:00</v>
+      </c>
+      <c r="F478" t="str">
+        <v/>
+      </c>
+      <c r="G478">
+        <v>0</v>
+      </c>
+      <c r="H478" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I478" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J478" t="str">
+        <v>2026-09-02 13:30</v>
+      </c>
+      <c r="K478" t="str">
+        <v>1톤 기타차량</v>
+      </c>
+      <c r="L478">
+        <v>1</v>
+      </c>
+      <c r="M478" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N478" t="str">
+        <v>2026-09-02 17:27:24</v>
+      </c>
+      <c r="O478" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P478" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q478" t="str">
+        <v>거래처비용청구(1대)</v>
+      </c>
+      <c r="R478" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S478" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>T260902-00012</v>
+      </c>
+      <c r="B479" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C479" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D479" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E479" t="str">
+        <v>2026-09-02 14:30</v>
+      </c>
+      <c r="F479" t="str">
+        <v/>
+      </c>
+      <c r="G479">
+        <v>0</v>
+      </c>
+      <c r="H479" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I479" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J479" t="str">
+        <v>2026-09-02 15:30</v>
+      </c>
+      <c r="K479" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L479">
+        <v>1</v>
+      </c>
+      <c r="M479" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N479" t="str">
+        <v>2026-09-02 17:26:30</v>
+      </c>
+      <c r="O479" s="1">
+        <v>70000</v>
+      </c>
+      <c r="P479" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q479" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="R479" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S479" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>T260902-00011</v>
+      </c>
+      <c r="B480" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C480" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D480" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E480" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="F480" t="str">
+        <v/>
+      </c>
+      <c r="G480">
+        <v>0</v>
+      </c>
+      <c r="H480" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I480" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J480" t="str">
+        <v>2026-09-02 13:30</v>
+      </c>
+      <c r="K480" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L480">
+        <v>1</v>
+      </c>
+      <c r="M480" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N480" t="str">
+        <v>2026-09-02 17:25:43</v>
+      </c>
+      <c r="O480" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P480" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q480" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="R480" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S480" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>T260902-00010</v>
+      </c>
+      <c r="B481" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C481" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D481" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E481" t="str">
+        <v>2026-09-02 17:10</v>
+      </c>
+      <c r="F481" t="str">
+        <v/>
+      </c>
+      <c r="G481">
+        <v>0</v>
+      </c>
+      <c r="H481" t="str">
+        <v>마산 하이마트 하이얼</v>
+      </c>
+      <c r="I481" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 하이얼</v>
+      </c>
+      <c r="J481" t="str">
+        <v>2026-09-03 09:30</v>
+      </c>
+      <c r="K481" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L481">
+        <v>1</v>
+      </c>
+      <c r="M481" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N481" t="str">
+        <v>2026-09-02 16:04:12</v>
+      </c>
+      <c r="O481" s="1">
+        <v>340000</v>
+      </c>
+      <c r="P481" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q481" t="str">
+        <v>하이얼  마산 하이마트 물류</v>
+      </c>
+      <c r="R481" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S481" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>T260902-00009</v>
+      </c>
+      <c r="B482" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C482" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D482" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E482" t="str">
+        <v>2026-09-02 16:30</v>
+      </c>
+      <c r="F482" t="str">
+        <v/>
+      </c>
+      <c r="G482">
+        <v>0</v>
+      </c>
+      <c r="H482" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I482" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="J482" t="str">
+        <v>2026-09-02 17:30</v>
+      </c>
+      <c r="K482" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L482">
+        <v>1</v>
+      </c>
+      <c r="M482" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N482" t="str">
+        <v>2026-09-02 16:01:28</v>
+      </c>
+      <c r="O482" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P482" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q482" t="str">
+        <v/>
+      </c>
+      <c r="R482" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S482" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>T260902-00008</v>
+      </c>
+      <c r="B483" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C483" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D483" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E483" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="F483" t="str">
+        <v/>
+      </c>
+      <c r="G483">
+        <v>0</v>
+      </c>
+      <c r="H483" t="str">
+        <v>이천 하이마트 하이얼</v>
+      </c>
+      <c r="I483" t="str">
+        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 하이얼</v>
+      </c>
+      <c r="J483" t="str">
+        <v>2026-09-02 15:00</v>
+      </c>
+      <c r="K483" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L483">
+        <v>1</v>
+      </c>
+      <c r="M483" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N483" t="str">
+        <v>2026-09-02 10:54:59</v>
+      </c>
+      <c r="O483" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P483" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q483" t="str">
+        <v>하이얼 이천 하이마트 물류</v>
+      </c>
+      <c r="R483" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S483" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>T260902-00007</v>
+      </c>
+      <c r="B484" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C484" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D484" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E484" t="str">
+        <v>2026-09-02 09:40</v>
+      </c>
+      <c r="F484" t="str">
+        <v/>
+      </c>
+      <c r="G484">
+        <v>0</v>
+      </c>
+      <c r="H484" t="str">
+        <v>화성 하이마트 하이얼</v>
+      </c>
+      <c r="I484" t="str">
+        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 하이얼</v>
+      </c>
+      <c r="J484" t="str">
+        <v>2026-09-02 03:00</v>
+      </c>
+      <c r="K484" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L484">
+        <v>1</v>
+      </c>
+      <c r="M484" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N484" t="str">
+        <v>2026-09-02 10:50:30</v>
+      </c>
+      <c r="O484" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P484" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q484" t="str">
+        <v>히이얼 화성 하이마트 물류</v>
+      </c>
+      <c r="R484" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S484" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>T260902-00006</v>
+      </c>
+      <c r="B485" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C485" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D485" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E485" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F485" t="str">
+        <v/>
+      </c>
+      <c r="G485">
+        <v>0</v>
+      </c>
+      <c r="H485" t="str">
+        <v>인천 하이마트 하이얼</v>
+      </c>
+      <c r="I485" t="str">
+        <v>인천 중구 서해대로94번길 132 인천 하이마트 하이얼</v>
+      </c>
+      <c r="J485" t="str">
+        <v>2026-09-02 03:00</v>
+      </c>
+      <c r="K485" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L485">
+        <v>1</v>
+      </c>
+      <c r="M485" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N485" t="str">
+        <v>2026-09-02 10:36:26</v>
+      </c>
+      <c r="O485" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P485" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q485" t="str">
+        <v>하이얼 인천 하이마트 물류</v>
+      </c>
+      <c r="R485" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S485" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>T260902-00005</v>
+      </c>
+      <c r="B486" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C486" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D486" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E486" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F486" t="str">
+        <v/>
+      </c>
+      <c r="G486">
+        <v>0</v>
+      </c>
+      <c r="H486" t="str">
+        <v>아임테크날러지 창고</v>
+      </c>
+      <c r="I486" t="str">
+        <v>경기 김포시 통진읍 월하로479번길 32-42 가동, 나동</v>
+      </c>
+      <c r="J486" t="str">
+        <v>2026-09-02 11:00</v>
+      </c>
+      <c r="K486" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L486">
+        <v>1</v>
+      </c>
+      <c r="M486" t="str">
+        <v>차순권</v>
+      </c>
+      <c r="N486" t="str">
+        <v>2026-09-02 09:52:58</v>
+      </c>
+      <c r="O486" s="1">
+        <v>230000</v>
+      </c>
+      <c r="P486" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q486" t="str">
+        <v>아임테크 날러지 회수2, 가용 1파렛트 출하</v>
+      </c>
+      <c r="R486" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S486" t="str">
+        <v>아임테크날러지</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>T260902-00004</v>
+      </c>
+      <c r="B487" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C487" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D487" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E487" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F487" t="str">
+        <v/>
+      </c>
+      <c r="G487">
+        <v>0</v>
+      </c>
+      <c r="H487" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I487" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J487" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="K487" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L487">
+        <v>1</v>
+      </c>
+      <c r="M487" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N487" t="str">
+        <v>2026-09-02 09:49:55</v>
+      </c>
+      <c r="O487" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P487" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q487" t="str">
+        <v>중산물산 회수품</v>
+      </c>
+      <c r="R487" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S487" t="str">
+        <v>중산물산</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>T260902-00003</v>
+      </c>
+      <c r="B488" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C488" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D488" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E488" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F488" t="str">
+        <v/>
+      </c>
+      <c r="G488">
+        <v>0</v>
+      </c>
+      <c r="H488" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I488" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J488" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="K488" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L488">
+        <v>1</v>
+      </c>
+      <c r="M488" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N488" t="str">
+        <v>2026-09-02 09:37:44</v>
+      </c>
+      <c r="O488" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P488" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q488" t="str">
+        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
+      </c>
+      <c r="R488" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S488" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>T260902-00002</v>
+      </c>
+      <c r="B489" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C489" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D489" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E489" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F489" t="str">
+        <v/>
+      </c>
+      <c r="G489">
+        <v>0</v>
+      </c>
+      <c r="H489" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I489" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J489" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="K489" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L489">
+        <v>1</v>
+      </c>
+      <c r="M489" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N489" t="str">
+        <v>2026-09-02 09:37:02</v>
+      </c>
+      <c r="O489" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P489" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q489" t="str">
+        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
+      </c>
+      <c r="R489" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S489" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>T260902-00001</v>
+      </c>
+      <c r="B490" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C490" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D490" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E490" t="str">
+        <v>2026-09-02 09:50</v>
+      </c>
+      <c r="F490" t="str">
+        <v/>
+      </c>
+      <c r="G490">
+        <v>0</v>
+      </c>
+      <c r="H490" t="str">
+        <v>아임테크</v>
+      </c>
+      <c r="I490" t="str">
+        <v>경기 김포시 통진읍 귀전리 537-4 아임테크</v>
+      </c>
+      <c r="J490" t="str">
+        <v>2026-09-02 11:00</v>
+      </c>
+      <c r="K490" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L490">
+        <v>1</v>
+      </c>
+      <c r="M490" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N490" t="str">
+        <v>2026-09-02 09:33:24</v>
+      </c>
+      <c r="O490" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P490" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q490" t="str">
+        <v>아임테크날러지 전량 출하</v>
+      </c>
+      <c r="R490" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S490" t="str">
+        <v>아임테크날러지</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>T260901-00019</v>
+      </c>
+      <c r="B491" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C491" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D491" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E491" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F491" t="str">
+        <v>시흥ACP,인천ACP</v>
+      </c>
+      <c r="G491">
+        <v>2</v>
+      </c>
+      <c r="H491" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="I491" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="J491" t="str">
+        <v>2026-09-02 07:00</v>
+      </c>
+      <c r="K491" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L491">
+        <v>1</v>
+      </c>
+      <c r="M491" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N491" t="str">
+        <v>2026-09-01 19:27:06</v>
+      </c>
+      <c r="O491" s="1">
+        <v>230000</v>
+      </c>
+      <c r="P491" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q491" t="str">
+        <v/>
+      </c>
+      <c r="R491" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S491" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>T260901-00018</v>
+      </c>
+      <c r="B492" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C492" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D492" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E492" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F492" t="str">
+        <v>대전중구ACP,대전대덕ACP</v>
+      </c>
+      <c r="G492">
+        <v>2</v>
+      </c>
+      <c r="H492" t="str">
+        <v>군산ACP</v>
+      </c>
+      <c r="I492" t="str">
+        <v>전북특별자치도 군산시 구암3.1로 60 군산ACP</v>
+      </c>
+      <c r="J492" t="str">
+        <v>2026-09-02 07:00</v>
+      </c>
+      <c r="K492" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L492">
+        <v>1</v>
+      </c>
+      <c r="M492" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N492" t="str">
+        <v>2026-09-01 19:26:35</v>
+      </c>
+      <c r="O492" s="1">
+        <v>300000</v>
+      </c>
+      <c r="P492" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q492" t="str">
+        <v/>
+      </c>
+      <c r="R492" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S492" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>T260901-00017</v>
+      </c>
+      <c r="B493" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C493" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D493" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E493" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F493" t="str">
+        <v>안성ACP,화성ACP,용인ACP</v>
+      </c>
+      <c r="G493">
+        <v>3</v>
+      </c>
+      <c r="H493" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="I493" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="J493" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K493" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L493">
+        <v>1</v>
+      </c>
+      <c r="M493" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N493" t="str">
+        <v>2026-09-01 19:25:58</v>
+      </c>
+      <c r="O493" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P493" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q493" t="str">
+        <v/>
+      </c>
+      <c r="R493" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S493" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>T260901-00016</v>
+      </c>
+      <c r="B494" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C494" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D494" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E494" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F494" t="str">
+        <v/>
+      </c>
+      <c r="G494">
+        <v>0</v>
+      </c>
+      <c r="H494" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="I494" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="J494" t="str">
+        <v>2026-09-01 21:00</v>
+      </c>
+      <c r="K494" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L494">
+        <v>1</v>
+      </c>
+      <c r="M494" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N494" t="str">
+        <v>2026-09-01 19:25:13</v>
+      </c>
+      <c r="O494" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P494" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q494" t="str">
+        <v/>
+      </c>
+      <c r="R494" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S494" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>T260901-00015</v>
+      </c>
+      <c r="B495" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C495" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D495" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E495" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F495" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="G495">
+        <v>1</v>
+      </c>
+      <c r="H495" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="I495" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="J495" t="str">
+        <v>2026-09-01 22:00</v>
+      </c>
+      <c r="K495" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L495">
+        <v>1</v>
+      </c>
+      <c r="M495" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N495" t="str">
+        <v>2026-09-01 19:24:58</v>
+      </c>
+      <c r="O495" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P495" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q495" t="str">
+        <v/>
+      </c>
+      <c r="R495" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S495" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>T260901-00014</v>
+      </c>
+      <c r="B496" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C496" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D496" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E496" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F496" t="str">
+        <v/>
+      </c>
+      <c r="G496">
+        <v>0</v>
+      </c>
+      <c r="H496" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="I496" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="J496" t="str">
+        <v>2026-09-01 21:00</v>
+      </c>
+      <c r="K496" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L496">
+        <v>1</v>
+      </c>
+      <c r="M496" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N496" t="str">
+        <v>2026-09-01 19:24:38</v>
+      </c>
+      <c r="O496" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P496" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q496" t="str">
+        <v/>
+      </c>
+      <c r="R496" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S496" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>T260901-00013</v>
+      </c>
+      <c r="B497" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C497" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D497" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E497" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F497" t="str">
+        <v>원주FDC(신규)</v>
+      </c>
+      <c r="G497">
+        <v>1</v>
+      </c>
+      <c r="H497" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="I497" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="J497" t="str">
+        <v>2026-09-01 22:00</v>
+      </c>
+      <c r="K497" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L497">
+        <v>1</v>
+      </c>
+      <c r="M497" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N497" t="str">
+        <v>2026-09-01 19:24:22</v>
+      </c>
+      <c r="O497" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P497" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q497" t="str">
+        <v/>
+      </c>
+      <c r="R497" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S497" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
+        <v>T260901-00012</v>
+      </c>
+      <c r="B498" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C498" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D498" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E498" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F498" t="str">
+        <v>진주FDC,창원FDC</v>
+      </c>
+      <c r="G498">
+        <v>2</v>
+      </c>
+      <c r="H498" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="I498" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="J498" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K498" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L498">
+        <v>1</v>
+      </c>
+      <c r="M498" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N498" t="str">
+        <v>2026-09-01 19:23:57</v>
+      </c>
+      <c r="O498" s="1">
+        <v>730000</v>
+      </c>
+      <c r="P498" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q498" t="str">
+        <v/>
+      </c>
+      <c r="R498" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S498" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>T260901-00011</v>
+      </c>
+      <c r="B499" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C499" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D499" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E499" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F499" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="G499">
+        <v>1</v>
+      </c>
+      <c r="H499" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="I499" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="J499" t="str">
+        <v>2026-09-01 22:00</v>
+      </c>
+      <c r="K499" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L499">
+        <v>1</v>
+      </c>
+      <c r="M499" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N499" t="str">
+        <v>2026-09-01 19:23:32</v>
+      </c>
+      <c r="O499" s="1">
+        <v>370000</v>
+      </c>
+      <c r="P499" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q499" t="str">
+        <v/>
+      </c>
+      <c r="R499" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S499" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>T260901-00010</v>
+      </c>
+      <c r="B500" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C500" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D500" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E500" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F500" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="G500">
+        <v>1</v>
+      </c>
+      <c r="H500" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="I500" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="J500" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K500" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L500">
+        <v>1</v>
+      </c>
+      <c r="M500" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N500" t="str">
+        <v>2026-09-01 19:23:13</v>
+      </c>
+      <c r="O500" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P500" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q500" t="str">
+        <v/>
+      </c>
+      <c r="R500" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S500" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>T260901-00009</v>
+      </c>
+      <c r="B501" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C501" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D501" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E501" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F501" t="str">
+        <v/>
+      </c>
+      <c r="G501">
+        <v>0</v>
+      </c>
+      <c r="H501" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="I501" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="J501" t="str">
+        <v>2026-09-01 21:00</v>
+      </c>
+      <c r="K501" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L501">
+        <v>1</v>
+      </c>
+      <c r="M501" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N501" t="str">
+        <v>2026-09-01 19:22:26</v>
+      </c>
+      <c r="O501" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P501" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q501" t="str">
+        <v/>
+      </c>
+      <c r="R501" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S501" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
+        <v>T260901-00008</v>
+      </c>
+      <c r="B502" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C502" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D502" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E502" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F502" t="str">
+        <v>구미FDC(신규)</v>
+      </c>
+      <c r="G502">
+        <v>1</v>
+      </c>
+      <c r="H502" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="I502" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="J502" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K502" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L502">
+        <v>1</v>
+      </c>
+      <c r="M502" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N502" t="str">
+        <v>2026-09-01 19:22:10</v>
+      </c>
+      <c r="O502" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P502" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q502" t="str">
+        <v/>
+      </c>
+      <c r="R502" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S502" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>T260901-00007</v>
+      </c>
+      <c r="B503" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C503" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D503" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E503" t="str">
+        <v>2026-09-01 17:20</v>
+      </c>
+      <c r="F503" t="str">
+        <v/>
+      </c>
+      <c r="G503">
+        <v>0</v>
+      </c>
+      <c r="H503" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="I503" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="J503" t="str">
+        <v>2026-09-01 18:20</v>
+      </c>
+      <c r="K503" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L503">
+        <v>1</v>
+      </c>
+      <c r="M503" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N503" t="str">
+        <v>2026-09-01 19:20:06</v>
+      </c>
+      <c r="O503" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P503" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q503" t="str">
+        <v/>
+      </c>
+      <c r="R503" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S503" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>T260901-00006</v>
+      </c>
+      <c r="B504" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C504" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="D504" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="E504" t="str">
+        <v>2026-09-01 11:20</v>
+      </c>
+      <c r="F504" t="str">
+        <v/>
+      </c>
+      <c r="G504">
+        <v>0</v>
+      </c>
+      <c r="H504" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I504" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J504" t="str">
+        <v>2026-09-01 13:20</v>
+      </c>
+      <c r="K504" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L504">
+        <v>1</v>
+      </c>
+      <c r="M504" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N504" t="str">
+        <v>2026-09-01 19:19:31</v>
+      </c>
+      <c r="O504" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P504" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q504" t="str">
+        <v>거래처비용청구(2대)</v>
+      </c>
+      <c r="R504" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S504" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>T260901-00005</v>
+      </c>
+      <c r="B505" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C505" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D505" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E505" t="str">
+        <v>2026-09-01 14:20</v>
+      </c>
+      <c r="F505" t="str">
+        <v/>
+      </c>
+      <c r="G505">
+        <v>0</v>
+      </c>
+      <c r="H505" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I505" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J505" t="str">
+        <v>2026-09-01 15:20</v>
+      </c>
+      <c r="K505" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L505">
+        <v>1</v>
+      </c>
+      <c r="M505" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N505" t="str">
+        <v>2026-09-01 19:18:39</v>
+      </c>
+      <c r="O505" s="1">
+        <v>70000</v>
+      </c>
+      <c r="P505" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q505" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="R505" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S505" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>T260901-00004</v>
+      </c>
+      <c r="B506" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C506" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D506" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E506" t="str">
+        <v>2026-09-01 15:50</v>
+      </c>
+      <c r="F506" t="str">
+        <v/>
+      </c>
+      <c r="G506">
+        <v>0</v>
+      </c>
+      <c r="H506" t="str">
+        <v>공주 하이마트 하이얼</v>
+      </c>
+      <c r="I506" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="J506" t="str">
+        <v>2026-09-02 15:00</v>
+      </c>
+      <c r="K506" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L506">
+        <v>1</v>
+      </c>
+      <c r="M506" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N506" t="str">
+        <v>2026-09-01 15:50:14</v>
+      </c>
+      <c r="O506" s="1">
+        <v>220000</v>
+      </c>
+      <c r="P506" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q506" t="str">
+        <v>하이얼 공주 하이마트 물류</v>
+      </c>
+      <c r="R506" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S506" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>T260901-00003</v>
+      </c>
+      <c r="B507" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C507" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D507" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E507" t="str">
+        <v>2026-09-01 15:35</v>
+      </c>
+      <c r="F507" t="str">
+        <v/>
+      </c>
+      <c r="G507">
+        <v>0</v>
+      </c>
+      <c r="H507" t="str">
+        <v>대구 하이마트 하이얼</v>
+      </c>
+      <c r="I507" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="J507" t="str">
+        <v>2026-09-02 15:00</v>
+      </c>
+      <c r="K507" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L507">
+        <v>1</v>
+      </c>
+      <c r="M507" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N507" t="str">
+        <v>2026-09-01 13:37:23</v>
+      </c>
+      <c r="O507" s="1">
+        <v>300000</v>
+      </c>
+      <c r="P507" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q507" t="str">
+        <v>하이얼 대구 하이마트 물류</v>
+      </c>
+      <c r="R507" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S507" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>T260901-00002</v>
+      </c>
+      <c r="B508" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C508" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="D508" t="str">
+        <v>인천 서구 오류동 1653-2 인천FDC</v>
+      </c>
+      <c r="E508" t="str">
+        <v>2026-09-02 08:00</v>
+      </c>
+      <c r="F508" t="str">
+        <v/>
+      </c>
+      <c r="G508">
+        <v>0</v>
+      </c>
+      <c r="H508" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="I508" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="J508" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="K508" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L508">
+        <v>1</v>
+      </c>
+      <c r="M508" t="str">
+        <v>차순권</v>
+      </c>
+      <c r="N508" t="str">
+        <v>2026-09-01 13:22:36</v>
+      </c>
+      <c r="O508" s="1">
+        <v>50000</v>
+      </c>
+      <c r="P508" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q508" t="str">
+        <v>접수번호 : 1565331 / 취소 건 샤오미 창고로 출하 / 인천FDC에서 직접 배송함</v>
+      </c>
+      <c r="R508" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S508" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>T260901-00001</v>
+      </c>
+      <c r="B509" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C509" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="D509" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 821 곤지암FDC</v>
+      </c>
+      <c r="E509" t="str">
+        <v>2026-09-01 08:00</v>
+      </c>
+      <c r="F509" t="str">
+        <v/>
+      </c>
+      <c r="G509">
+        <v>0</v>
+      </c>
+      <c r="H509" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I509" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J509" t="str">
+        <v>2026-09-01 10:00</v>
+      </c>
+      <c r="K509" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L509">
+        <v>1</v>
+      </c>
+      <c r="M509" t="str">
+        <v>차순권</v>
+      </c>
+      <c r="N509" t="str">
+        <v>2026-09-01 09:03:56</v>
+      </c>
+      <c r="O509" s="1">
+        <v>80000</v>
+      </c>
+      <c r="P509" s="1">
+        <v>5000</v>
+      </c>
+      <c r="Q509" t="str">
+        <v>하이얼 가용재고 10개 이동</v>
+      </c>
+      <c r="R509" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S509" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S431"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S509"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -443,7 +443,7 @@
         <v>T261006-00024</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -502,7 +502,7 @@
         <v>T261006-00023</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -561,7 +561,7 @@
         <v>T261006-00022</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -620,7 +620,7 @@
         <v>T261006-00021</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -679,7 +679,7 @@
         <v>T261006-00020</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -738,7 +738,7 @@
         <v>T261006-00019</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -797,7 +797,7 @@
         <v>T261006-00018</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -856,7 +856,7 @@
         <v>T261006-00017</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -915,7 +915,7 @@
         <v>T261006-00016</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -974,7 +974,7 @@
         <v>T261006-00015</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1033,7 +1033,7 @@
         <v>T261006-00014</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1092,7 +1092,7 @@
         <v>T261006-00013</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1151,7 +1151,7 @@
         <v>T261006-00012</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1210,7 +1210,7 @@
         <v>T261006-00011</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1269,7 +1269,7 @@
         <v>T261006-00010</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>안성FC</v>
@@ -1328,7 +1328,7 @@
         <v>T261006-00009</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>안성FC</v>
@@ -1387,7 +1387,7 @@
         <v>T261006-00008</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>청주ARC</v>
@@ -1446,7 +1446,7 @@
         <v>T261006-00007</v>
       </c>
       <c r="B19" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>라꾸스토리</v>
@@ -1505,7 +1505,7 @@
         <v>T261006-00006</v>
       </c>
       <c r="B20" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>화성FDC</v>
@@ -1564,7 +1564,7 @@
         <v>T261006-00005</v>
       </c>
       <c r="B21" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C21" t="str">
         <v>아이베</v>
@@ -1623,7 +1623,7 @@
         <v>T261006-00004</v>
       </c>
       <c r="B22" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C22" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S441"/>
+  <dimension ref="A1:S549"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,7 +443,7 @@
         <v>T261007-00017</v>
       </c>
       <c r="B2" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -482,16 +482,16 @@
         <v>2026-10-07 18:25:36</v>
       </c>
       <c r="O2" s="1">
-        <v/>
+        <v>240000</v>
       </c>
       <c r="P2" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q2" t="str">
         <v/>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S2" t="str">
         <v>(주)위니온로지스</v>
@@ -502,7 +502,7 @@
         <v>T261007-00016</v>
       </c>
       <c r="B3" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -541,16 +541,16 @@
         <v>2026-10-07 18:24:52</v>
       </c>
       <c r="O3" s="1">
-        <v/>
+        <v>170000</v>
       </c>
       <c r="P3" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q3" t="str">
         <v/>
       </c>
       <c r="R3" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S3" t="str">
         <v>(주)위니온로지스</v>
@@ -561,7 +561,7 @@
         <v>T261007-00015</v>
       </c>
       <c r="B4" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -600,16 +600,16 @@
         <v>2026-10-07 18:24:29</v>
       </c>
       <c r="O4" s="1">
-        <v/>
+        <v>610000</v>
       </c>
       <c r="P4" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q4" t="str">
         <v/>
       </c>
       <c r="R4" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S4" t="str">
         <v>(주)위니온로지스</v>
@@ -620,7 +620,7 @@
         <v>T261007-00014</v>
       </c>
       <c r="B5" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -659,16 +659,16 @@
         <v>2026-10-07 18:23:21</v>
       </c>
       <c r="O5" s="1">
-        <v/>
+        <v>350000</v>
       </c>
       <c r="P5" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q5" t="str">
         <v/>
       </c>
       <c r="R5" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S5" t="str">
         <v>(주)위니온로지스</v>
@@ -679,7 +679,7 @@
         <v>T261007-00013</v>
       </c>
       <c r="B6" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -718,16 +718,16 @@
         <v>2026-10-07 18:22:56</v>
       </c>
       <c r="O6" s="1">
-        <v/>
+        <v>370000</v>
       </c>
       <c r="P6" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q6" t="str">
         <v/>
       </c>
       <c r="R6" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S6" t="str">
         <v>(주)위니온로지스</v>
@@ -738,7 +738,7 @@
         <v>T261007-00012</v>
       </c>
       <c r="B7" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -777,16 +777,16 @@
         <v>2026-10-07 18:22:26</v>
       </c>
       <c r="O7" s="1">
-        <v/>
+        <v>290000</v>
       </c>
       <c r="P7" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q7" t="str">
         <v/>
       </c>
       <c r="R7" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S7" t="str">
         <v>(주)위니온로지스</v>
@@ -797,7 +797,7 @@
         <v>T261007-00010</v>
       </c>
       <c r="B8" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -836,16 +836,16 @@
         <v>2026-10-07 18:21:25</v>
       </c>
       <c r="O8" s="1">
-        <v/>
+        <v>370000</v>
       </c>
       <c r="P8" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q8" t="str">
         <v/>
       </c>
       <c r="R8" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S8" t="str">
         <v>(주)위니온로지스</v>
@@ -856,7 +856,7 @@
         <v>T261007-00009</v>
       </c>
       <c r="B9" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -895,16 +895,16 @@
         <v>2026-10-07 18:21:03</v>
       </c>
       <c r="O9" s="1">
-        <v/>
+        <v>570000</v>
       </c>
       <c r="P9" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q9" t="str">
         <v/>
       </c>
       <c r="R9" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S9" t="str">
         <v>(주)위니온로지스</v>
@@ -915,7 +915,7 @@
         <v>T261007-00008</v>
       </c>
       <c r="B10" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -954,16 +954,16 @@
         <v>2026-10-07 18:20:39</v>
       </c>
       <c r="O10" s="1">
-        <v/>
+        <v>520000</v>
       </c>
       <c r="P10" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q10" t="str">
         <v/>
       </c>
       <c r="R10" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S10" t="str">
         <v>(주)위니온로지스</v>
@@ -974,7 +974,7 @@
         <v>T261007-00007</v>
       </c>
       <c r="B11" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1013,16 +1013,16 @@
         <v>2026-10-07 18:20:16</v>
       </c>
       <c r="O11" s="1">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="P11" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q11" t="str">
         <v/>
       </c>
       <c r="R11" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S11" t="str">
         <v>(주)위니온로지스</v>
@@ -1033,7 +1033,7 @@
         <v>T261007-00006</v>
       </c>
       <c r="B12" t="str">
-        <v>접수</v>
+        <v>배차완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1072,16 +1072,16 @@
         <v>2026-10-07 18:20:01</v>
       </c>
       <c r="O12" s="1">
-        <v/>
+        <v>240000</v>
       </c>
       <c r="P12" s="1">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q12" t="str">
         <v/>
       </c>
       <c r="R12" t="str">
-        <v/>
+        <v>JM컴퍼니</v>
       </c>
       <c r="S12" t="str">
         <v>(주)위니온로지스</v>
@@ -26398,9 +26398,6381 @@
         <v>일코전자</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>T260904-00030</v>
+      </c>
+      <c r="B442" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C442" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D442" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E442" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F442" t="str">
+        <v>시흥ACP,인천ACP</v>
+      </c>
+      <c r="G442">
+        <v>2</v>
+      </c>
+      <c r="H442" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="I442" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="J442" t="str">
+        <v>2026-09-05 08:00</v>
+      </c>
+      <c r="K442" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="L442">
+        <v>1</v>
+      </c>
+      <c r="M442" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N442" t="str">
+        <v>2026-09-04 19:35:26</v>
+      </c>
+      <c r="O442" s="1">
+        <v>250000</v>
+      </c>
+      <c r="P442" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q442" t="str">
+        <v/>
+      </c>
+      <c r="R442" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S442" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>T260904-00029</v>
+      </c>
+      <c r="B443" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C443" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D443" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E443" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F443" t="str">
+        <v>대전대덕ACP</v>
+      </c>
+      <c r="G443">
+        <v>1</v>
+      </c>
+      <c r="H443" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="I443" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="J443" t="str">
+        <v>2026-09-05 08:00</v>
+      </c>
+      <c r="K443" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L443">
+        <v>1</v>
+      </c>
+      <c r="M443" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N443" t="str">
+        <v>2026-09-04 19:34:55</v>
+      </c>
+      <c r="O443" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P443" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q443" t="str">
+        <v/>
+      </c>
+      <c r="R443" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S443" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>T260904-00028</v>
+      </c>
+      <c r="B444" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C444" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D444" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E444" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F444" t="str">
+        <v/>
+      </c>
+      <c r="G444">
+        <v>0</v>
+      </c>
+      <c r="H444" t="str">
+        <v>구미ACP</v>
+      </c>
+      <c r="I444" t="str">
+        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
+      </c>
+      <c r="J444" t="str">
+        <v>2026-09-04 22:00</v>
+      </c>
+      <c r="K444" t="str">
+        <v>1톤 기타차량</v>
+      </c>
+      <c r="L444">
+        <v>1</v>
+      </c>
+      <c r="M444" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N444" t="str">
+        <v>2026-09-04 19:34:17</v>
+      </c>
+      <c r="O444" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P444" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q444" t="str">
+        <v/>
+      </c>
+      <c r="R444" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S444" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
+        <v>T260904-00027</v>
+      </c>
+      <c r="B445" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C445" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D445" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E445" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F445" t="str">
+        <v>안성ACP,용인ACP,화성ACP,구리ACP</v>
+      </c>
+      <c r="G445">
+        <v>4</v>
+      </c>
+      <c r="H445" t="str">
+        <v>춘천ACP</v>
+      </c>
+      <c r="I445" t="str">
+        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
+      </c>
+      <c r="J445" t="str">
+        <v>2026-09-04 23:59</v>
+      </c>
+      <c r="K445" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L445">
+        <v>1</v>
+      </c>
+      <c r="M445" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N445" t="str">
+        <v>2026-09-04 19:33:56</v>
+      </c>
+      <c r="O445" s="1">
+        <v>380000</v>
+      </c>
+      <c r="P445" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q445" t="str">
+        <v/>
+      </c>
+      <c r="R445" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S445" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>T260904-00026</v>
+      </c>
+      <c r="B446" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C446" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D446" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E446" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F446" t="str">
+        <v/>
+      </c>
+      <c r="G446">
+        <v>0</v>
+      </c>
+      <c r="H446" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="I446" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="J446" t="str">
+        <v>2026-09-04 21:00</v>
+      </c>
+      <c r="K446" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L446">
+        <v>1</v>
+      </c>
+      <c r="M446" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N446" t="str">
+        <v>2026-09-04 19:33:14</v>
+      </c>
+      <c r="O446" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P446" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q446" t="str">
+        <v/>
+      </c>
+      <c r="R446" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S446" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>T260904-00025</v>
+      </c>
+      <c r="B447" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C447" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D447" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E447" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F447" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="G447">
+        <v>1</v>
+      </c>
+      <c r="H447" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="I447" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="J447" t="str">
+        <v>2026-09-04 22:00</v>
+      </c>
+      <c r="K447" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L447">
+        <v>1</v>
+      </c>
+      <c r="M447" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N447" t="str">
+        <v>2026-09-04 19:32:56</v>
+      </c>
+      <c r="O447" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P447" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q447" t="str">
+        <v/>
+      </c>
+      <c r="R447" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S447" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>T260904-00024</v>
+      </c>
+      <c r="B448" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C448" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D448" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E448" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F448" t="str">
+        <v/>
+      </c>
+      <c r="G448">
+        <v>0</v>
+      </c>
+      <c r="H448" t="str">
+        <v>진주FDC</v>
+      </c>
+      <c r="I448" t="str">
+        <v>경상남도 진주시 지수면 승산리 163-1(가운데 동) 진주FDC</v>
+      </c>
+      <c r="J448" t="str">
+        <v>2026-09-04 23:00</v>
+      </c>
+      <c r="K448" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L448">
+        <v>1</v>
+      </c>
+      <c r="M448" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N448" t="str">
+        <v>2026-09-04 19:32:37</v>
+      </c>
+      <c r="O448" s="1">
+        <v>310000</v>
+      </c>
+      <c r="P448" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q448" t="str">
+        <v/>
+      </c>
+      <c r="R448" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S448" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>T260904-00023</v>
+      </c>
+      <c r="B449" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C449" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D449" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E449" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F449" t="str">
+        <v/>
+      </c>
+      <c r="G449">
+        <v>0</v>
+      </c>
+      <c r="H449" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="I449" t="str">
+        <v>인천 검단구 오류동 1653-2 인천FDC</v>
+      </c>
+      <c r="J449" t="str">
+        <v>2026-09-04 21:00</v>
+      </c>
+      <c r="K449" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L449">
+        <v>1</v>
+      </c>
+      <c r="M449" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N449" t="str">
+        <v>2026-09-04 19:32:22</v>
+      </c>
+      <c r="O449" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P449" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q449" t="str">
+        <v/>
+      </c>
+      <c r="R449" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S449" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>T260904-00022</v>
+      </c>
+      <c r="B450" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C450" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D450" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E450" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F450" t="str">
+        <v>원주FDC(신규)</v>
+      </c>
+      <c r="G450">
+        <v>1</v>
+      </c>
+      <c r="H450" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="I450" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="J450" t="str">
+        <v>2026-09-04 22:00</v>
+      </c>
+      <c r="K450" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L450">
+        <v>1</v>
+      </c>
+      <c r="M450" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N450" t="str">
+        <v>2026-09-04 19:32:07</v>
+      </c>
+      <c r="O450" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P450" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q450" t="str">
+        <v/>
+      </c>
+      <c r="R450" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S450" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>T260904-00021</v>
+      </c>
+      <c r="B451" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C451" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D451" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E451" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F451" t="str">
+        <v>창원FDC</v>
+      </c>
+      <c r="G451">
+        <v>1</v>
+      </c>
+      <c r="H451" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="I451" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="J451" t="str">
+        <v>2026-09-04 23:00</v>
+      </c>
+      <c r="K451" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L451">
+        <v>1</v>
+      </c>
+      <c r="M451" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N451" t="str">
+        <v>2026-09-04 19:31:41</v>
+      </c>
+      <c r="O451" s="1">
+        <v>590000</v>
+      </c>
+      <c r="P451" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q451" t="str">
+        <v/>
+      </c>
+      <c r="R451" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S451" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>T260904-00020</v>
+      </c>
+      <c r="B452" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C452" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D452" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E452" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F452" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="G452">
+        <v>1</v>
+      </c>
+      <c r="H452" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="I452" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="J452" t="str">
+        <v>2026-09-04 22:00</v>
+      </c>
+      <c r="K452" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L452">
+        <v>1</v>
+      </c>
+      <c r="M452" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N452" t="str">
+        <v>2026-09-04 19:31:18</v>
+      </c>
+      <c r="O452" s="1">
+        <v>370000</v>
+      </c>
+      <c r="P452" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q452" t="str">
+        <v/>
+      </c>
+      <c r="R452" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S452" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>T260904-00019</v>
+      </c>
+      <c r="B453" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C453" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D453" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E453" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F453" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="G453">
+        <v>1</v>
+      </c>
+      <c r="H453" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="I453" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="J453" t="str">
+        <v>2026-09-04 23:00</v>
+      </c>
+      <c r="K453" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L453">
+        <v>1</v>
+      </c>
+      <c r="M453" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N453" t="str">
+        <v>2026-09-04 19:30:59</v>
+      </c>
+      <c r="O453" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P453" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q453" t="str">
+        <v/>
+      </c>
+      <c r="R453" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S453" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>T260904-00018</v>
+      </c>
+      <c r="B454" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C454" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D454" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E454" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F454" t="str">
+        <v/>
+      </c>
+      <c r="G454">
+        <v>0</v>
+      </c>
+      <c r="H454" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="I454" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="J454" t="str">
+        <v>2026-09-04 21:00</v>
+      </c>
+      <c r="K454" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L454">
+        <v>1</v>
+      </c>
+      <c r="M454" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N454" t="str">
+        <v>2026-09-04 19:30:34</v>
+      </c>
+      <c r="O454" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P454" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q454" t="str">
+        <v/>
+      </c>
+      <c r="R454" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S454" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>T260904-00017</v>
+      </c>
+      <c r="B455" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C455" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D455" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E455" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F455" t="str">
+        <v>구미FDC(신규)</v>
+      </c>
+      <c r="G455">
+        <v>1</v>
+      </c>
+      <c r="H455" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="I455" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="J455" t="str">
+        <v>2026-09-04 23:00</v>
+      </c>
+      <c r="K455" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L455">
+        <v>1</v>
+      </c>
+      <c r="M455" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N455" t="str">
+        <v>2026-09-04 19:30:19</v>
+      </c>
+      <c r="O455" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P455" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q455" t="str">
+        <v/>
+      </c>
+      <c r="R455" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S455" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>T260904-00016</v>
+      </c>
+      <c r="B456" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C456" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D456" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E456" t="str">
+        <v>2026-09-04 19:00</v>
+      </c>
+      <c r="F456" t="str">
+        <v/>
+      </c>
+      <c r="G456">
+        <v>0</v>
+      </c>
+      <c r="H456" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="I456" t="str">
+        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="J456" t="str">
+        <v>2026-09-04 22:00</v>
+      </c>
+      <c r="K456" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L456">
+        <v>1</v>
+      </c>
+      <c r="M456" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N456" t="str">
+        <v>2026-09-04 19:29:59</v>
+      </c>
+      <c r="O456" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P456" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q456" t="str">
+        <v/>
+      </c>
+      <c r="R456" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S456" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>T260904-00015</v>
+      </c>
+      <c r="B457" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C457" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D457" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E457" t="str">
+        <v>2026-09-04 16:50</v>
+      </c>
+      <c r="F457" t="str">
+        <v/>
+      </c>
+      <c r="G457">
+        <v>0</v>
+      </c>
+      <c r="H457" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="I457" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="J457" t="str">
+        <v>2026-09-04 17:50</v>
+      </c>
+      <c r="K457" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L457">
+        <v>1</v>
+      </c>
+      <c r="M457" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N457" t="str">
+        <v>2026-09-04 16:49:46</v>
+      </c>
+      <c r="O457" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P457" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q457" t="str">
+        <v/>
+      </c>
+      <c r="R457" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S457" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>T260904-00014</v>
+      </c>
+      <c r="B458" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C458" t="str">
+        <v>화성FDC</v>
+      </c>
+      <c r="D458" t="str">
+        <v>경기 화성시 장안면 3.1만세로 506-21 화성FDC</v>
+      </c>
+      <c r="E458" t="str">
+        <v>2026-09-04 13:50</v>
+      </c>
+      <c r="F458" t="str">
+        <v/>
+      </c>
+      <c r="G458">
+        <v>0</v>
+      </c>
+      <c r="H458" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="I458" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="J458" t="str">
+        <v>2026-09-04 15:50</v>
+      </c>
+      <c r="K458" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L458">
+        <v>1</v>
+      </c>
+      <c r="M458" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N458" t="str">
+        <v>2026-09-04 16:49:20</v>
+      </c>
+      <c r="O458" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P458" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q458" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="R458" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S458" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>T260904-00013</v>
+      </c>
+      <c r="B459" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C459" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="D459" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="E459" t="str">
+        <v>2026-09-04 11:00</v>
+      </c>
+      <c r="F459" t="str">
+        <v/>
+      </c>
+      <c r="G459">
+        <v>0</v>
+      </c>
+      <c r="H459" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I459" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J459" t="str">
+        <v>2026-09-04 13:50</v>
+      </c>
+      <c r="K459" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L459">
+        <v>1</v>
+      </c>
+      <c r="M459" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N459" t="str">
+        <v>2026-09-04 16:48:41</v>
+      </c>
+      <c r="O459" s="1">
+        <v>160000</v>
+      </c>
+      <c r="P459" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q459" t="str">
+        <v>거래처비용청구(7대)</v>
+      </c>
+      <c r="R459" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S459" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>T260904-00012</v>
+      </c>
+      <c r="B460" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C460" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D460" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E460" t="str">
+        <v>2026-09-04 14:50</v>
+      </c>
+      <c r="F460" t="str">
+        <v/>
+      </c>
+      <c r="G460">
+        <v>0</v>
+      </c>
+      <c r="H460" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I460" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J460" t="str">
+        <v>2026-09-04 15:50</v>
+      </c>
+      <c r="K460" t="str">
+        <v>1톤 기타차량</v>
+      </c>
+      <c r="L460">
+        <v>1</v>
+      </c>
+      <c r="M460" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N460" t="str">
+        <v>2026-09-04 16:47:48</v>
+      </c>
+      <c r="O460" s="1">
+        <v>55000</v>
+      </c>
+      <c r="P460" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q460" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="R460" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S460" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>T260904-00011</v>
+      </c>
+      <c r="B461" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C461" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D461" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E461" t="str">
+        <v>2026-09-04 10:00</v>
+      </c>
+      <c r="F461" t="str">
+        <v/>
+      </c>
+      <c r="G461">
+        <v>0</v>
+      </c>
+      <c r="H461" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I461" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J461" t="str">
+        <v>2026-09-04 13:50</v>
+      </c>
+      <c r="K461" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L461">
+        <v>1</v>
+      </c>
+      <c r="M461" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N461" t="str">
+        <v>2026-09-04 16:46:54</v>
+      </c>
+      <c r="O461" s="1">
+        <v>160000</v>
+      </c>
+      <c r="P461" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q461" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="R461" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S461" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>T260904-00010</v>
+      </c>
+      <c r="B462" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C462" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D462" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E462" t="str">
+        <v>2026-09-04 16:30</v>
+      </c>
+      <c r="F462" t="str">
+        <v/>
+      </c>
+      <c r="G462">
+        <v>0</v>
+      </c>
+      <c r="H462" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I462" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="J462" t="str">
+        <v>2026-09-04 17:30</v>
+      </c>
+      <c r="K462" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L462">
+        <v>1</v>
+      </c>
+      <c r="M462" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N462" t="str">
+        <v>2026-09-04 15:59:08</v>
+      </c>
+      <c r="O462" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P462" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q462" t="str">
+        <v/>
+      </c>
+      <c r="R462" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S462" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>T260904-00009</v>
+      </c>
+      <c r="B463" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C463" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D463" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E463" t="str">
+        <v>2026-09-04 12:20</v>
+      </c>
+      <c r="F463" t="str">
+        <v/>
+      </c>
+      <c r="G463">
+        <v>0</v>
+      </c>
+      <c r="H463" t="str">
+        <v>인천 하이마트 물류</v>
+      </c>
+      <c r="I463" t="str">
+        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
+      </c>
+      <c r="J463" t="str">
+        <v>2026-09-04 14:00</v>
+      </c>
+      <c r="K463" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L463">
+        <v>1</v>
+      </c>
+      <c r="M463" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N463" t="str">
+        <v>2026-09-04 11:55:28</v>
+      </c>
+      <c r="O463" s="1">
+        <v>250000</v>
+      </c>
+      <c r="P463" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q463" t="str">
+        <v>일코전자 인천 하이마트 물류</v>
+      </c>
+      <c r="R463" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S463" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>T260904-00008</v>
+      </c>
+      <c r="B464" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C464" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D464" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E464" t="str">
+        <v>2026-09-04 10:40</v>
+      </c>
+      <c r="F464" t="str">
+        <v/>
+      </c>
+      <c r="G464">
+        <v>0</v>
+      </c>
+      <c r="H464" t="str">
+        <v>인천 하이마트 물류</v>
+      </c>
+      <c r="I464" t="str">
+        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
+      </c>
+      <c r="J464" t="str">
+        <v>2026-09-04 13:00</v>
+      </c>
+      <c r="K464" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L464">
+        <v>1</v>
+      </c>
+      <c r="M464" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N464" t="str">
+        <v>2026-09-04 10:28:30</v>
+      </c>
+      <c r="O464" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P464" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q464" t="str">
+        <v>일코전자 인천 하이마트 물류</v>
+      </c>
+      <c r="R464" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S464" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>T260904-00007</v>
+      </c>
+      <c r="B465" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C465" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D465" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E465" t="str">
+        <v>2026-09-04 10:10</v>
+      </c>
+      <c r="F465" t="str">
+        <v/>
+      </c>
+      <c r="G465">
+        <v>0</v>
+      </c>
+      <c r="H465" t="str">
+        <v>화성 하이마트 물류</v>
+      </c>
+      <c r="I465" t="str">
+        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 물류</v>
+      </c>
+      <c r="J465" t="str">
+        <v>2026-09-04 12:00</v>
+      </c>
+      <c r="K465" t="str">
+        <v>3.5톤 카고</v>
+      </c>
+      <c r="L465">
+        <v>1</v>
+      </c>
+      <c r="M465" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N465" t="str">
+        <v>2026-09-04 09:43:35</v>
+      </c>
+      <c r="O465" s="1">
+        <v>130000</v>
+      </c>
+      <c r="P465" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q465" t="str">
+        <v>일코전자 화성 하이마트 물류</v>
+      </c>
+      <c r="R465" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S465" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>T260904-00006</v>
+      </c>
+      <c r="B466" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C466" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D466" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E466" t="str">
+        <v>2026-09-04 10:00</v>
+      </c>
+      <c r="F466" t="str">
+        <v/>
+      </c>
+      <c r="G466">
+        <v>0</v>
+      </c>
+      <c r="H466" t="str">
+        <v>이천 하이마트 물류</v>
+      </c>
+      <c r="I466" t="str">
+        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
+      </c>
+      <c r="J466" t="str">
+        <v>2026-09-04 12:00</v>
+      </c>
+      <c r="K466" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L466">
+        <v>1</v>
+      </c>
+      <c r="M466" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N466" t="str">
+        <v>2026-09-04 09:43:01</v>
+      </c>
+      <c r="O466" s="1">
+        <v>80000</v>
+      </c>
+      <c r="P466" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q466" t="str">
+        <v>일코전자 이천 하이마트 물류</v>
+      </c>
+      <c r="R466" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S466" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>T260904-00005</v>
+      </c>
+      <c r="B467" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C467" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D467" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E467" t="str">
+        <v>2026-09-04 10:00</v>
+      </c>
+      <c r="F467" t="str">
+        <v/>
+      </c>
+      <c r="G467">
+        <v>0</v>
+      </c>
+      <c r="H467" t="str">
+        <v>이천 하이마트 물류</v>
+      </c>
+      <c r="I467" t="str">
+        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
+      </c>
+      <c r="J467" t="str">
+        <v>2026-09-04 12:00</v>
+      </c>
+      <c r="K467" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L467">
+        <v>1</v>
+      </c>
+      <c r="M467" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N467" t="str">
+        <v>2026-09-04 09:19:08</v>
+      </c>
+      <c r="O467" s="1">
+        <v>170000</v>
+      </c>
+      <c r="P467" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q467" t="str">
+        <v>일코전자 이천 하이마트 물류</v>
+      </c>
+      <c r="R467" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S467" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>T260904-00004</v>
+      </c>
+      <c r="B468" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C468" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D468" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E468" t="str">
+        <v>2026-09-04 10:00</v>
+      </c>
+      <c r="F468" t="str">
+        <v/>
+      </c>
+      <c r="G468">
+        <v>0</v>
+      </c>
+      <c r="H468" t="str">
+        <v>양산 하이마트 물류</v>
+      </c>
+      <c r="I468" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
+      </c>
+      <c r="J468" t="str">
+        <v>2026-09-04 13:00</v>
+      </c>
+      <c r="K468" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L468">
+        <v>1</v>
+      </c>
+      <c r="M468" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N468" t="str">
+        <v>2026-09-04 09:18:25</v>
+      </c>
+      <c r="O468" s="1">
+        <v>470000</v>
+      </c>
+      <c r="P468" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q468" t="str">
+        <v>일코전자 양산 하이마트 물류</v>
+      </c>
+      <c r="R468" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S468" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>T260904-00003</v>
+      </c>
+      <c r="B469" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C469" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D469" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E469" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="F469" t="str">
+        <v/>
+      </c>
+      <c r="G469">
+        <v>0</v>
+      </c>
+      <c r="H469" t="str">
+        <v>광주 하이마트 물류</v>
+      </c>
+      <c r="I469" t="str">
+        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
+      </c>
+      <c r="J469" t="str">
+        <v>2026-09-04 01:00</v>
+      </c>
+      <c r="K469" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L469">
+        <v>1</v>
+      </c>
+      <c r="M469" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N469" t="str">
+        <v>2026-09-04 09:17:40</v>
+      </c>
+      <c r="O469" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P469" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q469" t="str">
+        <v>일코전자 광주 하이마트 물류</v>
+      </c>
+      <c r="R469" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S469" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>T260904-00002</v>
+      </c>
+      <c r="B470" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C470" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D470" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E470" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="F470" t="str">
+        <v/>
+      </c>
+      <c r="G470">
+        <v>0</v>
+      </c>
+      <c r="H470" t="str">
+        <v>파주 하이마트 물류</v>
+      </c>
+      <c r="I470" t="str">
+        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
+      </c>
+      <c r="J470" t="str">
+        <v>2026-09-04 11:00</v>
+      </c>
+      <c r="K470" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L470">
+        <v>1</v>
+      </c>
+      <c r="M470" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N470" t="str">
+        <v>2026-09-04 09:17:14</v>
+      </c>
+      <c r="O470" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P470" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q470" t="str">
+        <v>일코전자 파주 하이마트 물류</v>
+      </c>
+      <c r="R470" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S470" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>T260904-00001</v>
+      </c>
+      <c r="B471" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C471" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D471" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E471" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="F471" t="str">
+        <v/>
+      </c>
+      <c r="G471">
+        <v>0</v>
+      </c>
+      <c r="H471" t="str">
+        <v>마산 하이마트 물류</v>
+      </c>
+      <c r="I471" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
+      </c>
+      <c r="J471" t="str">
+        <v>2026-09-04 13:00</v>
+      </c>
+      <c r="K471" t="str">
+        <v>5톤축 카고</v>
+      </c>
+      <c r="L471">
+        <v>1</v>
+      </c>
+      <c r="M471" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N471" t="str">
+        <v>2026-09-04 09:16:39</v>
+      </c>
+      <c r="O471" s="1">
+        <v>410000</v>
+      </c>
+      <c r="P471" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q471" t="str">
+        <v>일코 마산 하이마트 물류</v>
+      </c>
+      <c r="R471" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S471" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>T260903-00029</v>
+      </c>
+      <c r="B472" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C472" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D472" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E472" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F472" t="str">
+        <v>시흥ACP,인천ACP</v>
+      </c>
+      <c r="G472">
+        <v>2</v>
+      </c>
+      <c r="H472" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="I472" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="J472" t="str">
+        <v>2026-09-04 08:00</v>
+      </c>
+      <c r="K472" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L472">
+        <v>1</v>
+      </c>
+      <c r="M472" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N472" t="str">
+        <v>2026-09-03 18:24:00</v>
+      </c>
+      <c r="O472" s="1">
+        <v>230000</v>
+      </c>
+      <c r="P472" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q472" t="str">
+        <v/>
+      </c>
+      <c r="R472" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S472" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>T260903-00028</v>
+      </c>
+      <c r="B473" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C473" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D473" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E473" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F473" t="str">
+        <v>대전중구ACP,군산ACP</v>
+      </c>
+      <c r="G473">
+        <v>2</v>
+      </c>
+      <c r="H473" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="I473" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="J473" t="str">
+        <v>2026-09-04 07:00</v>
+      </c>
+      <c r="K473" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L473">
+        <v>1</v>
+      </c>
+      <c r="M473" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N473" t="str">
+        <v>2026-09-03 18:23:24</v>
+      </c>
+      <c r="O473" s="1">
+        <v>300000</v>
+      </c>
+      <c r="P473" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q473" t="str">
+        <v/>
+      </c>
+      <c r="R473" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S473" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>T260903-00027</v>
+      </c>
+      <c r="B474" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C474" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D474" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E474" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F474" t="str">
+        <v>안성ACP,용인ACP,화성ACP</v>
+      </c>
+      <c r="G474">
+        <v>3</v>
+      </c>
+      <c r="H474" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="I474" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="J474" t="str">
+        <v>2026-09-03 23:00</v>
+      </c>
+      <c r="K474" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L474">
+        <v>1</v>
+      </c>
+      <c r="M474" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N474" t="str">
+        <v>2026-09-03 18:22:50</v>
+      </c>
+      <c r="O474" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P474" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q474" t="str">
+        <v/>
+      </c>
+      <c r="R474" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S474" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>T260903-00026</v>
+      </c>
+      <c r="B475" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C475" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D475" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E475" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F475" t="str">
+        <v/>
+      </c>
+      <c r="G475">
+        <v>0</v>
+      </c>
+      <c r="H475" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="I475" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="J475" t="str">
+        <v>2026-09-03 21:00</v>
+      </c>
+      <c r="K475" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L475">
+        <v>1</v>
+      </c>
+      <c r="M475" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N475" t="str">
+        <v>2026-09-03 18:22:08</v>
+      </c>
+      <c r="O475" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P475" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q475" t="str">
+        <v/>
+      </c>
+      <c r="R475" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S475" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>T260903-00025</v>
+      </c>
+      <c r="B476" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C476" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D476" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E476" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F476" t="str">
+        <v/>
+      </c>
+      <c r="G476">
+        <v>0</v>
+      </c>
+      <c r="H476" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="I476" t="str">
+        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
+      </c>
+      <c r="J476" t="str">
+        <v>2026-09-03 22:00</v>
+      </c>
+      <c r="K476" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L476">
+        <v>1</v>
+      </c>
+      <c r="M476" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N476" t="str">
+        <v>2026-09-03 18:21:51</v>
+      </c>
+      <c r="O476" s="1">
+        <v>230000</v>
+      </c>
+      <c r="P476" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q476" t="str">
+        <v/>
+      </c>
+      <c r="R476" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S476" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>T260903-00024</v>
+      </c>
+      <c r="B477" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C477" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D477" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E477" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F477" t="str">
+        <v/>
+      </c>
+      <c r="G477">
+        <v>0</v>
+      </c>
+      <c r="H477" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="I477" t="str">
+        <v>인천 검단구 오류동 1653-2 인천FDC</v>
+      </c>
+      <c r="J477" t="str">
+        <v>2026-09-03 21:00</v>
+      </c>
+      <c r="K477" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L477">
+        <v>1</v>
+      </c>
+      <c r="M477" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N477" t="str">
+        <v>2026-09-03 18:21:35</v>
+      </c>
+      <c r="O477" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P477" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q477" t="str">
+        <v/>
+      </c>
+      <c r="R477" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S477" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>T260903-00023</v>
+      </c>
+      <c r="B478" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C478" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D478" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E478" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F478" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="G478">
+        <v>1</v>
+      </c>
+      <c r="H478" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="I478" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="J478" t="str">
+        <v>2026-09-03 22:00</v>
+      </c>
+      <c r="K478" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L478">
+        <v>1</v>
+      </c>
+      <c r="M478" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N478" t="str">
+        <v>2026-09-03 18:21:18</v>
+      </c>
+      <c r="O478" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P478" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q478" t="str">
+        <v/>
+      </c>
+      <c r="R478" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S478" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>T260903-00022</v>
+      </c>
+      <c r="B479" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C479" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D479" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E479" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F479" t="str">
+        <v>원주FDC(신규)</v>
+      </c>
+      <c r="G479">
+        <v>1</v>
+      </c>
+      <c r="H479" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="I479" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="J479" t="str">
+        <v>2026-09-03 22:00</v>
+      </c>
+      <c r="K479" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L479">
+        <v>1</v>
+      </c>
+      <c r="M479" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N479" t="str">
+        <v>2026-09-03 18:20:56</v>
+      </c>
+      <c r="O479" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P479" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q479" t="str">
+        <v/>
+      </c>
+      <c r="R479" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S479" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>T260903-00021</v>
+      </c>
+      <c r="B480" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C480" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D480" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E480" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F480" t="str">
+        <v>진주FDC,창원FDC</v>
+      </c>
+      <c r="G480">
+        <v>2</v>
+      </c>
+      <c r="H480" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="I480" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="J480" t="str">
+        <v>2026-09-03 23:00</v>
+      </c>
+      <c r="K480" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L480">
+        <v>1</v>
+      </c>
+      <c r="M480" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N480" t="str">
+        <v>2026-09-03 18:20:35</v>
+      </c>
+      <c r="O480" s="1">
+        <v>730000</v>
+      </c>
+      <c r="P480" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q480" t="str">
+        <v/>
+      </c>
+      <c r="R480" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S480" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>T260903-00020</v>
+      </c>
+      <c r="B481" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C481" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D481" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E481" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F481" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="G481">
+        <v>1</v>
+      </c>
+      <c r="H481" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="I481" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="J481" t="str">
+        <v>2026-09-03 22:00</v>
+      </c>
+      <c r="K481" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L481">
+        <v>1</v>
+      </c>
+      <c r="M481" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N481" t="str">
+        <v>2026-09-03 18:20:07</v>
+      </c>
+      <c r="O481" s="1">
+        <v>370000</v>
+      </c>
+      <c r="P481" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q481" t="str">
+        <v/>
+      </c>
+      <c r="R481" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S481" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>T260903-00019</v>
+      </c>
+      <c r="B482" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C482" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D482" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E482" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F482" t="str">
+        <v/>
+      </c>
+      <c r="G482">
+        <v>0</v>
+      </c>
+      <c r="H482" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="I482" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="J482" t="str">
+        <v>2026-09-03 23:00</v>
+      </c>
+      <c r="K482" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L482">
+        <v>1</v>
+      </c>
+      <c r="M482" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N482" t="str">
+        <v>2026-09-03 18:19:48</v>
+      </c>
+      <c r="O482" s="1">
+        <v>420000</v>
+      </c>
+      <c r="P482" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q482" t="str">
+        <v/>
+      </c>
+      <c r="R482" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S482" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>T260903-00018</v>
+      </c>
+      <c r="B483" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C483" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D483" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E483" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F483" t="str">
+        <v/>
+      </c>
+      <c r="G483">
+        <v>0</v>
+      </c>
+      <c r="H483" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="I483" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="J483" t="str">
+        <v>2026-09-03 21:00</v>
+      </c>
+      <c r="K483" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L483">
+        <v>1</v>
+      </c>
+      <c r="M483" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N483" t="str">
+        <v>2026-09-03 18:19:30</v>
+      </c>
+      <c r="O483" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P483" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q483" t="str">
+        <v/>
+      </c>
+      <c r="R483" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S483" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>T260903-00017</v>
+      </c>
+      <c r="B484" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C484" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D484" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E484" t="str">
+        <v>2026-09-03 19:00</v>
+      </c>
+      <c r="F484" t="str">
+        <v>구미FDC(신규)</v>
+      </c>
+      <c r="G484">
+        <v>1</v>
+      </c>
+      <c r="H484" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="I484" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="J484" t="str">
+        <v>2026-09-03 23:00</v>
+      </c>
+      <c r="K484" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L484">
+        <v>1</v>
+      </c>
+      <c r="M484" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N484" t="str">
+        <v>2026-09-03 18:19:12</v>
+      </c>
+      <c r="O484" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P484" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q484" t="str">
+        <v/>
+      </c>
+      <c r="R484" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S484" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>T260903-00016</v>
+      </c>
+      <c r="B485" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C485" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D485" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E485" t="str">
+        <v>2026-09-03 18:00</v>
+      </c>
+      <c r="F485" t="str">
+        <v/>
+      </c>
+      <c r="G485">
+        <v>0</v>
+      </c>
+      <c r="H485" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="I485" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="J485" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="K485" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L485">
+        <v>1</v>
+      </c>
+      <c r="M485" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N485" t="str">
+        <v>2026-09-03 17:43:12</v>
+      </c>
+      <c r="O485" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P485" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q485" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="R485" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S485" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>T260903-00015</v>
+      </c>
+      <c r="B486" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C486" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D486" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E486" t="str">
+        <v>2026-09-03 17:30</v>
+      </c>
+      <c r="F486" t="str">
+        <v/>
+      </c>
+      <c r="G486">
+        <v>0</v>
+      </c>
+      <c r="H486" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="I486" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="J486" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="K486" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L486">
+        <v>1</v>
+      </c>
+      <c r="M486" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N486" t="str">
+        <v>2026-09-03 17:10:21</v>
+      </c>
+      <c r="O486" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P486" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q486" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="R486" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S486" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>T260903-00014</v>
+      </c>
+      <c r="B487" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C487" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D487" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E487" t="str">
+        <v>2026-09-03 17:30</v>
+      </c>
+      <c r="F487" t="str">
+        <v/>
+      </c>
+      <c r="G487">
+        <v>0</v>
+      </c>
+      <c r="H487" t="str">
+        <v>공주 하이마트 물류</v>
+      </c>
+      <c r="I487" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="J487" t="str">
+        <v>2026-09-04 21:00</v>
+      </c>
+      <c r="K487" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L487">
+        <v>1</v>
+      </c>
+      <c r="M487" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N487" t="str">
+        <v>2026-09-03 17:09:57</v>
+      </c>
+      <c r="O487" s="1">
+        <v>220000</v>
+      </c>
+      <c r="P487" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q487" t="str">
+        <v>일코전자 공주 하이마트 물류</v>
+      </c>
+      <c r="R487" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S487" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>T260903-00013</v>
+      </c>
+      <c r="B488" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C488" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="D488" t="str">
+        <v>충남 아산시 음봉면 월랑리 440 천안FDC</v>
+      </c>
+      <c r="E488" t="str">
+        <v>2026-09-03 21:30</v>
+      </c>
+      <c r="F488" t="str">
+        <v/>
+      </c>
+      <c r="G488">
+        <v>0</v>
+      </c>
+      <c r="H488" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="I488" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="J488" t="str">
+        <v>2026-09-03 22:30</v>
+      </c>
+      <c r="K488" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L488">
+        <v>1</v>
+      </c>
+      <c r="M488" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N488" t="str">
+        <v>2026-09-03 16:23:31</v>
+      </c>
+      <c r="O488" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P488" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q488" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="R488" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S488" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>T260903-00012</v>
+      </c>
+      <c r="B489" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C489" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D489" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E489" t="str">
+        <v>2026-09-03 16:30</v>
+      </c>
+      <c r="F489" t="str">
+        <v/>
+      </c>
+      <c r="G489">
+        <v>0</v>
+      </c>
+      <c r="H489" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I489" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="J489" t="str">
+        <v>2026-09-03 17:30</v>
+      </c>
+      <c r="K489" t="str">
+        <v>1톤 카고/윙</v>
+      </c>
+      <c r="L489">
+        <v>1</v>
+      </c>
+      <c r="M489" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N489" t="str">
+        <v>2026-09-03 15:51:43</v>
+      </c>
+      <c r="O489" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P489" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q489" t="str">
+        <v/>
+      </c>
+      <c r="R489" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S489" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>T260903-00011</v>
+      </c>
+      <c r="B490" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C490" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D490" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E490" t="str">
+        <v>2026-09-03 17:30</v>
+      </c>
+      <c r="F490" t="str">
+        <v/>
+      </c>
+      <c r="G490">
+        <v>0</v>
+      </c>
+      <c r="H490" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="I490" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="J490" t="str">
+        <v>2026-09-03 18:30</v>
+      </c>
+      <c r="K490" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L490">
+        <v>1</v>
+      </c>
+      <c r="M490" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N490" t="str">
+        <v>2026-09-03 15:32:57</v>
+      </c>
+      <c r="O490" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P490" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q490" t="str">
+        <v/>
+      </c>
+      <c r="R490" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S490" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>T260903-00010</v>
+      </c>
+      <c r="B491" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C491" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="D491" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 821 곤지암FDC</v>
+      </c>
+      <c r="E491" t="str">
+        <v>2026-09-03 21:30</v>
+      </c>
+      <c r="F491" t="str">
+        <v/>
+      </c>
+      <c r="G491">
+        <v>0</v>
+      </c>
+      <c r="H491" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="I491" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="J491" t="str">
+        <v>2026-09-04 08:30</v>
+      </c>
+      <c r="K491" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L491">
+        <v>1</v>
+      </c>
+      <c r="M491" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N491" t="str">
+        <v>2026-09-03 15:32:28</v>
+      </c>
+      <c r="O491" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P491" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q491" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="R491" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S491" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>T260903-00009</v>
+      </c>
+      <c r="B492" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C492" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="D492" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5 김포FDC</v>
+      </c>
+      <c r="E492" t="str">
+        <v>2026-09-03 09:00</v>
+      </c>
+      <c r="F492" t="str">
+        <v/>
+      </c>
+      <c r="G492">
+        <v>0</v>
+      </c>
+      <c r="H492" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="I492" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="J492" t="str">
+        <v>2026-09-03 11:30</v>
+      </c>
+      <c r="K492" t="str">
+        <v>5톤 카고</v>
+      </c>
+      <c r="L492">
+        <v>1</v>
+      </c>
+      <c r="M492" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N492" t="str">
+        <v>2026-09-03 15:31:34</v>
+      </c>
+      <c r="O492" s="1">
+        <v>250000</v>
+      </c>
+      <c r="P492" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q492" t="str">
+        <v>반품회수</v>
+      </c>
+      <c r="R492" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S492" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>T260903-00008</v>
+      </c>
+      <c r="B493" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C493" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="D493" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="E493" t="str">
+        <v>2026-09-03 11:00</v>
+      </c>
+      <c r="F493" t="str">
+        <v/>
+      </c>
+      <c r="G493">
+        <v>0</v>
+      </c>
+      <c r="H493" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I493" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J493" t="str">
+        <v>2026-09-03 13:30</v>
+      </c>
+      <c r="K493" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L493">
+        <v>1</v>
+      </c>
+      <c r="M493" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N493" t="str">
+        <v>2026-09-03 15:30:52</v>
+      </c>
+      <c r="O493" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P493" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q493" t="str">
+        <v>거래처비용청구(3대)</v>
+      </c>
+      <c r="R493" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S493" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>T260903-00007</v>
+      </c>
+      <c r="B494" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C494" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D494" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E494" t="str">
+        <v>2026-09-03 14:30</v>
+      </c>
+      <c r="F494" t="str">
+        <v/>
+      </c>
+      <c r="G494">
+        <v>0</v>
+      </c>
+      <c r="H494" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I494" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J494" t="str">
+        <v>2026-09-03 15:30</v>
+      </c>
+      <c r="K494" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L494">
+        <v>1</v>
+      </c>
+      <c r="M494" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N494" t="str">
+        <v>2026-09-03 15:30:00</v>
+      </c>
+      <c r="O494" s="1">
+        <v>70000</v>
+      </c>
+      <c r="P494" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q494" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="R494" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S494" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>T260903-00006</v>
+      </c>
+      <c r="B495" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C495" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D495" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E495" t="str">
+        <v>2026-09-03 10:00</v>
+      </c>
+      <c r="F495" t="str">
+        <v/>
+      </c>
+      <c r="G495">
+        <v>0</v>
+      </c>
+      <c r="H495" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I495" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J495" t="str">
+        <v>2026-09-03 13:30</v>
+      </c>
+      <c r="K495" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L495">
+        <v>1</v>
+      </c>
+      <c r="M495" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N495" t="str">
+        <v>2026-09-03 15:29:14</v>
+      </c>
+      <c r="O495" s="1">
+        <v>160000</v>
+      </c>
+      <c r="P495" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q495" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="R495" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S495" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>T260903-00005</v>
+      </c>
+      <c r="B496" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C496" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D496" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E496" t="str">
+        <v>2026-09-03 13:50</v>
+      </c>
+      <c r="F496" t="str">
+        <v/>
+      </c>
+      <c r="G496">
+        <v>0</v>
+      </c>
+      <c r="H496" t="str">
+        <v>펠리체산후조리원하이얼</v>
+      </c>
+      <c r="I496" t="str">
+        <v>경기 화성시 만세구 꽃내음1길 19-22 펠리체산후조리원 하이얼</v>
+      </c>
+      <c r="J496" t="str">
+        <v>2026-09-03 16:00</v>
+      </c>
+      <c r="K496" t="str">
+        <v>1.5톤 카고</v>
+      </c>
+      <c r="L496">
+        <v>1</v>
+      </c>
+      <c r="M496" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N496" t="str">
+        <v>2026-09-03 13:37:58</v>
+      </c>
+      <c r="O496" s="1">
+        <v>110000</v>
+      </c>
+      <c r="P496" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q496" t="str">
+        <v/>
+      </c>
+      <c r="R496" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S496" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>T260903-00004</v>
+      </c>
+      <c r="B497" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C497" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D497" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E497" t="str">
+        <v>2026-09-03 16:00</v>
+      </c>
+      <c r="F497" t="str">
+        <v/>
+      </c>
+      <c r="G497">
+        <v>0</v>
+      </c>
+      <c r="H497" t="str">
+        <v>광주 하이마트 물류</v>
+      </c>
+      <c r="I497" t="str">
+        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
+      </c>
+      <c r="J497" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="K497" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L497">
+        <v>1</v>
+      </c>
+      <c r="M497" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N497" t="str">
+        <v>2026-09-03 13:14:56</v>
+      </c>
+      <c r="O497" s="1">
+        <v>400000</v>
+      </c>
+      <c r="P497" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q497" t="str">
+        <v>일코전자 광주 하이마트 물류</v>
+      </c>
+      <c r="R497" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S497" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
+        <v>T260903-00003</v>
+      </c>
+      <c r="B498" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C498" t="str">
+        <v>위니온 안성HUB</v>
+      </c>
+      <c r="D498" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E498" t="str">
+        <v>2026-09-03 15:00</v>
+      </c>
+      <c r="F498" t="str">
+        <v/>
+      </c>
+      <c r="G498">
+        <v>0</v>
+      </c>
+      <c r="H498" t="str">
+        <v>대구 하이마트 물류</v>
+      </c>
+      <c r="I498" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="J498" t="str">
+        <v>2026-09-04 09:00</v>
+      </c>
+      <c r="K498" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L498">
+        <v>1</v>
+      </c>
+      <c r="M498" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N498" t="str">
+        <v>2026-09-03 10:24:04</v>
+      </c>
+      <c r="O498" s="1">
+        <v>340000</v>
+      </c>
+      <c r="P498" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q498" t="str">
+        <v>일코전자 대구 하이마트 물류</v>
+      </c>
+      <c r="R498" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S498" t="str">
+        <v>일코전자</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>T260903-00002</v>
+      </c>
+      <c r="B499" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C499" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D499" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E499" t="str">
+        <v>2026-09-03 10:10</v>
+      </c>
+      <c r="F499" t="str">
+        <v/>
+      </c>
+      <c r="G499">
+        <v>0</v>
+      </c>
+      <c r="H499" t="str">
+        <v>마이디어 늘품마루</v>
+      </c>
+      <c r="I499" t="str">
+        <v>경기 이천시 백사면 지읍로 54 지하 2층 33번 도크</v>
+      </c>
+      <c r="J499" t="str">
+        <v>2026-09-03 11:30</v>
+      </c>
+      <c r="K499" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="L499">
+        <v>1</v>
+      </c>
+      <c r="M499" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N499" t="str">
+        <v>2026-09-03 10:23:19</v>
+      </c>
+      <c r="O499" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P499" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q499" t="str">
+        <v>마이디어 늘품마루</v>
+      </c>
+      <c r="R499" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S499" t="str">
+        <v>마이디어</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>T260903-00001</v>
+      </c>
+      <c r="B500" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C500" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D500" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E500" t="str">
+        <v>2026-09-03 09:00</v>
+      </c>
+      <c r="F500" t="str">
+        <v/>
+      </c>
+      <c r="G500">
+        <v>0</v>
+      </c>
+      <c r="H500" t="str">
+        <v>마이디어 늘품마루</v>
+      </c>
+      <c r="I500" t="str">
+        <v>경기 이천시 백사면 지읍로 54 지하 2층 33번 도크</v>
+      </c>
+      <c r="J500" t="str">
+        <v>2026-09-03 11:00</v>
+      </c>
+      <c r="K500" t="str">
+        <v>5톤축 윙바디</v>
+      </c>
+      <c r="L500">
+        <v>1</v>
+      </c>
+      <c r="M500" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N500" t="str">
+        <v>2026-09-03 09:06:29</v>
+      </c>
+      <c r="O500" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P500" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q500" t="str">
+        <v>마이디어 늘품마루</v>
+      </c>
+      <c r="R500" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S500" t="str">
+        <v>마이디어</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>T260902-00030</v>
+      </c>
+      <c r="B501" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C501" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D501" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E501" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F501" t="str">
+        <v>대전중구ACP</v>
+      </c>
+      <c r="G501">
+        <v>1</v>
+      </c>
+      <c r="H501" t="str">
+        <v>대전대덕ACP</v>
+      </c>
+      <c r="I501" t="str">
+        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
+      </c>
+      <c r="J501" t="str">
+        <v>2026-09-03 06:00</v>
+      </c>
+      <c r="K501" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L501">
+        <v>1</v>
+      </c>
+      <c r="M501" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N501" t="str">
+        <v>2026-09-02 19:24:10</v>
+      </c>
+      <c r="O501" s="1">
+        <v>170000</v>
+      </c>
+      <c r="P501" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q501" t="str">
+        <v/>
+      </c>
+      <c r="R501" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S501" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
+        <v>T260902-00029</v>
+      </c>
+      <c r="B502" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C502" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D502" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E502" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F502" t="str">
+        <v>인천ACP</v>
+      </c>
+      <c r="G502">
+        <v>1</v>
+      </c>
+      <c r="H502" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="I502" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="J502" t="str">
+        <v>2026-09-03 07:00</v>
+      </c>
+      <c r="K502" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L502">
+        <v>1</v>
+      </c>
+      <c r="M502" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N502" t="str">
+        <v>2026-09-02 19:23:42</v>
+      </c>
+      <c r="O502" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P502" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q502" t="str">
+        <v/>
+      </c>
+      <c r="R502" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S502" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>T260902-00028</v>
+      </c>
+      <c r="B503" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C503" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D503" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E503" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F503" t="str">
+        <v>이천ACP,원주ACP</v>
+      </c>
+      <c r="G503">
+        <v>2</v>
+      </c>
+      <c r="H503" t="str">
+        <v>춘천ACP</v>
+      </c>
+      <c r="I503" t="str">
+        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
+      </c>
+      <c r="J503" t="str">
+        <v>2026-09-03 06:00</v>
+      </c>
+      <c r="K503" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L503">
+        <v>1</v>
+      </c>
+      <c r="M503" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N503" t="str">
+        <v>2026-09-02 19:23:13</v>
+      </c>
+      <c r="O503" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P503" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q503" t="str">
+        <v/>
+      </c>
+      <c r="R503" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S503" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>T260902-00027</v>
+      </c>
+      <c r="B504" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C504" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D504" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E504" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F504" t="str">
+        <v>군산ACP</v>
+      </c>
+      <c r="G504">
+        <v>1</v>
+      </c>
+      <c r="H504" t="str">
+        <v>전주ACP</v>
+      </c>
+      <c r="I504" t="str">
+        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
+      </c>
+      <c r="J504" t="str">
+        <v>2026-09-03 08:00</v>
+      </c>
+      <c r="K504" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L504">
+        <v>1</v>
+      </c>
+      <c r="M504" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N504" t="str">
+        <v>2026-09-02 19:22:37</v>
+      </c>
+      <c r="O504" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P504" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q504" t="str">
+        <v/>
+      </c>
+      <c r="R504" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S504" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>T260902-00026</v>
+      </c>
+      <c r="B505" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C505" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D505" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E505" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F505" t="str">
+        <v>용인ACP,화성ACP</v>
+      </c>
+      <c r="G505">
+        <v>2</v>
+      </c>
+      <c r="H505" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="I505" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="J505" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K505" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L505">
+        <v>1</v>
+      </c>
+      <c r="M505" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N505" t="str">
+        <v>2026-09-02 19:22:09</v>
+      </c>
+      <c r="O505" s="1">
+        <v>220000</v>
+      </c>
+      <c r="P505" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q505" t="str">
+        <v/>
+      </c>
+      <c r="R505" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S505" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>T260902-00025</v>
+      </c>
+      <c r="B506" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C506" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D506" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E506" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F506" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="G506">
+        <v>1</v>
+      </c>
+      <c r="H506" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="I506" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="J506" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K506" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L506">
+        <v>1</v>
+      </c>
+      <c r="M506" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N506" t="str">
+        <v>2026-09-02 19:21:37</v>
+      </c>
+      <c r="O506" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P506" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q506" t="str">
+        <v/>
+      </c>
+      <c r="R506" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S506" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>T260902-00024</v>
+      </c>
+      <c r="B507" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C507" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D507" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E507" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F507" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="G507">
+        <v>1</v>
+      </c>
+      <c r="H507" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="I507" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="J507" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K507" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L507">
+        <v>1</v>
+      </c>
+      <c r="M507" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N507" t="str">
+        <v>2026-09-02 19:21:17</v>
+      </c>
+      <c r="O507" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P507" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q507" t="str">
+        <v/>
+      </c>
+      <c r="R507" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S507" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>T260902-00023</v>
+      </c>
+      <c r="B508" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C508" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D508" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E508" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F508" t="str">
+        <v>원주FDC(신규)</v>
+      </c>
+      <c r="G508">
+        <v>1</v>
+      </c>
+      <c r="H508" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="I508" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="J508" t="str">
+        <v>2026-09-02 22:00</v>
+      </c>
+      <c r="K508" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L508">
+        <v>1</v>
+      </c>
+      <c r="M508" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N508" t="str">
+        <v>2026-09-02 19:20:40</v>
+      </c>
+      <c r="O508" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P508" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q508" t="str">
+        <v/>
+      </c>
+      <c r="R508" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S508" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>T260902-00022</v>
+      </c>
+      <c r="B509" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C509" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D509" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E509" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F509" t="str">
+        <v>진주FDC,창원FDC</v>
+      </c>
+      <c r="G509">
+        <v>2</v>
+      </c>
+      <c r="H509" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="I509" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="J509" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K509" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L509">
+        <v>1</v>
+      </c>
+      <c r="M509" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N509" t="str">
+        <v>2026-09-02 19:20:16</v>
+      </c>
+      <c r="O509" s="1">
+        <v>730000</v>
+      </c>
+      <c r="P509" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q509" t="str">
+        <v/>
+      </c>
+      <c r="R509" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S509" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>T260902-00021</v>
+      </c>
+      <c r="B510" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C510" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D510" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E510" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F510" t="str">
+        <v/>
+      </c>
+      <c r="G510">
+        <v>0</v>
+      </c>
+      <c r="H510" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="I510" t="str">
+        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
+      </c>
+      <c r="J510" t="str">
+        <v>2026-09-02 21:00</v>
+      </c>
+      <c r="K510" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L510">
+        <v>1</v>
+      </c>
+      <c r="M510" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N510" t="str">
+        <v>2026-09-02 19:19:46</v>
+      </c>
+      <c r="O510" s="1">
+        <v>250000</v>
+      </c>
+      <c r="P510" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q510" t="str">
+        <v/>
+      </c>
+      <c r="R510" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S510" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>T260902-00020</v>
+      </c>
+      <c r="B511" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C511" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D511" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E511" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F511" t="str">
+        <v/>
+      </c>
+      <c r="G511">
+        <v>0</v>
+      </c>
+      <c r="H511" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="I511" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="J511" t="str">
+        <v>2026-09-02 21:00</v>
+      </c>
+      <c r="K511" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L511">
+        <v>1</v>
+      </c>
+      <c r="M511" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N511" t="str">
+        <v>2026-09-02 19:19:30</v>
+      </c>
+      <c r="O511" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P511" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q511" t="str">
+        <v/>
+      </c>
+      <c r="R511" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S511" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
+        <v>T260902-00019</v>
+      </c>
+      <c r="B512" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C512" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D512" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E512" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F512" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="G512">
+        <v>1</v>
+      </c>
+      <c r="H512" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="I512" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="J512" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K512" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L512">
+        <v>1</v>
+      </c>
+      <c r="M512" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N512" t="str">
+        <v>2026-09-02 19:19:13</v>
+      </c>
+      <c r="O512" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P512" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q512" t="str">
+        <v/>
+      </c>
+      <c r="R512" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S512" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>T260902-00018</v>
+      </c>
+      <c r="B513" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C513" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D513" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E513" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F513" t="str">
+        <v/>
+      </c>
+      <c r="G513">
+        <v>0</v>
+      </c>
+      <c r="H513" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="I513" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="J513" t="str">
+        <v>2026-09-02 21:00</v>
+      </c>
+      <c r="K513" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L513">
+        <v>1</v>
+      </c>
+      <c r="M513" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N513" t="str">
+        <v>2026-09-02 19:18:47</v>
+      </c>
+      <c r="O513" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P513" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q513" t="str">
+        <v/>
+      </c>
+      <c r="R513" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S513" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>T260902-00017</v>
+      </c>
+      <c r="B514" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C514" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D514" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E514" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F514" t="str">
+        <v>구미FDC(신규)</v>
+      </c>
+      <c r="G514">
+        <v>1</v>
+      </c>
+      <c r="H514" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="I514" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="J514" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K514" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L514">
+        <v>1</v>
+      </c>
+      <c r="M514" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N514" t="str">
+        <v>2026-09-02 19:17:37</v>
+      </c>
+      <c r="O514" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P514" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q514" t="str">
+        <v/>
+      </c>
+      <c r="R514" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S514" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>T260902-00016</v>
+      </c>
+      <c r="B515" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C515" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D515" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E515" t="str">
+        <v>2026-09-02 19:00</v>
+      </c>
+      <c r="F515" t="str">
+        <v>강릉ACP</v>
+      </c>
+      <c r="G515">
+        <v>1</v>
+      </c>
+      <c r="H515" t="str">
+        <v>강릉FDC</v>
+      </c>
+      <c r="I515" t="str">
+        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
+      </c>
+      <c r="J515" t="str">
+        <v>2026-09-02 23:00</v>
+      </c>
+      <c r="K515" t="str">
+        <v>2.5톤 윙바디</v>
+      </c>
+      <c r="L515">
+        <v>1</v>
+      </c>
+      <c r="M515" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N515" t="str">
+        <v>2026-09-02 19:16:53</v>
+      </c>
+      <c r="O515" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P515" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q515" t="str">
+        <v/>
+      </c>
+      <c r="R515" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S515" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>T260902-00015</v>
+      </c>
+      <c r="B516" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C516" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D516" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E516" t="str">
+        <v>2026-09-02 18:10</v>
+      </c>
+      <c r="F516" t="str">
+        <v/>
+      </c>
+      <c r="G516">
+        <v>0</v>
+      </c>
+      <c r="H516" t="str">
+        <v>양산 하이마트 하이얼</v>
+      </c>
+      <c r="I516" t="str">
+        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 하이얼</v>
+      </c>
+      <c r="J516" t="str">
+        <v>2026-09-03 21:30</v>
+      </c>
+      <c r="K516" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L516">
+        <v>1</v>
+      </c>
+      <c r="M516" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N516" t="str">
+        <v>2026-09-02 17:49:53</v>
+      </c>
+      <c r="O516" s="1">
+        <v>340000</v>
+      </c>
+      <c r="P516" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q516" t="str">
+        <v>하이얼 양산 하이마트 물류</v>
+      </c>
+      <c r="R516" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S516" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>T260902-00014</v>
+      </c>
+      <c r="B517" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C517" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D517" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E517" t="str">
+        <v>2026-09-02 17:30</v>
+      </c>
+      <c r="F517" t="str">
+        <v/>
+      </c>
+      <c r="G517">
+        <v>0</v>
+      </c>
+      <c r="H517" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="I517" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="J517" t="str">
+        <v>2026-09-02 18:30</v>
+      </c>
+      <c r="K517" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L517">
+        <v>1</v>
+      </c>
+      <c r="M517" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N517" t="str">
+        <v>2026-09-02 17:27:54</v>
+      </c>
+      <c r="O517" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P517" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q517" t="str">
+        <v/>
+      </c>
+      <c r="R517" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S517" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>T260902-00013</v>
+      </c>
+      <c r="B518" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C518" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="D518" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="E518" t="str">
+        <v>2026-09-02 11:00</v>
+      </c>
+      <c r="F518" t="str">
+        <v/>
+      </c>
+      <c r="G518">
+        <v>0</v>
+      </c>
+      <c r="H518" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I518" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J518" t="str">
+        <v>2026-09-02 13:30</v>
+      </c>
+      <c r="K518" t="str">
+        <v>1톤 기타차량</v>
+      </c>
+      <c r="L518">
+        <v>1</v>
+      </c>
+      <c r="M518" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N518" t="str">
+        <v>2026-09-02 17:27:24</v>
+      </c>
+      <c r="O518" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P518" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q518" t="str">
+        <v>거래처비용청구(1대)</v>
+      </c>
+      <c r="R518" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S518" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>T260902-00012</v>
+      </c>
+      <c r="B519" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C519" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D519" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E519" t="str">
+        <v>2026-09-02 14:30</v>
+      </c>
+      <c r="F519" t="str">
+        <v/>
+      </c>
+      <c r="G519">
+        <v>0</v>
+      </c>
+      <c r="H519" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I519" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J519" t="str">
+        <v>2026-09-02 15:30</v>
+      </c>
+      <c r="K519" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L519">
+        <v>1</v>
+      </c>
+      <c r="M519" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N519" t="str">
+        <v>2026-09-02 17:26:30</v>
+      </c>
+      <c r="O519" s="1">
+        <v>70000</v>
+      </c>
+      <c r="P519" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q519" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="R519" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S519" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>T260902-00011</v>
+      </c>
+      <c r="B520" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C520" t="str">
+        <v>듀오백</v>
+      </c>
+      <c r="D520" t="str">
+        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
+      </c>
+      <c r="E520" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="F520" t="str">
+        <v/>
+      </c>
+      <c r="G520">
+        <v>0</v>
+      </c>
+      <c r="H520" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I520" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J520" t="str">
+        <v>2026-09-02 13:30</v>
+      </c>
+      <c r="K520" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L520">
+        <v>1</v>
+      </c>
+      <c r="M520" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N520" t="str">
+        <v>2026-09-02 17:25:43</v>
+      </c>
+      <c r="O520" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P520" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q520" t="str">
+        <v>듀오백 외주사입고</v>
+      </c>
+      <c r="R520" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S520" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>T260902-00010</v>
+      </c>
+      <c r="B521" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C521" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D521" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E521" t="str">
+        <v>2026-09-02 17:10</v>
+      </c>
+      <c r="F521" t="str">
+        <v/>
+      </c>
+      <c r="G521">
+        <v>0</v>
+      </c>
+      <c r="H521" t="str">
+        <v>마산 하이마트 하이얼</v>
+      </c>
+      <c r="I521" t="str">
+        <v>경남 함안군 법수면 법수로 546 마산 하이마트 하이얼</v>
+      </c>
+      <c r="J521" t="str">
+        <v>2026-09-03 09:30</v>
+      </c>
+      <c r="K521" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L521">
+        <v>1</v>
+      </c>
+      <c r="M521" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N521" t="str">
+        <v>2026-09-02 16:04:12</v>
+      </c>
+      <c r="O521" s="1">
+        <v>340000</v>
+      </c>
+      <c r="P521" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q521" t="str">
+        <v>하이얼  마산 하이마트 물류</v>
+      </c>
+      <c r="R521" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S521" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>T260902-00009</v>
+      </c>
+      <c r="B522" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C522" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D522" t="str">
+        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
+      </c>
+      <c r="E522" t="str">
+        <v>2026-09-02 16:30</v>
+      </c>
+      <c r="F522" t="str">
+        <v/>
+      </c>
+      <c r="G522">
+        <v>0</v>
+      </c>
+      <c r="H522" t="str">
+        <v>경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="I522" t="str">
+        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
+      </c>
+      <c r="J522" t="str">
+        <v>2026-09-02 17:30</v>
+      </c>
+      <c r="K522" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L522">
+        <v>1</v>
+      </c>
+      <c r="M522" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N522" t="str">
+        <v>2026-09-02 16:01:28</v>
+      </c>
+      <c r="O522" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P522" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q522" t="str">
+        <v/>
+      </c>
+      <c r="R522" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S522" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>T260902-00008</v>
+      </c>
+      <c r="B523" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C523" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D523" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E523" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="F523" t="str">
+        <v/>
+      </c>
+      <c r="G523">
+        <v>0</v>
+      </c>
+      <c r="H523" t="str">
+        <v>이천 하이마트 하이얼</v>
+      </c>
+      <c r="I523" t="str">
+        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 하이얼</v>
+      </c>
+      <c r="J523" t="str">
+        <v>2026-09-02 15:00</v>
+      </c>
+      <c r="K523" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L523">
+        <v>1</v>
+      </c>
+      <c r="M523" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N523" t="str">
+        <v>2026-09-02 10:54:59</v>
+      </c>
+      <c r="O523" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P523" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q523" t="str">
+        <v>하이얼 이천 하이마트 물류</v>
+      </c>
+      <c r="R523" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S523" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>T260902-00007</v>
+      </c>
+      <c r="B524" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C524" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D524" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E524" t="str">
+        <v>2026-09-02 09:40</v>
+      </c>
+      <c r="F524" t="str">
+        <v/>
+      </c>
+      <c r="G524">
+        <v>0</v>
+      </c>
+      <c r="H524" t="str">
+        <v>화성 하이마트 하이얼</v>
+      </c>
+      <c r="I524" t="str">
+        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 하이얼</v>
+      </c>
+      <c r="J524" t="str">
+        <v>2026-09-02 03:00</v>
+      </c>
+      <c r="K524" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L524">
+        <v>1</v>
+      </c>
+      <c r="M524" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N524" t="str">
+        <v>2026-09-02 10:50:30</v>
+      </c>
+      <c r="O524" s="1">
+        <v>140000</v>
+      </c>
+      <c r="P524" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q524" t="str">
+        <v>히이얼 화성 하이마트 물류</v>
+      </c>
+      <c r="R524" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S524" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>T260902-00006</v>
+      </c>
+      <c r="B525" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C525" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D525" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E525" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F525" t="str">
+        <v/>
+      </c>
+      <c r="G525">
+        <v>0</v>
+      </c>
+      <c r="H525" t="str">
+        <v>인천 하이마트 하이얼</v>
+      </c>
+      <c r="I525" t="str">
+        <v>인천 중구 서해대로94번길 132 인천 하이마트 하이얼</v>
+      </c>
+      <c r="J525" t="str">
+        <v>2026-09-02 03:00</v>
+      </c>
+      <c r="K525" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L525">
+        <v>1</v>
+      </c>
+      <c r="M525" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N525" t="str">
+        <v>2026-09-02 10:36:26</v>
+      </c>
+      <c r="O525" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P525" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q525" t="str">
+        <v>하이얼 인천 하이마트 물류</v>
+      </c>
+      <c r="R525" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S525" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>T260902-00005</v>
+      </c>
+      <c r="B526" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C526" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D526" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E526" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F526" t="str">
+        <v/>
+      </c>
+      <c r="G526">
+        <v>0</v>
+      </c>
+      <c r="H526" t="str">
+        <v>아임테크날러지 창고</v>
+      </c>
+      <c r="I526" t="str">
+        <v>경기 김포시 통진읍 월하로479번길 32-42 가동, 나동</v>
+      </c>
+      <c r="J526" t="str">
+        <v>2026-09-02 11:00</v>
+      </c>
+      <c r="K526" t="str">
+        <v>3.5톤 윙바디</v>
+      </c>
+      <c r="L526">
+        <v>1</v>
+      </c>
+      <c r="M526" t="str">
+        <v>차순권</v>
+      </c>
+      <c r="N526" t="str">
+        <v>2026-09-02 09:52:58</v>
+      </c>
+      <c r="O526" s="1">
+        <v>230000</v>
+      </c>
+      <c r="P526" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q526" t="str">
+        <v>아임테크 날러지 회수2, 가용 1파렛트 출하</v>
+      </c>
+      <c r="R526" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S526" t="str">
+        <v>아임테크날러지</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>T260902-00004</v>
+      </c>
+      <c r="B527" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C527" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D527" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E527" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F527" t="str">
+        <v/>
+      </c>
+      <c r="G527">
+        <v>0</v>
+      </c>
+      <c r="H527" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I527" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J527" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="K527" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L527">
+        <v>1</v>
+      </c>
+      <c r="M527" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N527" t="str">
+        <v>2026-09-02 09:49:55</v>
+      </c>
+      <c r="O527" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P527" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q527" t="str">
+        <v>중산물산 회수품</v>
+      </c>
+      <c r="R527" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S527" t="str">
+        <v>중산물산</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>T260902-00003</v>
+      </c>
+      <c r="B528" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C528" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D528" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E528" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F528" t="str">
+        <v/>
+      </c>
+      <c r="G528">
+        <v>0</v>
+      </c>
+      <c r="H528" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I528" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J528" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="K528" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L528">
+        <v>1</v>
+      </c>
+      <c r="M528" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N528" t="str">
+        <v>2026-09-02 09:37:44</v>
+      </c>
+      <c r="O528" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P528" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q528" t="str">
+        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
+      </c>
+      <c r="R528" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S528" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
+        <v>T260902-00002</v>
+      </c>
+      <c r="B529" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C529" t="str">
+        <v>청주ARC</v>
+      </c>
+      <c r="D529" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
+      </c>
+      <c r="E529" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="F529" t="str">
+        <v/>
+      </c>
+      <c r="G529">
+        <v>0</v>
+      </c>
+      <c r="H529" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I529" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J529" t="str">
+        <v>2026-09-02 10:00</v>
+      </c>
+      <c r="K529" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L529">
+        <v>1</v>
+      </c>
+      <c r="M529" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N529" t="str">
+        <v>2026-09-02 09:37:02</v>
+      </c>
+      <c r="O529" s="1">
+        <v>180000</v>
+      </c>
+      <c r="P529" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q529" t="str">
+        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
+      </c>
+      <c r="R529" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S529" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
+        <v>T260902-00001</v>
+      </c>
+      <c r="B530" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C530" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D530" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E530" t="str">
+        <v>2026-09-02 09:50</v>
+      </c>
+      <c r="F530" t="str">
+        <v/>
+      </c>
+      <c r="G530">
+        <v>0</v>
+      </c>
+      <c r="H530" t="str">
+        <v>아임테크</v>
+      </c>
+      <c r="I530" t="str">
+        <v>경기 김포시 통진읍 귀전리 537-4 아임테크</v>
+      </c>
+      <c r="J530" t="str">
+        <v>2026-09-02 11:00</v>
+      </c>
+      <c r="K530" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L530">
+        <v>1</v>
+      </c>
+      <c r="M530" t="str">
+        <v>임태양</v>
+      </c>
+      <c r="N530" t="str">
+        <v>2026-09-02 09:33:24</v>
+      </c>
+      <c r="O530" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P530" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q530" t="str">
+        <v>아임테크날러지 전량 출하</v>
+      </c>
+      <c r="R530" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S530" t="str">
+        <v>아임테크날러지</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>T260901-00019</v>
+      </c>
+      <c r="B531" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C531" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D531" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E531" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F531" t="str">
+        <v>시흥ACP,인천ACP</v>
+      </c>
+      <c r="G531">
+        <v>2</v>
+      </c>
+      <c r="H531" t="str">
+        <v>파주ACP</v>
+      </c>
+      <c r="I531" t="str">
+        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
+      </c>
+      <c r="J531" t="str">
+        <v>2026-09-02 07:00</v>
+      </c>
+      <c r="K531" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L531">
+        <v>1</v>
+      </c>
+      <c r="M531" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N531" t="str">
+        <v>2026-09-01 19:27:06</v>
+      </c>
+      <c r="O531" s="1">
+        <v>230000</v>
+      </c>
+      <c r="P531" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q531" t="str">
+        <v/>
+      </c>
+      <c r="R531" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S531" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>T260901-00018</v>
+      </c>
+      <c r="B532" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C532" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D532" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E532" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F532" t="str">
+        <v>대전중구ACP,대전대덕ACP</v>
+      </c>
+      <c r="G532">
+        <v>2</v>
+      </c>
+      <c r="H532" t="str">
+        <v>군산ACP</v>
+      </c>
+      <c r="I532" t="str">
+        <v>전북특별자치도 군산시 구암3.1로 60 군산ACP</v>
+      </c>
+      <c r="J532" t="str">
+        <v>2026-09-02 07:00</v>
+      </c>
+      <c r="K532" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L532">
+        <v>1</v>
+      </c>
+      <c r="M532" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N532" t="str">
+        <v>2026-09-01 19:26:35</v>
+      </c>
+      <c r="O532" s="1">
+        <v>300000</v>
+      </c>
+      <c r="P532" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q532" t="str">
+        <v/>
+      </c>
+      <c r="R532" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S532" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>T260901-00017</v>
+      </c>
+      <c r="B533" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C533" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D533" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E533" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F533" t="str">
+        <v>안성ACP,화성ACP,용인ACP</v>
+      </c>
+      <c r="G533">
+        <v>3</v>
+      </c>
+      <c r="H533" t="str">
+        <v>구리ACP</v>
+      </c>
+      <c r="I533" t="str">
+        <v>경기 구리시 사노동 110 구리ACP</v>
+      </c>
+      <c r="J533" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K533" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L533">
+        <v>1</v>
+      </c>
+      <c r="M533" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N533" t="str">
+        <v>2026-09-01 19:25:58</v>
+      </c>
+      <c r="O533" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P533" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q533" t="str">
+        <v/>
+      </c>
+      <c r="R533" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S533" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>T260901-00016</v>
+      </c>
+      <c r="B534" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C534" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D534" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E534" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F534" t="str">
+        <v/>
+      </c>
+      <c r="G534">
+        <v>0</v>
+      </c>
+      <c r="H534" t="str">
+        <v>화성FDC(신규)</v>
+      </c>
+      <c r="I534" t="str">
+        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
+      </c>
+      <c r="J534" t="str">
+        <v>2026-09-01 21:00</v>
+      </c>
+      <c r="K534" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L534">
+        <v>1</v>
+      </c>
+      <c r="M534" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N534" t="str">
+        <v>2026-09-01 19:25:13</v>
+      </c>
+      <c r="O534" s="1">
+        <v>240000</v>
+      </c>
+      <c r="P534" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q534" t="str">
+        <v/>
+      </c>
+      <c r="R534" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S534" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>T260901-00015</v>
+      </c>
+      <c r="B535" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C535" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D535" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E535" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F535" t="str">
+        <v>천안FDC</v>
+      </c>
+      <c r="G535">
+        <v>1</v>
+      </c>
+      <c r="H535" t="str">
+        <v>청주FDC</v>
+      </c>
+      <c r="I535" t="str">
+        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
+      </c>
+      <c r="J535" t="str">
+        <v>2026-09-01 22:00</v>
+      </c>
+      <c r="K535" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L535">
+        <v>1</v>
+      </c>
+      <c r="M535" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N535" t="str">
+        <v>2026-09-01 19:24:58</v>
+      </c>
+      <c r="O535" s="1">
+        <v>350000</v>
+      </c>
+      <c r="P535" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q535" t="str">
+        <v/>
+      </c>
+      <c r="R535" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S535" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>T260901-00014</v>
+      </c>
+      <c r="B536" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C536" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D536" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E536" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F536" t="str">
+        <v/>
+      </c>
+      <c r="G536">
+        <v>0</v>
+      </c>
+      <c r="H536" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="I536" t="str">
+        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
+      </c>
+      <c r="J536" t="str">
+        <v>2026-09-01 21:00</v>
+      </c>
+      <c r="K536" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L536">
+        <v>1</v>
+      </c>
+      <c r="M536" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N536" t="str">
+        <v>2026-09-01 19:24:38</v>
+      </c>
+      <c r="O536" s="1">
+        <v>260000</v>
+      </c>
+      <c r="P536" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q536" t="str">
+        <v/>
+      </c>
+      <c r="R536" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S536" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>T260901-00013</v>
+      </c>
+      <c r="B537" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C537" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D537" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E537" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F537" t="str">
+        <v>원주FDC(신규)</v>
+      </c>
+      <c r="G537">
+        <v>1</v>
+      </c>
+      <c r="H537" t="str">
+        <v>제천FDC</v>
+      </c>
+      <c r="I537" t="str">
+        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
+      </c>
+      <c r="J537" t="str">
+        <v>2026-09-01 22:00</v>
+      </c>
+      <c r="K537" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L537">
+        <v>1</v>
+      </c>
+      <c r="M537" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N537" t="str">
+        <v>2026-09-01 19:24:22</v>
+      </c>
+      <c r="O537" s="1">
+        <v>290000</v>
+      </c>
+      <c r="P537" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q537" t="str">
+        <v/>
+      </c>
+      <c r="R537" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S537" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>T260901-00012</v>
+      </c>
+      <c r="B538" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C538" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D538" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E538" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F538" t="str">
+        <v>진주FDC,창원FDC</v>
+      </c>
+      <c r="G538">
+        <v>2</v>
+      </c>
+      <c r="H538" t="str">
+        <v>양산FDC</v>
+      </c>
+      <c r="I538" t="str">
+        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
+      </c>
+      <c r="J538" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K538" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L538">
+        <v>1</v>
+      </c>
+      <c r="M538" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N538" t="str">
+        <v>2026-09-01 19:23:57</v>
+      </c>
+      <c r="O538" s="1">
+        <v>730000</v>
+      </c>
+      <c r="P538" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q538" t="str">
+        <v/>
+      </c>
+      <c r="R538" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S538" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>T260901-00011</v>
+      </c>
+      <c r="B539" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C539" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D539" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E539" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F539" t="str">
+        <v>남양주FDC</v>
+      </c>
+      <c r="G539">
+        <v>1</v>
+      </c>
+      <c r="H539" t="str">
+        <v>김포FDC</v>
+      </c>
+      <c r="I539" t="str">
+        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
+      </c>
+      <c r="J539" t="str">
+        <v>2026-09-01 22:00</v>
+      </c>
+      <c r="K539" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L539">
+        <v>1</v>
+      </c>
+      <c r="M539" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N539" t="str">
+        <v>2026-09-01 19:23:32</v>
+      </c>
+      <c r="O539" s="1">
+        <v>370000</v>
+      </c>
+      <c r="P539" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q539" t="str">
+        <v/>
+      </c>
+      <c r="R539" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S539" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>T260901-00010</v>
+      </c>
+      <c r="B540" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C540" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D540" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E540" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F540" t="str">
+        <v>전주FDC</v>
+      </c>
+      <c r="G540">
+        <v>1</v>
+      </c>
+      <c r="H540" t="str">
+        <v>광주FDC</v>
+      </c>
+      <c r="I540" t="str">
+        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
+      </c>
+      <c r="J540" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K540" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L540">
+        <v>1</v>
+      </c>
+      <c r="M540" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N540" t="str">
+        <v>2026-09-01 19:23:13</v>
+      </c>
+      <c r="O540" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P540" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q540" t="str">
+        <v/>
+      </c>
+      <c r="R540" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S540" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>T260901-00009</v>
+      </c>
+      <c r="B541" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C541" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D541" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E541" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F541" t="str">
+        <v/>
+      </c>
+      <c r="G541">
+        <v>0</v>
+      </c>
+      <c r="H541" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="I541" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
+      </c>
+      <c r="J541" t="str">
+        <v>2026-09-01 21:00</v>
+      </c>
+      <c r="K541" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L541">
+        <v>1</v>
+      </c>
+      <c r="M541" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N541" t="str">
+        <v>2026-09-01 19:22:26</v>
+      </c>
+      <c r="O541" s="1">
+        <v>200000</v>
+      </c>
+      <c r="P541" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q541" t="str">
+        <v/>
+      </c>
+      <c r="R541" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S541" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>T260901-00008</v>
+      </c>
+      <c r="B542" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C542" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D542" t="str">
+        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
+      </c>
+      <c r="E542" t="str">
+        <v>2026-09-01 19:00</v>
+      </c>
+      <c r="F542" t="str">
+        <v>구미FDC(신규)</v>
+      </c>
+      <c r="G542">
+        <v>1</v>
+      </c>
+      <c r="H542" t="str">
+        <v>경산FDC</v>
+      </c>
+      <c r="I542" t="str">
+        <v>경산시 자인면 일언리11-3 경산FDC</v>
+      </c>
+      <c r="J542" t="str">
+        <v>2026-09-01 23:00</v>
+      </c>
+      <c r="K542" t="str">
+        <v>11톤 윙바디</v>
+      </c>
+      <c r="L542">
+        <v>1</v>
+      </c>
+      <c r="M542" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N542" t="str">
+        <v>2026-09-01 19:22:10</v>
+      </c>
+      <c r="O542" s="1">
+        <v>520000</v>
+      </c>
+      <c r="P542" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q542" t="str">
+        <v/>
+      </c>
+      <c r="R542" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S542" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>T260901-00007</v>
+      </c>
+      <c r="B543" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C543" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D543" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="E543" t="str">
+        <v>2026-09-01 17:20</v>
+      </c>
+      <c r="F543" t="str">
+        <v/>
+      </c>
+      <c r="G543">
+        <v>0</v>
+      </c>
+      <c r="H543" t="str">
+        <v>한진택배</v>
+      </c>
+      <c r="I543" t="str">
+        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
+      </c>
+      <c r="J543" t="str">
+        <v>2026-09-01 18:20</v>
+      </c>
+      <c r="K543" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L543">
+        <v>1</v>
+      </c>
+      <c r="M543" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N543" t="str">
+        <v>2026-09-01 19:20:06</v>
+      </c>
+      <c r="O543" s="1">
+        <v>100000</v>
+      </c>
+      <c r="P543" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q543" t="str">
+        <v/>
+      </c>
+      <c r="R543" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S543" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>T260901-00006</v>
+      </c>
+      <c r="B544" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C544" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="D544" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="E544" t="str">
+        <v>2026-09-01 11:20</v>
+      </c>
+      <c r="F544" t="str">
+        <v/>
+      </c>
+      <c r="G544">
+        <v>0</v>
+      </c>
+      <c r="H544" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I544" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J544" t="str">
+        <v>2026-09-01 13:20</v>
+      </c>
+      <c r="K544" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L544">
+        <v>1</v>
+      </c>
+      <c r="M544" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N544" t="str">
+        <v>2026-09-01 19:19:31</v>
+      </c>
+      <c r="O544" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P544" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q544" t="str">
+        <v>거래처비용청구(2대)</v>
+      </c>
+      <c r="R544" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S544" t="str">
+        <v>샤오미</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>T260901-00005</v>
+      </c>
+      <c r="B545" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C545" t="str">
+        <v>아이베</v>
+      </c>
+      <c r="D545" t="str">
+        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
+      </c>
+      <c r="E545" t="str">
+        <v>2026-09-01 14:20</v>
+      </c>
+      <c r="F545" t="str">
+        <v/>
+      </c>
+      <c r="G545">
+        <v>0</v>
+      </c>
+      <c r="H545" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I545" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J545" t="str">
+        <v>2026-09-01 15:20</v>
+      </c>
+      <c r="K545" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L545">
+        <v>1</v>
+      </c>
+      <c r="M545" t="str">
+        <v>윤태구</v>
+      </c>
+      <c r="N545" t="str">
+        <v>2026-09-01 19:18:39</v>
+      </c>
+      <c r="O545" s="1">
+        <v>70000</v>
+      </c>
+      <c r="P545" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q545" t="str">
+        <v>아이베 외주사입고</v>
+      </c>
+      <c r="R545" t="str">
+        <v>JM컴퍼니</v>
+      </c>
+      <c r="S545" t="str">
+        <v>아이베(신규)</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>T260901-00004</v>
+      </c>
+      <c r="B546" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C546" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D546" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E546" t="str">
+        <v>2026-09-01 15:50</v>
+      </c>
+      <c r="F546" t="str">
+        <v/>
+      </c>
+      <c r="G546">
+        <v>0</v>
+      </c>
+      <c r="H546" t="str">
+        <v>공주 하이마트 하이얼</v>
+      </c>
+      <c r="I546" t="str">
+        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
+      </c>
+      <c r="J546" t="str">
+        <v>2026-09-02 15:00</v>
+      </c>
+      <c r="K546" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L546">
+        <v>1</v>
+      </c>
+      <c r="M546" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N546" t="str">
+        <v>2026-09-01 15:50:14</v>
+      </c>
+      <c r="O546" s="1">
+        <v>220000</v>
+      </c>
+      <c r="P546" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q546" t="str">
+        <v>하이얼 공주 하이마트 물류</v>
+      </c>
+      <c r="R546" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S546" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>T260901-00003</v>
+      </c>
+      <c r="B547" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C547" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="D547" t="str">
+        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
+      </c>
+      <c r="E547" t="str">
+        <v>2026-09-01 15:35</v>
+      </c>
+      <c r="F547" t="str">
+        <v/>
+      </c>
+      <c r="G547">
+        <v>0</v>
+      </c>
+      <c r="H547" t="str">
+        <v>대구 하이마트 하이얼</v>
+      </c>
+      <c r="I547" t="str">
+        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
+      </c>
+      <c r="J547" t="str">
+        <v>2026-09-02 15:00</v>
+      </c>
+      <c r="K547" t="str">
+        <v>5톤 윙바디</v>
+      </c>
+      <c r="L547">
+        <v>1</v>
+      </c>
+      <c r="M547" t="str">
+        <v>박진실</v>
+      </c>
+      <c r="N547" t="str">
+        <v>2026-09-01 13:37:23</v>
+      </c>
+      <c r="O547" s="1">
+        <v>300000</v>
+      </c>
+      <c r="P547" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Q547" t="str">
+        <v>하이얼 대구 하이마트 물류</v>
+      </c>
+      <c r="R547" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S547" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>T260901-00002</v>
+      </c>
+      <c r="B548" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C548" t="str">
+        <v>인천FDC</v>
+      </c>
+      <c r="D548" t="str">
+        <v>인천 서구 오류동 1653-2 인천FDC</v>
+      </c>
+      <c r="E548" t="str">
+        <v>2026-09-02 08:00</v>
+      </c>
+      <c r="F548" t="str">
+        <v/>
+      </c>
+      <c r="G548">
+        <v>0</v>
+      </c>
+      <c r="H548" t="str">
+        <v>샤오미 집하장</v>
+      </c>
+      <c r="I548" t="str">
+        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
+      </c>
+      <c r="J548" t="str">
+        <v>2026-09-02 09:00</v>
+      </c>
+      <c r="K548" t="str">
+        <v>1톤 카고</v>
+      </c>
+      <c r="L548">
+        <v>1</v>
+      </c>
+      <c r="M548" t="str">
+        <v>차순권</v>
+      </c>
+      <c r="N548" t="str">
+        <v>2026-09-01 13:22:36</v>
+      </c>
+      <c r="O548" s="1">
+        <v>50000</v>
+      </c>
+      <c r="P548" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q548" t="str">
+        <v>접수번호 : 1565331 / 취소 건 샤오미 창고로 출하 / 인천FDC에서 직접 배송함</v>
+      </c>
+      <c r="R548" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S548" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>T260901-00001</v>
+      </c>
+      <c r="B549" t="str">
+        <v>운송완료</v>
+      </c>
+      <c r="C549" t="str">
+        <v>곤지암FDC</v>
+      </c>
+      <c r="D549" t="str">
+        <v>경기 용인시 처인구 모현읍 곡현로 821 곤지암FDC</v>
+      </c>
+      <c r="E549" t="str">
+        <v>2026-09-01 08:00</v>
+      </c>
+      <c r="F549" t="str">
+        <v/>
+      </c>
+      <c r="G549">
+        <v>0</v>
+      </c>
+      <c r="H549" t="str">
+        <v>안성FC</v>
+      </c>
+      <c r="I549" t="str">
+        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
+      </c>
+      <c r="J549" t="str">
+        <v>2026-09-01 10:00</v>
+      </c>
+      <c r="K549" t="str">
+        <v>1톤 윙바디</v>
+      </c>
+      <c r="L549">
+        <v>1</v>
+      </c>
+      <c r="M549" t="str">
+        <v>차순권</v>
+      </c>
+      <c r="N549" t="str">
+        <v>2026-09-01 09:03:56</v>
+      </c>
+      <c r="O549" s="1">
+        <v>80000</v>
+      </c>
+      <c r="P549" s="1">
+        <v>5000</v>
+      </c>
+      <c r="Q549" t="str">
+        <v>하이얼 가용재고 10개 이동</v>
+      </c>
+      <c r="R549" t="str">
+        <v>(주)위니온로지스</v>
+      </c>
+      <c r="S549" t="str">
+        <v>하이얼</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S441"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S549"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S549"/>
+  <dimension ref="A1:S441"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -26398,6381 +26398,9 @@
         <v>일코전자</v>
       </c>
     </row>
-    <row r="442">
-      <c r="A442" t="str">
-        <v>T260904-00030</v>
-      </c>
-      <c r="B442" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C442" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D442" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E442" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F442" t="str">
-        <v>시흥ACP,인천ACP</v>
-      </c>
-      <c r="G442">
-        <v>2</v>
-      </c>
-      <c r="H442" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="I442" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="J442" t="str">
-        <v>2026-09-05 08:00</v>
-      </c>
-      <c r="K442" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="L442">
-        <v>1</v>
-      </c>
-      <c r="M442" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N442" t="str">
-        <v>2026-09-04 19:35:26</v>
-      </c>
-      <c r="O442" s="1">
-        <v>250000</v>
-      </c>
-      <c r="P442" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q442" t="str">
-        <v/>
-      </c>
-      <c r="R442" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S442" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="str">
-        <v>T260904-00029</v>
-      </c>
-      <c r="B443" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C443" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D443" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E443" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F443" t="str">
-        <v>대전대덕ACP</v>
-      </c>
-      <c r="G443">
-        <v>1</v>
-      </c>
-      <c r="H443" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="I443" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="J443" t="str">
-        <v>2026-09-05 08:00</v>
-      </c>
-      <c r="K443" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L443">
-        <v>1</v>
-      </c>
-      <c r="M443" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N443" t="str">
-        <v>2026-09-04 19:34:55</v>
-      </c>
-      <c r="O443" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P443" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q443" t="str">
-        <v/>
-      </c>
-      <c r="R443" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S443" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="str">
-        <v>T260904-00028</v>
-      </c>
-      <c r="B444" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C444" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D444" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E444" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F444" t="str">
-        <v/>
-      </c>
-      <c r="G444">
-        <v>0</v>
-      </c>
-      <c r="H444" t="str">
-        <v>구미ACP</v>
-      </c>
-      <c r="I444" t="str">
-        <v>경북 구미시 봉곡남로1길 20 구미ACP</v>
-      </c>
-      <c r="J444" t="str">
-        <v>2026-09-04 22:00</v>
-      </c>
-      <c r="K444" t="str">
-        <v>1톤 기타차량</v>
-      </c>
-      <c r="L444">
-        <v>1</v>
-      </c>
-      <c r="M444" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N444" t="str">
-        <v>2026-09-04 19:34:17</v>
-      </c>
-      <c r="O444" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P444" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q444" t="str">
-        <v/>
-      </c>
-      <c r="R444" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S444" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="str">
-        <v>T260904-00027</v>
-      </c>
-      <c r="B445" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C445" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D445" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E445" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F445" t="str">
-        <v>안성ACP,용인ACP,화성ACP,구리ACP</v>
-      </c>
-      <c r="G445">
-        <v>4</v>
-      </c>
-      <c r="H445" t="str">
-        <v>춘천ACP</v>
-      </c>
-      <c r="I445" t="str">
-        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
-      </c>
-      <c r="J445" t="str">
-        <v>2026-09-04 23:59</v>
-      </c>
-      <c r="K445" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L445">
-        <v>1</v>
-      </c>
-      <c r="M445" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N445" t="str">
-        <v>2026-09-04 19:33:56</v>
-      </c>
-      <c r="O445" s="1">
-        <v>380000</v>
-      </c>
-      <c r="P445" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q445" t="str">
-        <v/>
-      </c>
-      <c r="R445" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S445" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="str">
-        <v>T260904-00026</v>
-      </c>
-      <c r="B446" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C446" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D446" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E446" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F446" t="str">
-        <v/>
-      </c>
-      <c r="G446">
-        <v>0</v>
-      </c>
-      <c r="H446" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="I446" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="J446" t="str">
-        <v>2026-09-04 21:00</v>
-      </c>
-      <c r="K446" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L446">
-        <v>1</v>
-      </c>
-      <c r="M446" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N446" t="str">
-        <v>2026-09-04 19:33:14</v>
-      </c>
-      <c r="O446" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P446" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q446" t="str">
-        <v/>
-      </c>
-      <c r="R446" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S446" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="str">
-        <v>T260904-00025</v>
-      </c>
-      <c r="B447" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C447" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D447" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E447" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F447" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="G447">
-        <v>1</v>
-      </c>
-      <c r="H447" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="I447" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="J447" t="str">
-        <v>2026-09-04 22:00</v>
-      </c>
-      <c r="K447" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L447">
-        <v>1</v>
-      </c>
-      <c r="M447" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N447" t="str">
-        <v>2026-09-04 19:32:56</v>
-      </c>
-      <c r="O447" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P447" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q447" t="str">
-        <v/>
-      </c>
-      <c r="R447" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S447" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="str">
-        <v>T260904-00024</v>
-      </c>
-      <c r="B448" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C448" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D448" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E448" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F448" t="str">
-        <v/>
-      </c>
-      <c r="G448">
-        <v>0</v>
-      </c>
-      <c r="H448" t="str">
-        <v>진주FDC</v>
-      </c>
-      <c r="I448" t="str">
-        <v>경상남도 진주시 지수면 승산리 163-1(가운데 동) 진주FDC</v>
-      </c>
-      <c r="J448" t="str">
-        <v>2026-09-04 23:00</v>
-      </c>
-      <c r="K448" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L448">
-        <v>1</v>
-      </c>
-      <c r="M448" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N448" t="str">
-        <v>2026-09-04 19:32:37</v>
-      </c>
-      <c r="O448" s="1">
-        <v>310000</v>
-      </c>
-      <c r="P448" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q448" t="str">
-        <v/>
-      </c>
-      <c r="R448" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S448" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="str">
-        <v>T260904-00023</v>
-      </c>
-      <c r="B449" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C449" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D449" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E449" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F449" t="str">
-        <v/>
-      </c>
-      <c r="G449">
-        <v>0</v>
-      </c>
-      <c r="H449" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="I449" t="str">
-        <v>인천 검단구 오류동 1653-2 인천FDC</v>
-      </c>
-      <c r="J449" t="str">
-        <v>2026-09-04 21:00</v>
-      </c>
-      <c r="K449" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L449">
-        <v>1</v>
-      </c>
-      <c r="M449" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N449" t="str">
-        <v>2026-09-04 19:32:22</v>
-      </c>
-      <c r="O449" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P449" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q449" t="str">
-        <v/>
-      </c>
-      <c r="R449" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S449" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="str">
-        <v>T260904-00022</v>
-      </c>
-      <c r="B450" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C450" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D450" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E450" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F450" t="str">
-        <v>원주FDC(신규)</v>
-      </c>
-      <c r="G450">
-        <v>1</v>
-      </c>
-      <c r="H450" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="I450" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="J450" t="str">
-        <v>2026-09-04 22:00</v>
-      </c>
-      <c r="K450" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L450">
-        <v>1</v>
-      </c>
-      <c r="M450" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N450" t="str">
-        <v>2026-09-04 19:32:07</v>
-      </c>
-      <c r="O450" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P450" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q450" t="str">
-        <v/>
-      </c>
-      <c r="R450" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S450" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="str">
-        <v>T260904-00021</v>
-      </c>
-      <c r="B451" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C451" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D451" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E451" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F451" t="str">
-        <v>창원FDC</v>
-      </c>
-      <c r="G451">
-        <v>1</v>
-      </c>
-      <c r="H451" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="I451" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="J451" t="str">
-        <v>2026-09-04 23:00</v>
-      </c>
-      <c r="K451" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L451">
-        <v>1</v>
-      </c>
-      <c r="M451" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N451" t="str">
-        <v>2026-09-04 19:31:41</v>
-      </c>
-      <c r="O451" s="1">
-        <v>590000</v>
-      </c>
-      <c r="P451" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q451" t="str">
-        <v/>
-      </c>
-      <c r="R451" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S451" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="str">
-        <v>T260904-00020</v>
-      </c>
-      <c r="B452" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C452" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D452" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E452" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F452" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="G452">
-        <v>1</v>
-      </c>
-      <c r="H452" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="I452" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="J452" t="str">
-        <v>2026-09-04 22:00</v>
-      </c>
-      <c r="K452" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L452">
-        <v>1</v>
-      </c>
-      <c r="M452" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N452" t="str">
-        <v>2026-09-04 19:31:18</v>
-      </c>
-      <c r="O452" s="1">
-        <v>370000</v>
-      </c>
-      <c r="P452" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q452" t="str">
-        <v/>
-      </c>
-      <c r="R452" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S452" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="str">
-        <v>T260904-00019</v>
-      </c>
-      <c r="B453" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C453" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D453" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E453" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F453" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="G453">
-        <v>1</v>
-      </c>
-      <c r="H453" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="I453" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="J453" t="str">
-        <v>2026-09-04 23:00</v>
-      </c>
-      <c r="K453" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L453">
-        <v>1</v>
-      </c>
-      <c r="M453" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N453" t="str">
-        <v>2026-09-04 19:30:59</v>
-      </c>
-      <c r="O453" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P453" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q453" t="str">
-        <v/>
-      </c>
-      <c r="R453" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S453" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="str">
-        <v>T260904-00018</v>
-      </c>
-      <c r="B454" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C454" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D454" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E454" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F454" t="str">
-        <v/>
-      </c>
-      <c r="G454">
-        <v>0</v>
-      </c>
-      <c r="H454" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="I454" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="J454" t="str">
-        <v>2026-09-04 21:00</v>
-      </c>
-      <c r="K454" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L454">
-        <v>1</v>
-      </c>
-      <c r="M454" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N454" t="str">
-        <v>2026-09-04 19:30:34</v>
-      </c>
-      <c r="O454" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P454" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q454" t="str">
-        <v/>
-      </c>
-      <c r="R454" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S454" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="str">
-        <v>T260904-00017</v>
-      </c>
-      <c r="B455" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C455" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D455" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E455" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F455" t="str">
-        <v>구미FDC(신규)</v>
-      </c>
-      <c r="G455">
-        <v>1</v>
-      </c>
-      <c r="H455" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="I455" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="J455" t="str">
-        <v>2026-09-04 23:00</v>
-      </c>
-      <c r="K455" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L455">
-        <v>1</v>
-      </c>
-      <c r="M455" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N455" t="str">
-        <v>2026-09-04 19:30:19</v>
-      </c>
-      <c r="O455" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P455" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q455" t="str">
-        <v/>
-      </c>
-      <c r="R455" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S455" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="str">
-        <v>T260904-00016</v>
-      </c>
-      <c r="B456" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C456" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D456" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E456" t="str">
-        <v>2026-09-04 19:00</v>
-      </c>
-      <c r="F456" t="str">
-        <v/>
-      </c>
-      <c r="G456">
-        <v>0</v>
-      </c>
-      <c r="H456" t="str">
-        <v>강릉FDC</v>
-      </c>
-      <c r="I456" t="str">
-        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
-      </c>
-      <c r="J456" t="str">
-        <v>2026-09-04 22:00</v>
-      </c>
-      <c r="K456" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L456">
-        <v>1</v>
-      </c>
-      <c r="M456" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N456" t="str">
-        <v>2026-09-04 19:29:59</v>
-      </c>
-      <c r="O456" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P456" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q456" t="str">
-        <v/>
-      </c>
-      <c r="R456" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S456" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="str">
-        <v>T260904-00015</v>
-      </c>
-      <c r="B457" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C457" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D457" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E457" t="str">
-        <v>2026-09-04 16:50</v>
-      </c>
-      <c r="F457" t="str">
-        <v/>
-      </c>
-      <c r="G457">
-        <v>0</v>
-      </c>
-      <c r="H457" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="I457" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="J457" t="str">
-        <v>2026-09-04 17:50</v>
-      </c>
-      <c r="K457" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L457">
-        <v>1</v>
-      </c>
-      <c r="M457" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N457" t="str">
-        <v>2026-09-04 16:49:46</v>
-      </c>
-      <c r="O457" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P457" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q457" t="str">
-        <v/>
-      </c>
-      <c r="R457" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S457" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="str">
-        <v>T260904-00014</v>
-      </c>
-      <c r="B458" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C458" t="str">
-        <v>화성FDC</v>
-      </c>
-      <c r="D458" t="str">
-        <v>경기 화성시 장안면 3.1만세로 506-21 화성FDC</v>
-      </c>
-      <c r="E458" t="str">
-        <v>2026-09-04 13:50</v>
-      </c>
-      <c r="F458" t="str">
-        <v/>
-      </c>
-      <c r="G458">
-        <v>0</v>
-      </c>
-      <c r="H458" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="I458" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="J458" t="str">
-        <v>2026-09-04 15:50</v>
-      </c>
-      <c r="K458" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L458">
-        <v>1</v>
-      </c>
-      <c r="M458" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N458" t="str">
-        <v>2026-09-04 16:49:20</v>
-      </c>
-      <c r="O458" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P458" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q458" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="R458" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S458" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="str">
-        <v>T260904-00013</v>
-      </c>
-      <c r="B459" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C459" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="D459" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="E459" t="str">
-        <v>2026-09-04 11:00</v>
-      </c>
-      <c r="F459" t="str">
-        <v/>
-      </c>
-      <c r="G459">
-        <v>0</v>
-      </c>
-      <c r="H459" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I459" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J459" t="str">
-        <v>2026-09-04 13:50</v>
-      </c>
-      <c r="K459" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L459">
-        <v>1</v>
-      </c>
-      <c r="M459" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N459" t="str">
-        <v>2026-09-04 16:48:41</v>
-      </c>
-      <c r="O459" s="1">
-        <v>160000</v>
-      </c>
-      <c r="P459" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q459" t="str">
-        <v>거래처비용청구(7대)</v>
-      </c>
-      <c r="R459" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S459" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="str">
-        <v>T260904-00012</v>
-      </c>
-      <c r="B460" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C460" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D460" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E460" t="str">
-        <v>2026-09-04 14:50</v>
-      </c>
-      <c r="F460" t="str">
-        <v/>
-      </c>
-      <c r="G460">
-        <v>0</v>
-      </c>
-      <c r="H460" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I460" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J460" t="str">
-        <v>2026-09-04 15:50</v>
-      </c>
-      <c r="K460" t="str">
-        <v>1톤 기타차량</v>
-      </c>
-      <c r="L460">
-        <v>1</v>
-      </c>
-      <c r="M460" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N460" t="str">
-        <v>2026-09-04 16:47:48</v>
-      </c>
-      <c r="O460" s="1">
-        <v>55000</v>
-      </c>
-      <c r="P460" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q460" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="R460" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S460" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="str">
-        <v>T260904-00011</v>
-      </c>
-      <c r="B461" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C461" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D461" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E461" t="str">
-        <v>2026-09-04 10:00</v>
-      </c>
-      <c r="F461" t="str">
-        <v/>
-      </c>
-      <c r="G461">
-        <v>0</v>
-      </c>
-      <c r="H461" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I461" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J461" t="str">
-        <v>2026-09-04 13:50</v>
-      </c>
-      <c r="K461" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L461">
-        <v>1</v>
-      </c>
-      <c r="M461" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N461" t="str">
-        <v>2026-09-04 16:46:54</v>
-      </c>
-      <c r="O461" s="1">
-        <v>160000</v>
-      </c>
-      <c r="P461" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q461" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="R461" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S461" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="str">
-        <v>T260904-00010</v>
-      </c>
-      <c r="B462" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C462" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D462" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E462" t="str">
-        <v>2026-09-04 16:30</v>
-      </c>
-      <c r="F462" t="str">
-        <v/>
-      </c>
-      <c r="G462">
-        <v>0</v>
-      </c>
-      <c r="H462" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I462" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="J462" t="str">
-        <v>2026-09-04 17:30</v>
-      </c>
-      <c r="K462" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L462">
-        <v>1</v>
-      </c>
-      <c r="M462" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N462" t="str">
-        <v>2026-09-04 15:59:08</v>
-      </c>
-      <c r="O462" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P462" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q462" t="str">
-        <v/>
-      </c>
-      <c r="R462" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S462" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="str">
-        <v>T260904-00009</v>
-      </c>
-      <c r="B463" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C463" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D463" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E463" t="str">
-        <v>2026-09-04 12:20</v>
-      </c>
-      <c r="F463" t="str">
-        <v/>
-      </c>
-      <c r="G463">
-        <v>0</v>
-      </c>
-      <c r="H463" t="str">
-        <v>인천 하이마트 물류</v>
-      </c>
-      <c r="I463" t="str">
-        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
-      </c>
-      <c r="J463" t="str">
-        <v>2026-09-04 14:00</v>
-      </c>
-      <c r="K463" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L463">
-        <v>1</v>
-      </c>
-      <c r="M463" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N463" t="str">
-        <v>2026-09-04 11:55:28</v>
-      </c>
-      <c r="O463" s="1">
-        <v>250000</v>
-      </c>
-      <c r="P463" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q463" t="str">
-        <v>일코전자 인천 하이마트 물류</v>
-      </c>
-      <c r="R463" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S463" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="str">
-        <v>T260904-00008</v>
-      </c>
-      <c r="B464" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C464" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D464" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E464" t="str">
-        <v>2026-09-04 10:40</v>
-      </c>
-      <c r="F464" t="str">
-        <v/>
-      </c>
-      <c r="G464">
-        <v>0</v>
-      </c>
-      <c r="H464" t="str">
-        <v>인천 하이마트 물류</v>
-      </c>
-      <c r="I464" t="str">
-        <v>인천 중구 서해대로94번길 132 인천 하이마트 물류</v>
-      </c>
-      <c r="J464" t="str">
-        <v>2026-09-04 13:00</v>
-      </c>
-      <c r="K464" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L464">
-        <v>1</v>
-      </c>
-      <c r="M464" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N464" t="str">
-        <v>2026-09-04 10:28:30</v>
-      </c>
-      <c r="O464" s="1">
-        <v>120000</v>
-      </c>
-      <c r="P464" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q464" t="str">
-        <v>일코전자 인천 하이마트 물류</v>
-      </c>
-      <c r="R464" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S464" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="str">
-        <v>T260904-00007</v>
-      </c>
-      <c r="B465" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C465" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D465" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E465" t="str">
-        <v>2026-09-04 10:10</v>
-      </c>
-      <c r="F465" t="str">
-        <v/>
-      </c>
-      <c r="G465">
-        <v>0</v>
-      </c>
-      <c r="H465" t="str">
-        <v>화성 하이마트 물류</v>
-      </c>
-      <c r="I465" t="str">
-        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 물류</v>
-      </c>
-      <c r="J465" t="str">
-        <v>2026-09-04 12:00</v>
-      </c>
-      <c r="K465" t="str">
-        <v>3.5톤 카고</v>
-      </c>
-      <c r="L465">
-        <v>1</v>
-      </c>
-      <c r="M465" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N465" t="str">
-        <v>2026-09-04 09:43:35</v>
-      </c>
-      <c r="O465" s="1">
-        <v>130000</v>
-      </c>
-      <c r="P465" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q465" t="str">
-        <v>일코전자 화성 하이마트 물류</v>
-      </c>
-      <c r="R465" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S465" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="str">
-        <v>T260904-00006</v>
-      </c>
-      <c r="B466" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C466" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D466" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E466" t="str">
-        <v>2026-09-04 10:00</v>
-      </c>
-      <c r="F466" t="str">
-        <v/>
-      </c>
-      <c r="G466">
-        <v>0</v>
-      </c>
-      <c r="H466" t="str">
-        <v>이천 하이마트 물류</v>
-      </c>
-      <c r="I466" t="str">
-        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
-      </c>
-      <c r="J466" t="str">
-        <v>2026-09-04 12:00</v>
-      </c>
-      <c r="K466" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L466">
-        <v>1</v>
-      </c>
-      <c r="M466" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N466" t="str">
-        <v>2026-09-04 09:43:01</v>
-      </c>
-      <c r="O466" s="1">
-        <v>80000</v>
-      </c>
-      <c r="P466" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q466" t="str">
-        <v>일코전자 이천 하이마트 물류</v>
-      </c>
-      <c r="R466" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S466" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="str">
-        <v>T260904-00005</v>
-      </c>
-      <c r="B467" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C467" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D467" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E467" t="str">
-        <v>2026-09-04 10:00</v>
-      </c>
-      <c r="F467" t="str">
-        <v/>
-      </c>
-      <c r="G467">
-        <v>0</v>
-      </c>
-      <c r="H467" t="str">
-        <v>이천 하이마트 물류</v>
-      </c>
-      <c r="I467" t="str">
-        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 물류</v>
-      </c>
-      <c r="J467" t="str">
-        <v>2026-09-04 12:00</v>
-      </c>
-      <c r="K467" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L467">
-        <v>1</v>
-      </c>
-      <c r="M467" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N467" t="str">
-        <v>2026-09-04 09:19:08</v>
-      </c>
-      <c r="O467" s="1">
-        <v>170000</v>
-      </c>
-      <c r="P467" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q467" t="str">
-        <v>일코전자 이천 하이마트 물류</v>
-      </c>
-      <c r="R467" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S467" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="str">
-        <v>T260904-00004</v>
-      </c>
-      <c r="B468" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C468" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D468" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E468" t="str">
-        <v>2026-09-04 10:00</v>
-      </c>
-      <c r="F468" t="str">
-        <v/>
-      </c>
-      <c r="G468">
-        <v>0</v>
-      </c>
-      <c r="H468" t="str">
-        <v>양산 하이마트 물류</v>
-      </c>
-      <c r="I468" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 물류</v>
-      </c>
-      <c r="J468" t="str">
-        <v>2026-09-04 13:00</v>
-      </c>
-      <c r="K468" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L468">
-        <v>1</v>
-      </c>
-      <c r="M468" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N468" t="str">
-        <v>2026-09-04 09:18:25</v>
-      </c>
-      <c r="O468" s="1">
-        <v>470000</v>
-      </c>
-      <c r="P468" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q468" t="str">
-        <v>일코전자 양산 하이마트 물류</v>
-      </c>
-      <c r="R468" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S468" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="str">
-        <v>T260904-00003</v>
-      </c>
-      <c r="B469" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C469" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D469" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E469" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="F469" t="str">
-        <v/>
-      </c>
-      <c r="G469">
-        <v>0</v>
-      </c>
-      <c r="H469" t="str">
-        <v>광주 하이마트 물류</v>
-      </c>
-      <c r="I469" t="str">
-        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
-      </c>
-      <c r="J469" t="str">
-        <v>2026-09-04 01:00</v>
-      </c>
-      <c r="K469" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L469">
-        <v>1</v>
-      </c>
-      <c r="M469" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N469" t="str">
-        <v>2026-09-04 09:17:40</v>
-      </c>
-      <c r="O469" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P469" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q469" t="str">
-        <v>일코전자 광주 하이마트 물류</v>
-      </c>
-      <c r="R469" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S469" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="str">
-        <v>T260904-00002</v>
-      </c>
-      <c r="B470" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C470" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D470" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E470" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="F470" t="str">
-        <v/>
-      </c>
-      <c r="G470">
-        <v>0</v>
-      </c>
-      <c r="H470" t="str">
-        <v>파주 하이마트 물류</v>
-      </c>
-      <c r="I470" t="str">
-        <v>경기 파주시 탄현면 월롱산로 296 파주 하이마트 물류</v>
-      </c>
-      <c r="J470" t="str">
-        <v>2026-09-04 11:00</v>
-      </c>
-      <c r="K470" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L470">
-        <v>1</v>
-      </c>
-      <c r="M470" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N470" t="str">
-        <v>2026-09-04 09:17:14</v>
-      </c>
-      <c r="O470" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P470" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q470" t="str">
-        <v>일코전자 파주 하이마트 물류</v>
-      </c>
-      <c r="R470" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S470" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="str">
-        <v>T260904-00001</v>
-      </c>
-      <c r="B471" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C471" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D471" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E471" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="F471" t="str">
-        <v/>
-      </c>
-      <c r="G471">
-        <v>0</v>
-      </c>
-      <c r="H471" t="str">
-        <v>마산 하이마트 물류</v>
-      </c>
-      <c r="I471" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 물류</v>
-      </c>
-      <c r="J471" t="str">
-        <v>2026-09-04 13:00</v>
-      </c>
-      <c r="K471" t="str">
-        <v>5톤축 카고</v>
-      </c>
-      <c r="L471">
-        <v>1</v>
-      </c>
-      <c r="M471" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N471" t="str">
-        <v>2026-09-04 09:16:39</v>
-      </c>
-      <c r="O471" s="1">
-        <v>410000</v>
-      </c>
-      <c r="P471" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q471" t="str">
-        <v>일코 마산 하이마트 물류</v>
-      </c>
-      <c r="R471" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S471" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="str">
-        <v>T260903-00029</v>
-      </c>
-      <c r="B472" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C472" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D472" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E472" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F472" t="str">
-        <v>시흥ACP,인천ACP</v>
-      </c>
-      <c r="G472">
-        <v>2</v>
-      </c>
-      <c r="H472" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="I472" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="J472" t="str">
-        <v>2026-09-04 08:00</v>
-      </c>
-      <c r="K472" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L472">
-        <v>1</v>
-      </c>
-      <c r="M472" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N472" t="str">
-        <v>2026-09-03 18:24:00</v>
-      </c>
-      <c r="O472" s="1">
-        <v>230000</v>
-      </c>
-      <c r="P472" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q472" t="str">
-        <v/>
-      </c>
-      <c r="R472" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S472" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="str">
-        <v>T260903-00028</v>
-      </c>
-      <c r="B473" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C473" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D473" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E473" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F473" t="str">
-        <v>대전중구ACP,군산ACP</v>
-      </c>
-      <c r="G473">
-        <v>2</v>
-      </c>
-      <c r="H473" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="I473" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="J473" t="str">
-        <v>2026-09-04 07:00</v>
-      </c>
-      <c r="K473" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L473">
-        <v>1</v>
-      </c>
-      <c r="M473" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N473" t="str">
-        <v>2026-09-03 18:23:24</v>
-      </c>
-      <c r="O473" s="1">
-        <v>300000</v>
-      </c>
-      <c r="P473" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q473" t="str">
-        <v/>
-      </c>
-      <c r="R473" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S473" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="str">
-        <v>T260903-00027</v>
-      </c>
-      <c r="B474" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C474" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D474" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E474" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F474" t="str">
-        <v>안성ACP,용인ACP,화성ACP</v>
-      </c>
-      <c r="G474">
-        <v>3</v>
-      </c>
-      <c r="H474" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="I474" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="J474" t="str">
-        <v>2026-09-03 23:00</v>
-      </c>
-      <c r="K474" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L474">
-        <v>1</v>
-      </c>
-      <c r="M474" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N474" t="str">
-        <v>2026-09-03 18:22:50</v>
-      </c>
-      <c r="O474" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P474" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q474" t="str">
-        <v/>
-      </c>
-      <c r="R474" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S474" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="str">
-        <v>T260903-00026</v>
-      </c>
-      <c r="B475" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C475" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D475" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E475" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F475" t="str">
-        <v/>
-      </c>
-      <c r="G475">
-        <v>0</v>
-      </c>
-      <c r="H475" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="I475" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="J475" t="str">
-        <v>2026-09-03 21:00</v>
-      </c>
-      <c r="K475" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L475">
-        <v>1</v>
-      </c>
-      <c r="M475" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N475" t="str">
-        <v>2026-09-03 18:22:08</v>
-      </c>
-      <c r="O475" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P475" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q475" t="str">
-        <v/>
-      </c>
-      <c r="R475" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S475" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="str">
-        <v>T260903-00025</v>
-      </c>
-      <c r="B476" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C476" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D476" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E476" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F476" t="str">
-        <v/>
-      </c>
-      <c r="G476">
-        <v>0</v>
-      </c>
-      <c r="H476" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="I476" t="str">
-        <v>전북특별자치도 완주군 이서면 상개리 659-3 전주FDC</v>
-      </c>
-      <c r="J476" t="str">
-        <v>2026-09-03 22:00</v>
-      </c>
-      <c r="K476" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L476">
-        <v>1</v>
-      </c>
-      <c r="M476" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N476" t="str">
-        <v>2026-09-03 18:21:51</v>
-      </c>
-      <c r="O476" s="1">
-        <v>230000</v>
-      </c>
-      <c r="P476" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q476" t="str">
-        <v/>
-      </c>
-      <c r="R476" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S476" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="str">
-        <v>T260903-00024</v>
-      </c>
-      <c r="B477" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C477" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D477" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E477" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F477" t="str">
-        <v/>
-      </c>
-      <c r="G477">
-        <v>0</v>
-      </c>
-      <c r="H477" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="I477" t="str">
-        <v>인천 검단구 오류동 1653-2 인천FDC</v>
-      </c>
-      <c r="J477" t="str">
-        <v>2026-09-03 21:00</v>
-      </c>
-      <c r="K477" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L477">
-        <v>1</v>
-      </c>
-      <c r="M477" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N477" t="str">
-        <v>2026-09-03 18:21:35</v>
-      </c>
-      <c r="O477" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P477" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q477" t="str">
-        <v/>
-      </c>
-      <c r="R477" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S477" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="str">
-        <v>T260903-00023</v>
-      </c>
-      <c r="B478" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C478" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D478" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E478" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F478" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="G478">
-        <v>1</v>
-      </c>
-      <c r="H478" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="I478" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="J478" t="str">
-        <v>2026-09-03 22:00</v>
-      </c>
-      <c r="K478" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L478">
-        <v>1</v>
-      </c>
-      <c r="M478" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N478" t="str">
-        <v>2026-09-03 18:21:18</v>
-      </c>
-      <c r="O478" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P478" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q478" t="str">
-        <v/>
-      </c>
-      <c r="R478" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S478" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="str">
-        <v>T260903-00022</v>
-      </c>
-      <c r="B479" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C479" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D479" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E479" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F479" t="str">
-        <v>원주FDC(신규)</v>
-      </c>
-      <c r="G479">
-        <v>1</v>
-      </c>
-      <c r="H479" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="I479" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="J479" t="str">
-        <v>2026-09-03 22:00</v>
-      </c>
-      <c r="K479" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L479">
-        <v>1</v>
-      </c>
-      <c r="M479" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N479" t="str">
-        <v>2026-09-03 18:20:56</v>
-      </c>
-      <c r="O479" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P479" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q479" t="str">
-        <v/>
-      </c>
-      <c r="R479" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S479" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="str">
-        <v>T260903-00021</v>
-      </c>
-      <c r="B480" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C480" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D480" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E480" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F480" t="str">
-        <v>진주FDC,창원FDC</v>
-      </c>
-      <c r="G480">
-        <v>2</v>
-      </c>
-      <c r="H480" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="I480" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="J480" t="str">
-        <v>2026-09-03 23:00</v>
-      </c>
-      <c r="K480" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L480">
-        <v>1</v>
-      </c>
-      <c r="M480" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N480" t="str">
-        <v>2026-09-03 18:20:35</v>
-      </c>
-      <c r="O480" s="1">
-        <v>730000</v>
-      </c>
-      <c r="P480" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q480" t="str">
-        <v/>
-      </c>
-      <c r="R480" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S480" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="str">
-        <v>T260903-00020</v>
-      </c>
-      <c r="B481" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C481" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D481" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E481" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F481" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="G481">
-        <v>1</v>
-      </c>
-      <c r="H481" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="I481" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="J481" t="str">
-        <v>2026-09-03 22:00</v>
-      </c>
-      <c r="K481" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L481">
-        <v>1</v>
-      </c>
-      <c r="M481" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N481" t="str">
-        <v>2026-09-03 18:20:07</v>
-      </c>
-      <c r="O481" s="1">
-        <v>370000</v>
-      </c>
-      <c r="P481" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q481" t="str">
-        <v/>
-      </c>
-      <c r="R481" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S481" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="str">
-        <v>T260903-00019</v>
-      </c>
-      <c r="B482" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C482" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D482" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E482" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F482" t="str">
-        <v/>
-      </c>
-      <c r="G482">
-        <v>0</v>
-      </c>
-      <c r="H482" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="I482" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="J482" t="str">
-        <v>2026-09-03 23:00</v>
-      </c>
-      <c r="K482" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L482">
-        <v>1</v>
-      </c>
-      <c r="M482" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N482" t="str">
-        <v>2026-09-03 18:19:48</v>
-      </c>
-      <c r="O482" s="1">
-        <v>420000</v>
-      </c>
-      <c r="P482" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q482" t="str">
-        <v/>
-      </c>
-      <c r="R482" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S482" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="str">
-        <v>T260903-00018</v>
-      </c>
-      <c r="B483" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C483" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D483" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E483" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F483" t="str">
-        <v/>
-      </c>
-      <c r="G483">
-        <v>0</v>
-      </c>
-      <c r="H483" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="I483" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="J483" t="str">
-        <v>2026-09-03 21:00</v>
-      </c>
-      <c r="K483" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L483">
-        <v>1</v>
-      </c>
-      <c r="M483" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N483" t="str">
-        <v>2026-09-03 18:19:30</v>
-      </c>
-      <c r="O483" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P483" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q483" t="str">
-        <v/>
-      </c>
-      <c r="R483" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S483" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="str">
-        <v>T260903-00017</v>
-      </c>
-      <c r="B484" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C484" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D484" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E484" t="str">
-        <v>2026-09-03 19:00</v>
-      </c>
-      <c r="F484" t="str">
-        <v>구미FDC(신규)</v>
-      </c>
-      <c r="G484">
-        <v>1</v>
-      </c>
-      <c r="H484" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="I484" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="J484" t="str">
-        <v>2026-09-03 23:00</v>
-      </c>
-      <c r="K484" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L484">
-        <v>1</v>
-      </c>
-      <c r="M484" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N484" t="str">
-        <v>2026-09-03 18:19:12</v>
-      </c>
-      <c r="O484" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P484" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q484" t="str">
-        <v/>
-      </c>
-      <c r="R484" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S484" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="str">
-        <v>T260903-00016</v>
-      </c>
-      <c r="B485" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C485" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D485" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E485" t="str">
-        <v>2026-09-03 18:00</v>
-      </c>
-      <c r="F485" t="str">
-        <v/>
-      </c>
-      <c r="G485">
-        <v>0</v>
-      </c>
-      <c r="H485" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="I485" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="J485" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="K485" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L485">
-        <v>1</v>
-      </c>
-      <c r="M485" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N485" t="str">
-        <v>2026-09-03 17:43:12</v>
-      </c>
-      <c r="O485" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P485" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q485" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="R485" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S485" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="str">
-        <v>T260903-00015</v>
-      </c>
-      <c r="B486" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C486" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D486" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E486" t="str">
-        <v>2026-09-03 17:30</v>
-      </c>
-      <c r="F486" t="str">
-        <v/>
-      </c>
-      <c r="G486">
-        <v>0</v>
-      </c>
-      <c r="H486" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="I486" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="J486" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="K486" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L486">
-        <v>1</v>
-      </c>
-      <c r="M486" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N486" t="str">
-        <v>2026-09-03 17:10:21</v>
-      </c>
-      <c r="O486" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P486" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q486" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="R486" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S486" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="str">
-        <v>T260903-00014</v>
-      </c>
-      <c r="B487" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C487" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D487" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E487" t="str">
-        <v>2026-09-03 17:30</v>
-      </c>
-      <c r="F487" t="str">
-        <v/>
-      </c>
-      <c r="G487">
-        <v>0</v>
-      </c>
-      <c r="H487" t="str">
-        <v>공주 하이마트 물류</v>
-      </c>
-      <c r="I487" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="J487" t="str">
-        <v>2026-09-04 21:00</v>
-      </c>
-      <c r="K487" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L487">
-        <v>1</v>
-      </c>
-      <c r="M487" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N487" t="str">
-        <v>2026-09-03 17:09:57</v>
-      </c>
-      <c r="O487" s="1">
-        <v>220000</v>
-      </c>
-      <c r="P487" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q487" t="str">
-        <v>일코전자 공주 하이마트 물류</v>
-      </c>
-      <c r="R487" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S487" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="str">
-        <v>T260903-00013</v>
-      </c>
-      <c r="B488" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C488" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="D488" t="str">
-        <v>충남 아산시 음봉면 월랑리 440 천안FDC</v>
-      </c>
-      <c r="E488" t="str">
-        <v>2026-09-03 21:30</v>
-      </c>
-      <c r="F488" t="str">
-        <v/>
-      </c>
-      <c r="G488">
-        <v>0</v>
-      </c>
-      <c r="H488" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="I488" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="J488" t="str">
-        <v>2026-09-03 22:30</v>
-      </c>
-      <c r="K488" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L488">
-        <v>1</v>
-      </c>
-      <c r="M488" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N488" t="str">
-        <v>2026-09-03 16:23:31</v>
-      </c>
-      <c r="O488" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P488" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q488" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="R488" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S488" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="str">
-        <v>T260903-00012</v>
-      </c>
-      <c r="B489" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C489" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D489" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E489" t="str">
-        <v>2026-09-03 16:30</v>
-      </c>
-      <c r="F489" t="str">
-        <v/>
-      </c>
-      <c r="G489">
-        <v>0</v>
-      </c>
-      <c r="H489" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I489" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="J489" t="str">
-        <v>2026-09-03 17:30</v>
-      </c>
-      <c r="K489" t="str">
-        <v>1톤 카고/윙</v>
-      </c>
-      <c r="L489">
-        <v>1</v>
-      </c>
-      <c r="M489" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N489" t="str">
-        <v>2026-09-03 15:51:43</v>
-      </c>
-      <c r="O489" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P489" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q489" t="str">
-        <v/>
-      </c>
-      <c r="R489" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S489" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="str">
-        <v>T260903-00011</v>
-      </c>
-      <c r="B490" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C490" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D490" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E490" t="str">
-        <v>2026-09-03 17:30</v>
-      </c>
-      <c r="F490" t="str">
-        <v/>
-      </c>
-      <c r="G490">
-        <v>0</v>
-      </c>
-      <c r="H490" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="I490" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="J490" t="str">
-        <v>2026-09-03 18:30</v>
-      </c>
-      <c r="K490" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L490">
-        <v>1</v>
-      </c>
-      <c r="M490" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N490" t="str">
-        <v>2026-09-03 15:32:57</v>
-      </c>
-      <c r="O490" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P490" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q490" t="str">
-        <v/>
-      </c>
-      <c r="R490" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S490" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="str">
-        <v>T260903-00010</v>
-      </c>
-      <c r="B491" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C491" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="D491" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 821 곤지암FDC</v>
-      </c>
-      <c r="E491" t="str">
-        <v>2026-09-03 21:30</v>
-      </c>
-      <c r="F491" t="str">
-        <v/>
-      </c>
-      <c r="G491">
-        <v>0</v>
-      </c>
-      <c r="H491" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="I491" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="J491" t="str">
-        <v>2026-09-04 08:30</v>
-      </c>
-      <c r="K491" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L491">
-        <v>1</v>
-      </c>
-      <c r="M491" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N491" t="str">
-        <v>2026-09-03 15:32:28</v>
-      </c>
-      <c r="O491" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P491" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q491" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="R491" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S491" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="str">
-        <v>T260903-00009</v>
-      </c>
-      <c r="B492" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C492" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="D492" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5 김포FDC</v>
-      </c>
-      <c r="E492" t="str">
-        <v>2026-09-03 09:00</v>
-      </c>
-      <c r="F492" t="str">
-        <v/>
-      </c>
-      <c r="G492">
-        <v>0</v>
-      </c>
-      <c r="H492" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="I492" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="J492" t="str">
-        <v>2026-09-03 11:30</v>
-      </c>
-      <c r="K492" t="str">
-        <v>5톤 카고</v>
-      </c>
-      <c r="L492">
-        <v>1</v>
-      </c>
-      <c r="M492" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N492" t="str">
-        <v>2026-09-03 15:31:34</v>
-      </c>
-      <c r="O492" s="1">
-        <v>250000</v>
-      </c>
-      <c r="P492" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q492" t="str">
-        <v>반품회수</v>
-      </c>
-      <c r="R492" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S492" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="str">
-        <v>T260903-00008</v>
-      </c>
-      <c r="B493" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C493" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="D493" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="E493" t="str">
-        <v>2026-09-03 11:00</v>
-      </c>
-      <c r="F493" t="str">
-        <v/>
-      </c>
-      <c r="G493">
-        <v>0</v>
-      </c>
-      <c r="H493" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I493" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J493" t="str">
-        <v>2026-09-03 13:30</v>
-      </c>
-      <c r="K493" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L493">
-        <v>1</v>
-      </c>
-      <c r="M493" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N493" t="str">
-        <v>2026-09-03 15:30:52</v>
-      </c>
-      <c r="O493" s="1">
-        <v>120000</v>
-      </c>
-      <c r="P493" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q493" t="str">
-        <v>거래처비용청구(3대)</v>
-      </c>
-      <c r="R493" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S493" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="str">
-        <v>T260903-00007</v>
-      </c>
-      <c r="B494" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C494" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D494" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E494" t="str">
-        <v>2026-09-03 14:30</v>
-      </c>
-      <c r="F494" t="str">
-        <v/>
-      </c>
-      <c r="G494">
-        <v>0</v>
-      </c>
-      <c r="H494" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I494" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J494" t="str">
-        <v>2026-09-03 15:30</v>
-      </c>
-      <c r="K494" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L494">
-        <v>1</v>
-      </c>
-      <c r="M494" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N494" t="str">
-        <v>2026-09-03 15:30:00</v>
-      </c>
-      <c r="O494" s="1">
-        <v>70000</v>
-      </c>
-      <c r="P494" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q494" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="R494" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S494" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="str">
-        <v>T260903-00006</v>
-      </c>
-      <c r="B495" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C495" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D495" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E495" t="str">
-        <v>2026-09-03 10:00</v>
-      </c>
-      <c r="F495" t="str">
-        <v/>
-      </c>
-      <c r="G495">
-        <v>0</v>
-      </c>
-      <c r="H495" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I495" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J495" t="str">
-        <v>2026-09-03 13:30</v>
-      </c>
-      <c r="K495" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L495">
-        <v>1</v>
-      </c>
-      <c r="M495" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N495" t="str">
-        <v>2026-09-03 15:29:14</v>
-      </c>
-      <c r="O495" s="1">
-        <v>160000</v>
-      </c>
-      <c r="P495" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q495" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="R495" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S495" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="str">
-        <v>T260903-00005</v>
-      </c>
-      <c r="B496" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C496" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D496" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E496" t="str">
-        <v>2026-09-03 13:50</v>
-      </c>
-      <c r="F496" t="str">
-        <v/>
-      </c>
-      <c r="G496">
-        <v>0</v>
-      </c>
-      <c r="H496" t="str">
-        <v>펠리체산후조리원하이얼</v>
-      </c>
-      <c r="I496" t="str">
-        <v>경기 화성시 만세구 꽃내음1길 19-22 펠리체산후조리원 하이얼</v>
-      </c>
-      <c r="J496" t="str">
-        <v>2026-09-03 16:00</v>
-      </c>
-      <c r="K496" t="str">
-        <v>1.5톤 카고</v>
-      </c>
-      <c r="L496">
-        <v>1</v>
-      </c>
-      <c r="M496" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N496" t="str">
-        <v>2026-09-03 13:37:58</v>
-      </c>
-      <c r="O496" s="1">
-        <v>110000</v>
-      </c>
-      <c r="P496" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q496" t="str">
-        <v/>
-      </c>
-      <c r="R496" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S496" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="str">
-        <v>T260903-00004</v>
-      </c>
-      <c r="B497" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C497" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D497" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E497" t="str">
-        <v>2026-09-03 16:00</v>
-      </c>
-      <c r="F497" t="str">
-        <v/>
-      </c>
-      <c r="G497">
-        <v>0</v>
-      </c>
-      <c r="H497" t="str">
-        <v>광주 하이마트 물류</v>
-      </c>
-      <c r="I497" t="str">
-        <v>전남 장성군 황룡면 신기길 41 광주 하이마트 물류</v>
-      </c>
-      <c r="J497" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="K497" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L497">
-        <v>1</v>
-      </c>
-      <c r="M497" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N497" t="str">
-        <v>2026-09-03 13:14:56</v>
-      </c>
-      <c r="O497" s="1">
-        <v>400000</v>
-      </c>
-      <c r="P497" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q497" t="str">
-        <v>일코전자 광주 하이마트 물류</v>
-      </c>
-      <c r="R497" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S497" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="str">
-        <v>T260903-00003</v>
-      </c>
-      <c r="B498" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C498" t="str">
-        <v>위니온 안성HUB</v>
-      </c>
-      <c r="D498" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E498" t="str">
-        <v>2026-09-03 15:00</v>
-      </c>
-      <c r="F498" t="str">
-        <v/>
-      </c>
-      <c r="G498">
-        <v>0</v>
-      </c>
-      <c r="H498" t="str">
-        <v>대구 하이마트 물류</v>
-      </c>
-      <c r="I498" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="J498" t="str">
-        <v>2026-09-04 09:00</v>
-      </c>
-      <c r="K498" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L498">
-        <v>1</v>
-      </c>
-      <c r="M498" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N498" t="str">
-        <v>2026-09-03 10:24:04</v>
-      </c>
-      <c r="O498" s="1">
-        <v>340000</v>
-      </c>
-      <c r="P498" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q498" t="str">
-        <v>일코전자 대구 하이마트 물류</v>
-      </c>
-      <c r="R498" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S498" t="str">
-        <v>일코전자</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="str">
-        <v>T260903-00002</v>
-      </c>
-      <c r="B499" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C499" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D499" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E499" t="str">
-        <v>2026-09-03 10:10</v>
-      </c>
-      <c r="F499" t="str">
-        <v/>
-      </c>
-      <c r="G499">
-        <v>0</v>
-      </c>
-      <c r="H499" t="str">
-        <v>마이디어 늘품마루</v>
-      </c>
-      <c r="I499" t="str">
-        <v>경기 이천시 백사면 지읍로 54 지하 2층 33번 도크</v>
-      </c>
-      <c r="J499" t="str">
-        <v>2026-09-03 11:30</v>
-      </c>
-      <c r="K499" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="L499">
-        <v>1</v>
-      </c>
-      <c r="M499" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N499" t="str">
-        <v>2026-09-03 10:23:19</v>
-      </c>
-      <c r="O499" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P499" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q499" t="str">
-        <v>마이디어 늘품마루</v>
-      </c>
-      <c r="R499" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S499" t="str">
-        <v>마이디어</v>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="str">
-        <v>T260903-00001</v>
-      </c>
-      <c r="B500" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C500" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D500" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E500" t="str">
-        <v>2026-09-03 09:00</v>
-      </c>
-      <c r="F500" t="str">
-        <v/>
-      </c>
-      <c r="G500">
-        <v>0</v>
-      </c>
-      <c r="H500" t="str">
-        <v>마이디어 늘품마루</v>
-      </c>
-      <c r="I500" t="str">
-        <v>경기 이천시 백사면 지읍로 54 지하 2층 33번 도크</v>
-      </c>
-      <c r="J500" t="str">
-        <v>2026-09-03 11:00</v>
-      </c>
-      <c r="K500" t="str">
-        <v>5톤축 윙바디</v>
-      </c>
-      <c r="L500">
-        <v>1</v>
-      </c>
-      <c r="M500" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N500" t="str">
-        <v>2026-09-03 09:06:29</v>
-      </c>
-      <c r="O500" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P500" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q500" t="str">
-        <v>마이디어 늘품마루</v>
-      </c>
-      <c r="R500" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S500" t="str">
-        <v>마이디어</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="str">
-        <v>T260902-00030</v>
-      </c>
-      <c r="B501" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C501" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D501" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E501" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F501" t="str">
-        <v>대전중구ACP</v>
-      </c>
-      <c r="G501">
-        <v>1</v>
-      </c>
-      <c r="H501" t="str">
-        <v>대전대덕ACP</v>
-      </c>
-      <c r="I501" t="str">
-        <v>대전 대덕구 석봉로38번길 12 대전대덕ACP</v>
-      </c>
-      <c r="J501" t="str">
-        <v>2026-09-03 06:00</v>
-      </c>
-      <c r="K501" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L501">
-        <v>1</v>
-      </c>
-      <c r="M501" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N501" t="str">
-        <v>2026-09-02 19:24:10</v>
-      </c>
-      <c r="O501" s="1">
-        <v>170000</v>
-      </c>
-      <c r="P501" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q501" t="str">
-        <v/>
-      </c>
-      <c r="R501" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S501" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="str">
-        <v>T260902-00029</v>
-      </c>
-      <c r="B502" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C502" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D502" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E502" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F502" t="str">
-        <v>인천ACP</v>
-      </c>
-      <c r="G502">
-        <v>1</v>
-      </c>
-      <c r="H502" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="I502" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="J502" t="str">
-        <v>2026-09-03 07:00</v>
-      </c>
-      <c r="K502" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L502">
-        <v>1</v>
-      </c>
-      <c r="M502" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N502" t="str">
-        <v>2026-09-02 19:23:42</v>
-      </c>
-      <c r="O502" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P502" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q502" t="str">
-        <v/>
-      </c>
-      <c r="R502" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S502" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="str">
-        <v>T260902-00028</v>
-      </c>
-      <c r="B503" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C503" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D503" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E503" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F503" t="str">
-        <v>이천ACP,원주ACP</v>
-      </c>
-      <c r="G503">
-        <v>2</v>
-      </c>
-      <c r="H503" t="str">
-        <v>춘천ACP</v>
-      </c>
-      <c r="I503" t="str">
-        <v>강원특별자치도 춘천시 동내면 대룡산길 100 춘천ACP</v>
-      </c>
-      <c r="J503" t="str">
-        <v>2026-09-03 06:00</v>
-      </c>
-      <c r="K503" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L503">
-        <v>1</v>
-      </c>
-      <c r="M503" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N503" t="str">
-        <v>2026-09-02 19:23:13</v>
-      </c>
-      <c r="O503" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P503" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q503" t="str">
-        <v/>
-      </c>
-      <c r="R503" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S503" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="str">
-        <v>T260902-00027</v>
-      </c>
-      <c r="B504" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C504" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D504" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E504" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F504" t="str">
-        <v>군산ACP</v>
-      </c>
-      <c r="G504">
-        <v>1</v>
-      </c>
-      <c r="H504" t="str">
-        <v>전주ACP</v>
-      </c>
-      <c r="I504" t="str">
-        <v>전북특별자치도 전주시 덕진구 용덕길 5-13 전주ACP</v>
-      </c>
-      <c r="J504" t="str">
-        <v>2026-09-03 08:00</v>
-      </c>
-      <c r="K504" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L504">
-        <v>1</v>
-      </c>
-      <c r="M504" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N504" t="str">
-        <v>2026-09-02 19:22:37</v>
-      </c>
-      <c r="O504" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P504" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q504" t="str">
-        <v/>
-      </c>
-      <c r="R504" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S504" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="str">
-        <v>T260902-00026</v>
-      </c>
-      <c r="B505" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C505" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D505" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E505" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F505" t="str">
-        <v>용인ACP,화성ACP</v>
-      </c>
-      <c r="G505">
-        <v>2</v>
-      </c>
-      <c r="H505" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="I505" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="J505" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K505" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L505">
-        <v>1</v>
-      </c>
-      <c r="M505" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N505" t="str">
-        <v>2026-09-02 19:22:09</v>
-      </c>
-      <c r="O505" s="1">
-        <v>220000</v>
-      </c>
-      <c r="P505" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q505" t="str">
-        <v/>
-      </c>
-      <c r="R505" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S505" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="str">
-        <v>T260902-00025</v>
-      </c>
-      <c r="B506" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C506" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D506" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E506" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F506" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="G506">
-        <v>1</v>
-      </c>
-      <c r="H506" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="I506" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="J506" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K506" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L506">
-        <v>1</v>
-      </c>
-      <c r="M506" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N506" t="str">
-        <v>2026-09-02 19:21:37</v>
-      </c>
-      <c r="O506" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P506" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q506" t="str">
-        <v/>
-      </c>
-      <c r="R506" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S506" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="str">
-        <v>T260902-00024</v>
-      </c>
-      <c r="B507" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C507" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D507" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E507" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F507" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="G507">
-        <v>1</v>
-      </c>
-      <c r="H507" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="I507" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="J507" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K507" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L507">
-        <v>1</v>
-      </c>
-      <c r="M507" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N507" t="str">
-        <v>2026-09-02 19:21:17</v>
-      </c>
-      <c r="O507" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P507" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q507" t="str">
-        <v/>
-      </c>
-      <c r="R507" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S507" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="str">
-        <v>T260902-00023</v>
-      </c>
-      <c r="B508" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C508" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D508" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E508" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F508" t="str">
-        <v>원주FDC(신규)</v>
-      </c>
-      <c r="G508">
-        <v>1</v>
-      </c>
-      <c r="H508" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="I508" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="J508" t="str">
-        <v>2026-09-02 22:00</v>
-      </c>
-      <c r="K508" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L508">
-        <v>1</v>
-      </c>
-      <c r="M508" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N508" t="str">
-        <v>2026-09-02 19:20:40</v>
-      </c>
-      <c r="O508" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P508" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q508" t="str">
-        <v/>
-      </c>
-      <c r="R508" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S508" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="str">
-        <v>T260902-00022</v>
-      </c>
-      <c r="B509" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C509" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D509" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E509" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F509" t="str">
-        <v>진주FDC,창원FDC</v>
-      </c>
-      <c r="G509">
-        <v>2</v>
-      </c>
-      <c r="H509" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="I509" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="J509" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K509" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L509">
-        <v>1</v>
-      </c>
-      <c r="M509" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N509" t="str">
-        <v>2026-09-02 19:20:16</v>
-      </c>
-      <c r="O509" s="1">
-        <v>730000</v>
-      </c>
-      <c r="P509" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q509" t="str">
-        <v/>
-      </c>
-      <c r="R509" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S509" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="str">
-        <v>T260902-00021</v>
-      </c>
-      <c r="B510" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C510" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D510" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E510" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F510" t="str">
-        <v/>
-      </c>
-      <c r="G510">
-        <v>0</v>
-      </c>
-      <c r="H510" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="I510" t="str">
-        <v>경기도 남양주시 오남읍 오남리 804 남양주FDC</v>
-      </c>
-      <c r="J510" t="str">
-        <v>2026-09-02 21:00</v>
-      </c>
-      <c r="K510" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L510">
-        <v>1</v>
-      </c>
-      <c r="M510" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N510" t="str">
-        <v>2026-09-02 19:19:46</v>
-      </c>
-      <c r="O510" s="1">
-        <v>250000</v>
-      </c>
-      <c r="P510" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q510" t="str">
-        <v/>
-      </c>
-      <c r="R510" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S510" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="str">
-        <v>T260902-00020</v>
-      </c>
-      <c r="B511" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C511" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D511" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E511" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F511" t="str">
-        <v/>
-      </c>
-      <c r="G511">
-        <v>0</v>
-      </c>
-      <c r="H511" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="I511" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="J511" t="str">
-        <v>2026-09-02 21:00</v>
-      </c>
-      <c r="K511" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L511">
-        <v>1</v>
-      </c>
-      <c r="M511" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N511" t="str">
-        <v>2026-09-02 19:19:30</v>
-      </c>
-      <c r="O511" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P511" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q511" t="str">
-        <v/>
-      </c>
-      <c r="R511" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S511" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="str">
-        <v>T260902-00019</v>
-      </c>
-      <c r="B512" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C512" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D512" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E512" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F512" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="G512">
-        <v>1</v>
-      </c>
-      <c r="H512" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="I512" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="J512" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K512" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L512">
-        <v>1</v>
-      </c>
-      <c r="M512" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N512" t="str">
-        <v>2026-09-02 19:19:13</v>
-      </c>
-      <c r="O512" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P512" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q512" t="str">
-        <v/>
-      </c>
-      <c r="R512" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S512" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="str">
-        <v>T260902-00018</v>
-      </c>
-      <c r="B513" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C513" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D513" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E513" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F513" t="str">
-        <v/>
-      </c>
-      <c r="G513">
-        <v>0</v>
-      </c>
-      <c r="H513" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="I513" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="J513" t="str">
-        <v>2026-09-02 21:00</v>
-      </c>
-      <c r="K513" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L513">
-        <v>1</v>
-      </c>
-      <c r="M513" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N513" t="str">
-        <v>2026-09-02 19:18:47</v>
-      </c>
-      <c r="O513" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P513" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q513" t="str">
-        <v/>
-      </c>
-      <c r="R513" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S513" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="str">
-        <v>T260902-00017</v>
-      </c>
-      <c r="B514" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C514" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D514" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E514" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F514" t="str">
-        <v>구미FDC(신규)</v>
-      </c>
-      <c r="G514">
-        <v>1</v>
-      </c>
-      <c r="H514" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="I514" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="J514" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K514" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L514">
-        <v>1</v>
-      </c>
-      <c r="M514" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N514" t="str">
-        <v>2026-09-02 19:17:37</v>
-      </c>
-      <c r="O514" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P514" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q514" t="str">
-        <v/>
-      </c>
-      <c r="R514" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S514" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="str">
-        <v>T260902-00016</v>
-      </c>
-      <c r="B515" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C515" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D515" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E515" t="str">
-        <v>2026-09-02 19:00</v>
-      </c>
-      <c r="F515" t="str">
-        <v>강릉ACP</v>
-      </c>
-      <c r="G515">
-        <v>1</v>
-      </c>
-      <c r="H515" t="str">
-        <v>강릉FDC</v>
-      </c>
-      <c r="I515" t="str">
-        <v>강릉시 구정면 구정옥봉길 143-5 강릉FDC</v>
-      </c>
-      <c r="J515" t="str">
-        <v>2026-09-02 23:00</v>
-      </c>
-      <c r="K515" t="str">
-        <v>2.5톤 윙바디</v>
-      </c>
-      <c r="L515">
-        <v>1</v>
-      </c>
-      <c r="M515" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N515" t="str">
-        <v>2026-09-02 19:16:53</v>
-      </c>
-      <c r="O515" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P515" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q515" t="str">
-        <v/>
-      </c>
-      <c r="R515" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S515" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="str">
-        <v>T260902-00015</v>
-      </c>
-      <c r="B516" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C516" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D516" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E516" t="str">
-        <v>2026-09-02 18:10</v>
-      </c>
-      <c r="F516" t="str">
-        <v/>
-      </c>
-      <c r="G516">
-        <v>0</v>
-      </c>
-      <c r="H516" t="str">
-        <v>양산 하이마트 하이얼</v>
-      </c>
-      <c r="I516" t="str">
-        <v>경남 양산시 물금읍 제방로 125 양산 하이마트 하이얼</v>
-      </c>
-      <c r="J516" t="str">
-        <v>2026-09-03 21:30</v>
-      </c>
-      <c r="K516" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L516">
-        <v>1</v>
-      </c>
-      <c r="M516" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N516" t="str">
-        <v>2026-09-02 17:49:53</v>
-      </c>
-      <c r="O516" s="1">
-        <v>340000</v>
-      </c>
-      <c r="P516" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q516" t="str">
-        <v>하이얼 양산 하이마트 물류</v>
-      </c>
-      <c r="R516" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S516" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="str">
-        <v>T260902-00014</v>
-      </c>
-      <c r="B517" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C517" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D517" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E517" t="str">
-        <v>2026-09-02 17:30</v>
-      </c>
-      <c r="F517" t="str">
-        <v/>
-      </c>
-      <c r="G517">
-        <v>0</v>
-      </c>
-      <c r="H517" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="I517" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="J517" t="str">
-        <v>2026-09-02 18:30</v>
-      </c>
-      <c r="K517" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L517">
-        <v>1</v>
-      </c>
-      <c r="M517" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N517" t="str">
-        <v>2026-09-02 17:27:54</v>
-      </c>
-      <c r="O517" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P517" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q517" t="str">
-        <v/>
-      </c>
-      <c r="R517" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S517" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="str">
-        <v>T260902-00013</v>
-      </c>
-      <c r="B518" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C518" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="D518" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="E518" t="str">
-        <v>2026-09-02 11:00</v>
-      </c>
-      <c r="F518" t="str">
-        <v/>
-      </c>
-      <c r="G518">
-        <v>0</v>
-      </c>
-      <c r="H518" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I518" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J518" t="str">
-        <v>2026-09-02 13:30</v>
-      </c>
-      <c r="K518" t="str">
-        <v>1톤 기타차량</v>
-      </c>
-      <c r="L518">
-        <v>1</v>
-      </c>
-      <c r="M518" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N518" t="str">
-        <v>2026-09-02 17:27:24</v>
-      </c>
-      <c r="O518" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P518" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q518" t="str">
-        <v>거래처비용청구(1대)</v>
-      </c>
-      <c r="R518" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S518" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="str">
-        <v>T260902-00012</v>
-      </c>
-      <c r="B519" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C519" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D519" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E519" t="str">
-        <v>2026-09-02 14:30</v>
-      </c>
-      <c r="F519" t="str">
-        <v/>
-      </c>
-      <c r="G519">
-        <v>0</v>
-      </c>
-      <c r="H519" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I519" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J519" t="str">
-        <v>2026-09-02 15:30</v>
-      </c>
-      <c r="K519" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L519">
-        <v>1</v>
-      </c>
-      <c r="M519" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N519" t="str">
-        <v>2026-09-02 17:26:30</v>
-      </c>
-      <c r="O519" s="1">
-        <v>70000</v>
-      </c>
-      <c r="P519" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q519" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="R519" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S519" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="str">
-        <v>T260902-00011</v>
-      </c>
-      <c r="B520" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C520" t="str">
-        <v>듀오백</v>
-      </c>
-      <c r="D520" t="str">
-        <v>인천 서구 가재울로32번길 27 듀오백코리아</v>
-      </c>
-      <c r="E520" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="F520" t="str">
-        <v/>
-      </c>
-      <c r="G520">
-        <v>0</v>
-      </c>
-      <c r="H520" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I520" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J520" t="str">
-        <v>2026-09-02 13:30</v>
-      </c>
-      <c r="K520" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L520">
-        <v>1</v>
-      </c>
-      <c r="M520" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N520" t="str">
-        <v>2026-09-02 17:25:43</v>
-      </c>
-      <c r="O520" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P520" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q520" t="str">
-        <v>듀오백 외주사입고</v>
-      </c>
-      <c r="R520" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S520" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="str">
-        <v>T260902-00010</v>
-      </c>
-      <c r="B521" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C521" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D521" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E521" t="str">
-        <v>2026-09-02 17:10</v>
-      </c>
-      <c r="F521" t="str">
-        <v/>
-      </c>
-      <c r="G521">
-        <v>0</v>
-      </c>
-      <c r="H521" t="str">
-        <v>마산 하이마트 하이얼</v>
-      </c>
-      <c r="I521" t="str">
-        <v>경남 함안군 법수면 법수로 546 마산 하이마트 하이얼</v>
-      </c>
-      <c r="J521" t="str">
-        <v>2026-09-03 09:30</v>
-      </c>
-      <c r="K521" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L521">
-        <v>1</v>
-      </c>
-      <c r="M521" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N521" t="str">
-        <v>2026-09-02 16:04:12</v>
-      </c>
-      <c r="O521" s="1">
-        <v>340000</v>
-      </c>
-      <c r="P521" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q521" t="str">
-        <v>하이얼  마산 하이마트 물류</v>
-      </c>
-      <c r="R521" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S521" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="str">
-        <v>T260902-00009</v>
-      </c>
-      <c r="B522" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C522" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D522" t="str">
-        <v>경기 안성시 죽산면 걸미로 723-9 안성FC</v>
-      </c>
-      <c r="E522" t="str">
-        <v>2026-09-02 16:30</v>
-      </c>
-      <c r="F522" t="str">
-        <v/>
-      </c>
-      <c r="G522">
-        <v>0</v>
-      </c>
-      <c r="H522" t="str">
-        <v>경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="I522" t="str">
-        <v>충북 청주시 서원구 남이면 가마길 49-35 경동택배 청주서원남이가마258 영업소</v>
-      </c>
-      <c r="J522" t="str">
-        <v>2026-09-02 17:30</v>
-      </c>
-      <c r="K522" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L522">
-        <v>1</v>
-      </c>
-      <c r="M522" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N522" t="str">
-        <v>2026-09-02 16:01:28</v>
-      </c>
-      <c r="O522" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P522" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q522" t="str">
-        <v/>
-      </c>
-      <c r="R522" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S522" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="str">
-        <v>T260902-00008</v>
-      </c>
-      <c r="B523" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C523" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D523" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E523" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="F523" t="str">
-        <v/>
-      </c>
-      <c r="G523">
-        <v>0</v>
-      </c>
-      <c r="H523" t="str">
-        <v>이천 하이마트 하이얼</v>
-      </c>
-      <c r="I523" t="str">
-        <v>경기 이천시 마장면 중부대로533번길 8 이천 하이마트 하이얼</v>
-      </c>
-      <c r="J523" t="str">
-        <v>2026-09-02 15:00</v>
-      </c>
-      <c r="K523" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L523">
-        <v>1</v>
-      </c>
-      <c r="M523" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N523" t="str">
-        <v>2026-09-02 10:54:59</v>
-      </c>
-      <c r="O523" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P523" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q523" t="str">
-        <v>하이얼 이천 하이마트 물류</v>
-      </c>
-      <c r="R523" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S523" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="str">
-        <v>T260902-00007</v>
-      </c>
-      <c r="B524" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C524" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D524" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E524" t="str">
-        <v>2026-09-02 09:40</v>
-      </c>
-      <c r="F524" t="str">
-        <v/>
-      </c>
-      <c r="G524">
-        <v>0</v>
-      </c>
-      <c r="H524" t="str">
-        <v>화성 하이마트 하이얼</v>
-      </c>
-      <c r="I524" t="str">
-        <v>경기 화성시 장안면 수촌리 22-19 화성 하이마트 하이얼</v>
-      </c>
-      <c r="J524" t="str">
-        <v>2026-09-02 03:00</v>
-      </c>
-      <c r="K524" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L524">
-        <v>1</v>
-      </c>
-      <c r="M524" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N524" t="str">
-        <v>2026-09-02 10:50:30</v>
-      </c>
-      <c r="O524" s="1">
-        <v>140000</v>
-      </c>
-      <c r="P524" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q524" t="str">
-        <v>히이얼 화성 하이마트 물류</v>
-      </c>
-      <c r="R524" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S524" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="str">
-        <v>T260902-00006</v>
-      </c>
-      <c r="B525" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C525" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D525" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E525" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F525" t="str">
-        <v/>
-      </c>
-      <c r="G525">
-        <v>0</v>
-      </c>
-      <c r="H525" t="str">
-        <v>인천 하이마트 하이얼</v>
-      </c>
-      <c r="I525" t="str">
-        <v>인천 중구 서해대로94번길 132 인천 하이마트 하이얼</v>
-      </c>
-      <c r="J525" t="str">
-        <v>2026-09-02 03:00</v>
-      </c>
-      <c r="K525" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L525">
-        <v>1</v>
-      </c>
-      <c r="M525" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N525" t="str">
-        <v>2026-09-02 10:36:26</v>
-      </c>
-      <c r="O525" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P525" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q525" t="str">
-        <v>하이얼 인천 하이마트 물류</v>
-      </c>
-      <c r="R525" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S525" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="str">
-        <v>T260902-00005</v>
-      </c>
-      <c r="B526" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C526" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D526" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E526" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F526" t="str">
-        <v/>
-      </c>
-      <c r="G526">
-        <v>0</v>
-      </c>
-      <c r="H526" t="str">
-        <v>아임테크날러지 창고</v>
-      </c>
-      <c r="I526" t="str">
-        <v>경기 김포시 통진읍 월하로479번길 32-42 가동, 나동</v>
-      </c>
-      <c r="J526" t="str">
-        <v>2026-09-02 11:00</v>
-      </c>
-      <c r="K526" t="str">
-        <v>3.5톤 윙바디</v>
-      </c>
-      <c r="L526">
-        <v>1</v>
-      </c>
-      <c r="M526" t="str">
-        <v>차순권</v>
-      </c>
-      <c r="N526" t="str">
-        <v>2026-09-02 09:52:58</v>
-      </c>
-      <c r="O526" s="1">
-        <v>230000</v>
-      </c>
-      <c r="P526" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q526" t="str">
-        <v>아임테크 날러지 회수2, 가용 1파렛트 출하</v>
-      </c>
-      <c r="R526" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S526" t="str">
-        <v>아임테크날러지</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="str">
-        <v>T260902-00004</v>
-      </c>
-      <c r="B527" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C527" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D527" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E527" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F527" t="str">
-        <v/>
-      </c>
-      <c r="G527">
-        <v>0</v>
-      </c>
-      <c r="H527" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I527" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J527" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="K527" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L527">
-        <v>1</v>
-      </c>
-      <c r="M527" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N527" t="str">
-        <v>2026-09-02 09:49:55</v>
-      </c>
-      <c r="O527" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P527" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q527" t="str">
-        <v>중산물산 회수품</v>
-      </c>
-      <c r="R527" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S527" t="str">
-        <v>중산물산</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="str">
-        <v>T260902-00003</v>
-      </c>
-      <c r="B528" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C528" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D528" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E528" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F528" t="str">
-        <v/>
-      </c>
-      <c r="G528">
-        <v>0</v>
-      </c>
-      <c r="H528" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I528" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J528" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="K528" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L528">
-        <v>1</v>
-      </c>
-      <c r="M528" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N528" t="str">
-        <v>2026-09-02 09:37:44</v>
-      </c>
-      <c r="O528" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P528" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q528" t="str">
-        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
-      </c>
-      <c r="R528" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S528" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="str">
-        <v>T260902-00002</v>
-      </c>
-      <c r="B529" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C529" t="str">
-        <v>청주ARC</v>
-      </c>
-      <c r="D529" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 (주)위니온 로지스</v>
-      </c>
-      <c r="E529" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="F529" t="str">
-        <v/>
-      </c>
-      <c r="G529">
-        <v>0</v>
-      </c>
-      <c r="H529" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I529" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J529" t="str">
-        <v>2026-09-02 10:00</v>
-      </c>
-      <c r="K529" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L529">
-        <v>1</v>
-      </c>
-      <c r="M529" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N529" t="str">
-        <v>2026-09-02 09:37:02</v>
-      </c>
-      <c r="O529" s="1">
-        <v>180000</v>
-      </c>
-      <c r="P529" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q529" t="str">
-        <v>가용재고 이동 / 간선비용 거래처별 1/N 청구예정</v>
-      </c>
-      <c r="R529" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S529" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="str">
-        <v>T260902-00001</v>
-      </c>
-      <c r="B530" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C530" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D530" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E530" t="str">
-        <v>2026-09-02 09:50</v>
-      </c>
-      <c r="F530" t="str">
-        <v/>
-      </c>
-      <c r="G530">
-        <v>0</v>
-      </c>
-      <c r="H530" t="str">
-        <v>아임테크</v>
-      </c>
-      <c r="I530" t="str">
-        <v>경기 김포시 통진읍 귀전리 537-4 아임테크</v>
-      </c>
-      <c r="J530" t="str">
-        <v>2026-09-02 11:00</v>
-      </c>
-      <c r="K530" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L530">
-        <v>1</v>
-      </c>
-      <c r="M530" t="str">
-        <v>임태양</v>
-      </c>
-      <c r="N530" t="str">
-        <v>2026-09-02 09:33:24</v>
-      </c>
-      <c r="O530" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P530" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q530" t="str">
-        <v>아임테크날러지 전량 출하</v>
-      </c>
-      <c r="R530" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S530" t="str">
-        <v>아임테크날러지</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="str">
-        <v>T260901-00019</v>
-      </c>
-      <c r="B531" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C531" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D531" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E531" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F531" t="str">
-        <v>시흥ACP,인천ACP</v>
-      </c>
-      <c r="G531">
-        <v>2</v>
-      </c>
-      <c r="H531" t="str">
-        <v>파주ACP</v>
-      </c>
-      <c r="I531" t="str">
-        <v>경기 파주시 조리읍 명봉산로 149 파주ACP</v>
-      </c>
-      <c r="J531" t="str">
-        <v>2026-09-02 07:00</v>
-      </c>
-      <c r="K531" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L531">
-        <v>1</v>
-      </c>
-      <c r="M531" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N531" t="str">
-        <v>2026-09-01 19:27:06</v>
-      </c>
-      <c r="O531" s="1">
-        <v>230000</v>
-      </c>
-      <c r="P531" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q531" t="str">
-        <v/>
-      </c>
-      <c r="R531" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S531" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="str">
-        <v>T260901-00018</v>
-      </c>
-      <c r="B532" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C532" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D532" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E532" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F532" t="str">
-        <v>대전중구ACP,대전대덕ACP</v>
-      </c>
-      <c r="G532">
-        <v>2</v>
-      </c>
-      <c r="H532" t="str">
-        <v>군산ACP</v>
-      </c>
-      <c r="I532" t="str">
-        <v>전북특별자치도 군산시 구암3.1로 60 군산ACP</v>
-      </c>
-      <c r="J532" t="str">
-        <v>2026-09-02 07:00</v>
-      </c>
-      <c r="K532" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L532">
-        <v>1</v>
-      </c>
-      <c r="M532" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N532" t="str">
-        <v>2026-09-01 19:26:35</v>
-      </c>
-      <c r="O532" s="1">
-        <v>300000</v>
-      </c>
-      <c r="P532" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q532" t="str">
-        <v/>
-      </c>
-      <c r="R532" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S532" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="str">
-        <v>T260901-00017</v>
-      </c>
-      <c r="B533" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C533" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D533" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E533" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F533" t="str">
-        <v>안성ACP,화성ACP,용인ACP</v>
-      </c>
-      <c r="G533">
-        <v>3</v>
-      </c>
-      <c r="H533" t="str">
-        <v>구리ACP</v>
-      </c>
-      <c r="I533" t="str">
-        <v>경기 구리시 사노동 110 구리ACP</v>
-      </c>
-      <c r="J533" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K533" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L533">
-        <v>1</v>
-      </c>
-      <c r="M533" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N533" t="str">
-        <v>2026-09-01 19:25:58</v>
-      </c>
-      <c r="O533" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P533" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q533" t="str">
-        <v/>
-      </c>
-      <c r="R533" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S533" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="str">
-        <v>T260901-00016</v>
-      </c>
-      <c r="B534" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C534" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D534" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E534" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F534" t="str">
-        <v/>
-      </c>
-      <c r="G534">
-        <v>0</v>
-      </c>
-      <c r="H534" t="str">
-        <v>화성FDC(신규)</v>
-      </c>
-      <c r="I534" t="str">
-        <v>경기도 화성시 장안면 3.1만세로 506-21 화성FDC(신규)</v>
-      </c>
-      <c r="J534" t="str">
-        <v>2026-09-01 21:00</v>
-      </c>
-      <c r="K534" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L534">
-        <v>1</v>
-      </c>
-      <c r="M534" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N534" t="str">
-        <v>2026-09-01 19:25:13</v>
-      </c>
-      <c r="O534" s="1">
-        <v>240000</v>
-      </c>
-      <c r="P534" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q534" t="str">
-        <v/>
-      </c>
-      <c r="R534" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S534" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="str">
-        <v>T260901-00015</v>
-      </c>
-      <c r="B535" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C535" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D535" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E535" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F535" t="str">
-        <v>천안FDC</v>
-      </c>
-      <c r="G535">
-        <v>1</v>
-      </c>
-      <c r="H535" t="str">
-        <v>청주FDC</v>
-      </c>
-      <c r="I535" t="str">
-        <v>충북 청주시 서원구 현도면 우록길 15-34 청주FDC</v>
-      </c>
-      <c r="J535" t="str">
-        <v>2026-09-01 22:00</v>
-      </c>
-      <c r="K535" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L535">
-        <v>1</v>
-      </c>
-      <c r="M535" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N535" t="str">
-        <v>2026-09-01 19:24:58</v>
-      </c>
-      <c r="O535" s="1">
-        <v>350000</v>
-      </c>
-      <c r="P535" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q535" t="str">
-        <v/>
-      </c>
-      <c r="R535" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S535" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="str">
-        <v>T260901-00014</v>
-      </c>
-      <c r="B536" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C536" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D536" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E536" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F536" t="str">
-        <v/>
-      </c>
-      <c r="G536">
-        <v>0</v>
-      </c>
-      <c r="H536" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="I536" t="str">
-        <v>인천 서구 오류동 1653-2 101호 인천FDC</v>
-      </c>
-      <c r="J536" t="str">
-        <v>2026-09-01 21:00</v>
-      </c>
-      <c r="K536" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L536">
-        <v>1</v>
-      </c>
-      <c r="M536" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N536" t="str">
-        <v>2026-09-01 19:24:38</v>
-      </c>
-      <c r="O536" s="1">
-        <v>260000</v>
-      </c>
-      <c r="P536" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q536" t="str">
-        <v/>
-      </c>
-      <c r="R536" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S536" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="str">
-        <v>T260901-00013</v>
-      </c>
-      <c r="B537" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C537" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D537" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E537" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F537" t="str">
-        <v>원주FDC(신규)</v>
-      </c>
-      <c r="G537">
-        <v>1</v>
-      </c>
-      <c r="H537" t="str">
-        <v>제천FDC</v>
-      </c>
-      <c r="I537" t="str">
-        <v>충북 제천시 봉양읍 장평로18 제천FDC</v>
-      </c>
-      <c r="J537" t="str">
-        <v>2026-09-01 22:00</v>
-      </c>
-      <c r="K537" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L537">
-        <v>1</v>
-      </c>
-      <c r="M537" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N537" t="str">
-        <v>2026-09-01 19:24:22</v>
-      </c>
-      <c r="O537" s="1">
-        <v>290000</v>
-      </c>
-      <c r="P537" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q537" t="str">
-        <v/>
-      </c>
-      <c r="R537" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S537" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="str">
-        <v>T260901-00012</v>
-      </c>
-      <c r="B538" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C538" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D538" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E538" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F538" t="str">
-        <v>진주FDC,창원FDC</v>
-      </c>
-      <c r="G538">
-        <v>2</v>
-      </c>
-      <c r="H538" t="str">
-        <v>양산FDC</v>
-      </c>
-      <c r="I538" t="str">
-        <v>경남 양산시 물금읍 제방로229 양산 ICD 3단지 동방 양산FDC</v>
-      </c>
-      <c r="J538" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K538" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L538">
-        <v>1</v>
-      </c>
-      <c r="M538" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N538" t="str">
-        <v>2026-09-01 19:23:57</v>
-      </c>
-      <c r="O538" s="1">
-        <v>730000</v>
-      </c>
-      <c r="P538" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q538" t="str">
-        <v/>
-      </c>
-      <c r="R538" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S538" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="str">
-        <v>T260901-00011</v>
-      </c>
-      <c r="B539" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C539" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D539" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E539" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F539" t="str">
-        <v>남양주FDC</v>
-      </c>
-      <c r="G539">
-        <v>1</v>
-      </c>
-      <c r="H539" t="str">
-        <v>김포FDC</v>
-      </c>
-      <c r="I539" t="str">
-        <v>경기 고양시 일산동구 문원길 82-5(지영동 413-36) 김포FDC</v>
-      </c>
-      <c r="J539" t="str">
-        <v>2026-09-01 22:00</v>
-      </c>
-      <c r="K539" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L539">
-        <v>1</v>
-      </c>
-      <c r="M539" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N539" t="str">
-        <v>2026-09-01 19:23:32</v>
-      </c>
-      <c r="O539" s="1">
-        <v>370000</v>
-      </c>
-      <c r="P539" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q539" t="str">
-        <v/>
-      </c>
-      <c r="R539" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S539" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="str">
-        <v>T260901-00010</v>
-      </c>
-      <c r="B540" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C540" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D540" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E540" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F540" t="str">
-        <v>전주FDC</v>
-      </c>
-      <c r="G540">
-        <v>1</v>
-      </c>
-      <c r="H540" t="str">
-        <v>광주FDC</v>
-      </c>
-      <c r="I540" t="str">
-        <v>광주광역시 광산구 연산동 1235 광주FDC</v>
-      </c>
-      <c r="J540" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K540" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L540">
-        <v>1</v>
-      </c>
-      <c r="M540" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N540" t="str">
-        <v>2026-09-01 19:23:13</v>
-      </c>
-      <c r="O540" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P540" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q540" t="str">
-        <v/>
-      </c>
-      <c r="R540" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S540" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="str">
-        <v>T260901-00009</v>
-      </c>
-      <c r="B541" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C541" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D541" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E541" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F541" t="str">
-        <v/>
-      </c>
-      <c r="G541">
-        <v>0</v>
-      </c>
-      <c r="H541" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="I541" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 819, 2동 곤지암FDC</v>
-      </c>
-      <c r="J541" t="str">
-        <v>2026-09-01 21:00</v>
-      </c>
-      <c r="K541" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L541">
-        <v>1</v>
-      </c>
-      <c r="M541" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N541" t="str">
-        <v>2026-09-01 19:22:26</v>
-      </c>
-      <c r="O541" s="1">
-        <v>200000</v>
-      </c>
-      <c r="P541" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q541" t="str">
-        <v/>
-      </c>
-      <c r="R541" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S541" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="str">
-        <v>T260901-00008</v>
-      </c>
-      <c r="B542" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C542" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D542" t="str">
-        <v>경기도 안성시 죽산면 장계리 161번지 안성FC</v>
-      </c>
-      <c r="E542" t="str">
-        <v>2026-09-01 19:00</v>
-      </c>
-      <c r="F542" t="str">
-        <v>구미FDC(신규)</v>
-      </c>
-      <c r="G542">
-        <v>1</v>
-      </c>
-      <c r="H542" t="str">
-        <v>경산FDC</v>
-      </c>
-      <c r="I542" t="str">
-        <v>경산시 자인면 일언리11-3 경산FDC</v>
-      </c>
-      <c r="J542" t="str">
-        <v>2026-09-01 23:00</v>
-      </c>
-      <c r="K542" t="str">
-        <v>11톤 윙바디</v>
-      </c>
-      <c r="L542">
-        <v>1</v>
-      </c>
-      <c r="M542" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N542" t="str">
-        <v>2026-09-01 19:22:10</v>
-      </c>
-      <c r="O542" s="1">
-        <v>520000</v>
-      </c>
-      <c r="P542" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q542" t="str">
-        <v/>
-      </c>
-      <c r="R542" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S542" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="str">
-        <v>T260901-00007</v>
-      </c>
-      <c r="B543" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C543" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D543" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="E543" t="str">
-        <v>2026-09-01 17:20</v>
-      </c>
-      <c r="F543" t="str">
-        <v/>
-      </c>
-      <c r="G543">
-        <v>0</v>
-      </c>
-      <c r="H543" t="str">
-        <v>한진택배</v>
-      </c>
-      <c r="I543" t="str">
-        <v>경기 안성시 미양면 미양로 752 한진 미양 영업소</v>
-      </c>
-      <c r="J543" t="str">
-        <v>2026-09-01 18:20</v>
-      </c>
-      <c r="K543" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L543">
-        <v>1</v>
-      </c>
-      <c r="M543" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N543" t="str">
-        <v>2026-09-01 19:20:06</v>
-      </c>
-      <c r="O543" s="1">
-        <v>100000</v>
-      </c>
-      <c r="P543" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q543" t="str">
-        <v/>
-      </c>
-      <c r="R543" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S543" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="str">
-        <v>T260901-00006</v>
-      </c>
-      <c r="B544" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C544" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="D544" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="E544" t="str">
-        <v>2026-09-01 11:20</v>
-      </c>
-      <c r="F544" t="str">
-        <v/>
-      </c>
-      <c r="G544">
-        <v>0</v>
-      </c>
-      <c r="H544" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I544" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J544" t="str">
-        <v>2026-09-01 13:20</v>
-      </c>
-      <c r="K544" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L544">
-        <v>1</v>
-      </c>
-      <c r="M544" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N544" t="str">
-        <v>2026-09-01 19:19:31</v>
-      </c>
-      <c r="O544" s="1">
-        <v>120000</v>
-      </c>
-      <c r="P544" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q544" t="str">
-        <v>거래처비용청구(2대)</v>
-      </c>
-      <c r="R544" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S544" t="str">
-        <v>샤오미</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="str">
-        <v>T260901-00005</v>
-      </c>
-      <c r="B545" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C545" t="str">
-        <v>아이베</v>
-      </c>
-      <c r="D545" t="str">
-        <v>경기 용인시 처인구 삼가동 146-15 아이베</v>
-      </c>
-      <c r="E545" t="str">
-        <v>2026-09-01 14:20</v>
-      </c>
-      <c r="F545" t="str">
-        <v/>
-      </c>
-      <c r="G545">
-        <v>0</v>
-      </c>
-      <c r="H545" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I545" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J545" t="str">
-        <v>2026-09-01 15:20</v>
-      </c>
-      <c r="K545" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L545">
-        <v>1</v>
-      </c>
-      <c r="M545" t="str">
-        <v>윤태구</v>
-      </c>
-      <c r="N545" t="str">
-        <v>2026-09-01 19:18:39</v>
-      </c>
-      <c r="O545" s="1">
-        <v>70000</v>
-      </c>
-      <c r="P545" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q545" t="str">
-        <v>아이베 외주사입고</v>
-      </c>
-      <c r="R545" t="str">
-        <v>JM컴퍼니</v>
-      </c>
-      <c r="S545" t="str">
-        <v>아이베(신규)</v>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="str">
-        <v>T260901-00004</v>
-      </c>
-      <c r="B546" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C546" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D546" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E546" t="str">
-        <v>2026-09-01 15:50</v>
-      </c>
-      <c r="F546" t="str">
-        <v/>
-      </c>
-      <c r="G546">
-        <v>0</v>
-      </c>
-      <c r="H546" t="str">
-        <v>공주 하이마트 하이얼</v>
-      </c>
-      <c r="I546" t="str">
-        <v>충남 공주시 탄천면 금백로 1299 공주 하이마트 물류</v>
-      </c>
-      <c r="J546" t="str">
-        <v>2026-09-02 15:00</v>
-      </c>
-      <c r="K546" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L546">
-        <v>1</v>
-      </c>
-      <c r="M546" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N546" t="str">
-        <v>2026-09-01 15:50:14</v>
-      </c>
-      <c r="O546" s="1">
-        <v>220000</v>
-      </c>
-      <c r="P546" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q546" t="str">
-        <v>하이얼 공주 하이마트 물류</v>
-      </c>
-      <c r="R546" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S546" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="str">
-        <v>T260901-00003</v>
-      </c>
-      <c r="B547" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C547" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="D547" t="str">
-        <v>경기 안성시 죽산면 장계리 161 1층 (주)위니온로지스</v>
-      </c>
-      <c r="E547" t="str">
-        <v>2026-09-01 15:35</v>
-      </c>
-      <c r="F547" t="str">
-        <v/>
-      </c>
-      <c r="G547">
-        <v>0</v>
-      </c>
-      <c r="H547" t="str">
-        <v>대구 하이마트 하이얼</v>
-      </c>
-      <c r="I547" t="str">
-        <v>경북 칠곡군 왜관읍 공단로6길 10 대구 하이마트 물류</v>
-      </c>
-      <c r="J547" t="str">
-        <v>2026-09-02 15:00</v>
-      </c>
-      <c r="K547" t="str">
-        <v>5톤 윙바디</v>
-      </c>
-      <c r="L547">
-        <v>1</v>
-      </c>
-      <c r="M547" t="str">
-        <v>박진실</v>
-      </c>
-      <c r="N547" t="str">
-        <v>2026-09-01 13:37:23</v>
-      </c>
-      <c r="O547" s="1">
-        <v>300000</v>
-      </c>
-      <c r="P547" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Q547" t="str">
-        <v>하이얼 대구 하이마트 물류</v>
-      </c>
-      <c r="R547" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S547" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="str">
-        <v>T260901-00002</v>
-      </c>
-      <c r="B548" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C548" t="str">
-        <v>인천FDC</v>
-      </c>
-      <c r="D548" t="str">
-        <v>인천 서구 오류동 1653-2 인천FDC</v>
-      </c>
-      <c r="E548" t="str">
-        <v>2026-09-02 08:00</v>
-      </c>
-      <c r="F548" t="str">
-        <v/>
-      </c>
-      <c r="G548">
-        <v>0</v>
-      </c>
-      <c r="H548" t="str">
-        <v>샤오미 집하장</v>
-      </c>
-      <c r="I548" t="str">
-        <v>인천 서해구 북항단지로 151 인천샤오미창고</v>
-      </c>
-      <c r="J548" t="str">
-        <v>2026-09-02 09:00</v>
-      </c>
-      <c r="K548" t="str">
-        <v>1톤 카고</v>
-      </c>
-      <c r="L548">
-        <v>1</v>
-      </c>
-      <c r="M548" t="str">
-        <v>차순권</v>
-      </c>
-      <c r="N548" t="str">
-        <v>2026-09-01 13:22:36</v>
-      </c>
-      <c r="O548" s="1">
-        <v>50000</v>
-      </c>
-      <c r="P548" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q548" t="str">
-        <v>접수번호 : 1565331 / 취소 건 샤오미 창고로 출하 / 인천FDC에서 직접 배송함</v>
-      </c>
-      <c r="R548" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S548" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="str">
-        <v>T260901-00001</v>
-      </c>
-      <c r="B549" t="str">
-        <v>운송완료</v>
-      </c>
-      <c r="C549" t="str">
-        <v>곤지암FDC</v>
-      </c>
-      <c r="D549" t="str">
-        <v>경기 용인시 처인구 모현읍 곡현로 821 곤지암FDC</v>
-      </c>
-      <c r="E549" t="str">
-        <v>2026-09-01 08:00</v>
-      </c>
-      <c r="F549" t="str">
-        <v/>
-      </c>
-      <c r="G549">
-        <v>0</v>
-      </c>
-      <c r="H549" t="str">
-        <v>안성FC</v>
-      </c>
-      <c r="I549" t="str">
-        <v>경기 안성시 죽산면 장계리 161 위니온로지스 안성HUB</v>
-      </c>
-      <c r="J549" t="str">
-        <v>2026-09-01 10:00</v>
-      </c>
-      <c r="K549" t="str">
-        <v>1톤 윙바디</v>
-      </c>
-      <c r="L549">
-        <v>1</v>
-      </c>
-      <c r="M549" t="str">
-        <v>차순권</v>
-      </c>
-      <c r="N549" t="str">
-        <v>2026-09-01 09:03:56</v>
-      </c>
-      <c r="O549" s="1">
-        <v>80000</v>
-      </c>
-      <c r="P549" s="1">
-        <v>5000</v>
-      </c>
-      <c r="Q549" t="str">
-        <v>하이얼 가용재고 10개 이동</v>
-      </c>
-      <c r="R549" t="str">
-        <v>(주)위니온로지스</v>
-      </c>
-      <c r="S549" t="str">
-        <v>하이얼</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S549"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S441"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -443,7 +443,7 @@
         <v>T261008-00017</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -502,7 +502,7 @@
         <v>T261008-00016</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -561,7 +561,7 @@
         <v>T261008-00015</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -620,7 +620,7 @@
         <v>T261008-00014</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -679,7 +679,7 @@
         <v>T261008-00013</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -738,7 +738,7 @@
         <v>T261008-00012</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -797,7 +797,7 @@
         <v>T261008-00011</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -856,7 +856,7 @@
         <v>T261008-00010</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -915,7 +915,7 @@
         <v>T261008-00009</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -974,7 +974,7 @@
         <v>T261008-00008</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1033,7 +1033,7 @@
         <v>T261008-00007</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1092,7 +1092,7 @@
         <v>T261008-00006</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1151,7 +1151,7 @@
         <v>T261008-00005</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>용인FDSYS</v>
@@ -1210,7 +1210,7 @@
         <v>T261008-00004</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>아이베</v>
@@ -1269,7 +1269,7 @@
         <v>T261008-00003</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -443,7 +443,7 @@
         <v>T261016-00024</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -502,7 +502,7 @@
         <v>T261016-00023</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -561,7 +561,7 @@
         <v>T261016-00022</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -620,7 +620,7 @@
         <v>T261016-00021</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -679,7 +679,7 @@
         <v>T261016-00020</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -738,7 +738,7 @@
         <v>T261016-00019</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -797,7 +797,7 @@
         <v>T261016-00018</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -856,7 +856,7 @@
         <v>T261016-00017</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -915,7 +915,7 @@
         <v>T261016-00016</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -974,7 +974,7 @@
         <v>T261016-00015</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1033,7 +1033,7 @@
         <v>T261016-00014</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1092,7 +1092,7 @@
         <v>T261016-00013</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1151,7 +1151,7 @@
         <v>T261016-00012</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1210,7 +1210,7 @@
         <v>T261016-00011</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1269,7 +1269,7 @@
         <v>T261016-00010</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>청주ARC</v>
@@ -1328,7 +1328,7 @@
         <v>T261016-00009</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>아이베</v>
@@ -1387,7 +1387,7 @@
         <v>T261016-00008</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -443,7 +443,7 @@
         <v>T261019-00022</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -502,7 +502,7 @@
         <v>T261019-00021</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -561,7 +561,7 @@
         <v>T261019-00020</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -620,7 +620,7 @@
         <v>T261019-00019</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -679,7 +679,7 @@
         <v>T261019-00018</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -738,7 +738,7 @@
         <v>T261019-00017</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -797,7 +797,7 @@
         <v>T261019-00016</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -856,7 +856,7 @@
         <v>T261019-00015</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -915,7 +915,7 @@
         <v>T261019-00014</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -974,7 +974,7 @@
         <v>T261019-00013</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1033,7 +1033,7 @@
         <v>T261019-00012</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1092,7 +1092,7 @@
         <v>T261019-00011</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1151,7 +1151,7 @@
         <v>T261019-00010</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>안성FC</v>
@@ -1210,7 +1210,7 @@
         <v>T261019-00009</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>안성FC</v>
@@ -1269,7 +1269,7 @@
         <v>T261019-00008</v>
       </c>
       <c r="B16" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C16" t="str">
         <v>김포FDC</v>
@@ -1328,7 +1328,7 @@
         <v>T261019-00007</v>
       </c>
       <c r="B17" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>아이베</v>
@@ -1387,7 +1387,7 @@
         <v>T261019-00006</v>
       </c>
       <c r="B18" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>듀오백</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -1328,7 +1328,7 @@
         <v>T261020-00004</v>
       </c>
       <c r="B17" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C17" t="str">
         <v>위니온 안성HUB</v>
@@ -1367,16 +1367,16 @@
         <v>2026-10-20 13:54:17</v>
       </c>
       <c r="O17" s="1">
-        <v>0</v>
+        <v>280000</v>
       </c>
       <c r="P17" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q17" t="str">
         <v>광주 하이마트 하이얼</v>
       </c>
       <c r="R17" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="S17" t="str">
         <v>하이얼</v>
@@ -1387,7 +1387,7 @@
         <v>T261020-00003</v>
       </c>
       <c r="B18" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C18" t="str">
         <v>위니온 안성HUB</v>
@@ -1426,16 +1426,16 @@
         <v>2026-10-20 13:14:15</v>
       </c>
       <c r="O18" s="1">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="P18" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q18" t="str">
         <v>대구 하이마트 하이얼</v>
       </c>
       <c r="R18" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="S18" t="str">
         <v>하이얼</v>
@@ -1446,7 +1446,7 @@
         <v>T261020-00002</v>
       </c>
       <c r="B19" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C19" t="str">
         <v>청주ARC</v>
@@ -1485,7 +1485,7 @@
         <v>2026-10-20 13:07:03</v>
       </c>
       <c r="O19" s="1">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="P19" s="1">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v/>
       </c>
       <c r="R19" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="S19" t="str">
         <v>일코전자</v>
@@ -1505,7 +1505,7 @@
         <v>T261020-00001</v>
       </c>
       <c r="B20" t="str">
-        <v>접수</v>
+        <v>운송완료</v>
       </c>
       <c r="C20" t="str">
         <v>위니온 안성HUB</v>
@@ -1544,16 +1544,16 @@
         <v>2026-10-20 13:00:07</v>
       </c>
       <c r="O20" s="1">
-        <v>0</v>
+        <v>340000</v>
       </c>
       <c r="P20" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q20" t="str">
         <v>마산 하이마트 하이얼</v>
       </c>
       <c r="R20" t="str">
-        <v/>
+        <v>(주)위니온로지스</v>
       </c>
       <c r="S20" t="str">
         <v>하이얼</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -443,7 +443,7 @@
         <v>T261023-00022</v>
       </c>
       <c r="B2" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C2" t="str">
         <v>안성FC</v>
@@ -502,7 +502,7 @@
         <v>T261023-00021</v>
       </c>
       <c r="B3" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C3" t="str">
         <v>안성FC</v>
@@ -561,7 +561,7 @@
         <v>T261023-00020</v>
       </c>
       <c r="B4" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C4" t="str">
         <v>안성FC</v>
@@ -620,7 +620,7 @@
         <v>T261023-00019</v>
       </c>
       <c r="B5" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C5" t="str">
         <v>안성FC</v>
@@ -679,7 +679,7 @@
         <v>T261023-00018</v>
       </c>
       <c r="B6" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C6" t="str">
         <v>안성FC</v>
@@ -738,7 +738,7 @@
         <v>T261023-00017</v>
       </c>
       <c r="B7" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C7" t="str">
         <v>안성FC</v>
@@ -797,7 +797,7 @@
         <v>T261023-00016</v>
       </c>
       <c r="B8" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C8" t="str">
         <v>안성FC</v>
@@ -856,7 +856,7 @@
         <v>T261023-00015</v>
       </c>
       <c r="B9" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C9" t="str">
         <v>안성FC</v>
@@ -915,7 +915,7 @@
         <v>T261023-00014</v>
       </c>
       <c r="B10" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C10" t="str">
         <v>안성FC</v>
@@ -974,7 +974,7 @@
         <v>T261023-00013</v>
       </c>
       <c r="B11" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C11" t="str">
         <v>안성FC</v>
@@ -1033,7 +1033,7 @@
         <v>T261023-00012</v>
       </c>
       <c r="B12" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C12" t="str">
         <v>안성FC</v>
@@ -1092,7 +1092,7 @@
         <v>T261023-00011</v>
       </c>
       <c r="B13" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C13" t="str">
         <v>안성FC</v>
@@ -1151,7 +1151,7 @@
         <v>T261023-00010</v>
       </c>
       <c r="B14" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C14" t="str">
         <v>아이베</v>
@@ -1210,7 +1210,7 @@
         <v>T261023-00009</v>
       </c>
       <c r="B15" t="str">
-        <v>배차완료</v>
+        <v>운송완료</v>
       </c>
       <c r="C15" t="str">
         <v>듀오백</v>
